--- a/簡易基本設計書【Laravel9】.xlsx
+++ b/簡易基本設計書【Laravel9】.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\daiki\Desktop\Atlas\AtlasSNS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9F5FA057-9626-44CD-9094-61FFD3426046}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{136070F9-DFF9-495E-BAA1-FA7BCD6F74D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="522" uniqueCount="335">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="521" uniqueCount="338">
   <si>
     <t>#環境準備</t>
   </si>
@@ -50,56 +50,6 @@
   </si>
   <si>
     <t>XAMPP/MAMP環境を用意する</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <u/>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-      </rPr>
-      <t>作業内容：
-■Laravelを動かすためのローカル環境を下記ツールで設定する。
-Macの人：MAMP
-Windowsの人：XAMPP</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <u/>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-      </rPr>
-      <t>■設定方法は</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <u/>
-        <sz val="10"/>
-        <color rgb="FF1155CC"/>
-        <rFont val="Arial"/>
-      </rPr>
-      <t>AtlasSNS環境構築手順書</t>
-    </r>
-    <r>
-      <rPr>
-        <u/>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-      </rPr>
-      <t>を参照。</t>
-    </r>
   </si>
   <si>
     <t>０２</t>
@@ -167,41 +117,10 @@
     <t>０４</t>
   </si>
   <si>
-    <t>マイグレーションでテーブルを作成する</t>
-  </si>
-  <si>
-    <t>作業内容：
-■課題フォルダ内に用意されたマイグレーションファイルを使いテーブルを作成する。</t>
-  </si>
-  <si>
     <t>０５</t>
   </si>
   <si>
-    <t>シードで初期ユーザーのデータを作成する</t>
-  </si>
-  <si>
-    <t>作業内容：
-■シードファイルを使いUsersテーブルに初期ユーザーのデータを登録する。
-■シードファイルは自身で作成する。
-■登録する値として「ユーザー名」「メールアドレス」「パスワード」は必須で登録する。
-■「パスワード」は暗号化処理を行って登録する。</t>
-  </si>
-  <si>
     <t>#ユーザー登録 / 登録完了 / ログイン</t>
-  </si>
-  <si>
-    <t>ユーザーの新規登録/ログイン処理を実装する</t>
-  </si>
-  <si>
-    <t>対象画面： 新規ユーザー登録ページ、ログインページ
-作業内容：
-■新規ユーザー登録ページ：
-・ルーティングを確認して正しく処理されるように記述する。
-■ログインページ：
-・ルーティングを確認して正しく処理されるように記述する。</t>
-  </si>
-  <si>
-    <t>ユーザーの新規登録処理にバリデーション処理を実装する</t>
   </si>
   <si>
     <t>対象画面： 新規ユーザー登録ページ
@@ -219,13 +138,6 @@
   </si>
   <si>
     <t>ログイン後に表示するページにアクセス制限をかける</t>
-  </si>
-  <si>
-    <t>対象画面： トップページ、プロフィール編集ページ、ユーザー検索ページ、フォローリストページ、フォロワーリストページ、相手ユーザーのプロフィールページ
-作業内容：
-■対象ページをログイン中のみ表示できるように制限をかける。
-■ログアウト中に対象ページを表示しようとした場合、ログインページへ遷移するように設定する。
-■今回はミドルウェアを用いて実装する。</t>
   </si>
   <si>
     <t>#共通ヘッダー&amp;サイドバー</t>
@@ -867,9 +779,6 @@
     <t>https://xd.adobe.com/view/2b948973-e752-4367-60d2-e0cf9adc8747-5da5/?hints=off</t>
   </si>
   <si>
-    <t>パスワード：AtlasSNS00</t>
-  </si>
-  <si>
     <t>ページ名</t>
   </si>
   <si>
@@ -1599,12 +1508,6 @@
 ・ログインしているユーザーの登録しているメールアドレスと一致しているか</t>
   </si>
   <si>
-    <t>・入力必須
-・5文字以上,40文字以内
-・登録済みメールアドレス使用不可
-・メールアドレスの形式</t>
-  </si>
-  <si>
     <t>Password</t>
   </si>
   <si>
@@ -1619,9 +1522,6 @@
   <si>
     <t>└ログインについては追加でバリデーション処理をつけなくて大丈夫です。
 （元々記述があるLaravelのAuthによる認証処理で実装できています）</t>
-  </si>
-  <si>
-    <t>PasswordConfirm</t>
   </si>
   <si>
     <t>・入力必須
@@ -1763,12 +1663,789 @@
     </r>
     <phoneticPr fontId="24"/>
   </si>
+  <si>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t xml:space="preserve">作業内容：
+</t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Segoe UI Symbol"/>
+        <family val="2"/>
+      </rPr>
+      <t>■</t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Laravel</t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t xml:space="preserve">を動かすためのローカル環境を下記ツールで設定する。
+</t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Mac</t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>の人：</t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>MAMP
+Windows</t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>の人：</t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>XAMPP</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Segoe UI Symbol"/>
+        <family val="2"/>
+      </rPr>
+      <t>■</t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>設定方法は</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <u/>
+        <sz val="10"/>
+        <color rgb="FF1155CC"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t>AtlasSNS</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <u/>
+        <sz val="10"/>
+        <color rgb="FF1155CC"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>環境構築手順書</t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>を参照。</t>
+    </r>
+    <phoneticPr fontId="24"/>
+  </si>
+  <si>
+    <t>マイグレーションでテーブルを作成する</t>
+    <phoneticPr fontId="24"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t xml:space="preserve">作業内容：
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Symbol"/>
+        <family val="2"/>
+      </rPr>
+      <t>■</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>課題フォルダ内に用意されたマイグレーションファイルを使いテーブルを作成する。</t>
+    </r>
+    <phoneticPr fontId="24"/>
+  </si>
+  <si>
+    <t>シードで初期ユーザーのデータを作成する</t>
+    <phoneticPr fontId="24"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t xml:space="preserve">作業内容：
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Symbol"/>
+        <family val="2"/>
+      </rPr>
+      <t>■</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>シードファイルを使い</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Users</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t xml:space="preserve">テーブルに初期ユーザーのデータを登録する。
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Symbol"/>
+        <family val="2"/>
+      </rPr>
+      <t>■</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t xml:space="preserve">シードファイルは自身で作成する。
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Symbol"/>
+        <family val="2"/>
+      </rPr>
+      <t>■</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t xml:space="preserve">登録する値として「ユーザー名」「メールアドレス」「パスワード」は必須で登録する。
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Symbol"/>
+        <family val="2"/>
+      </rPr>
+      <t>■</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>「パスワード」は暗号化処理を行って登録する。</t>
+    </r>
+    <phoneticPr fontId="24"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>対象画面：</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t xml:space="preserve">新規ユーザー登録ページ、ログインページ
+作業内容：
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Symbol"/>
+        <family val="2"/>
+      </rPr>
+      <t>■</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t xml:space="preserve">新規ユーザー登録ページ：
+・ルーティングを確認して正しく処理されるように記述する。
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Symbol"/>
+        <family val="2"/>
+      </rPr>
+      <t>■</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>ログインページ：
+・ルーティングを確認して正しく処理されるように記述する。</t>
+    </r>
+    <phoneticPr fontId="24"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>パスワード：</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>AtlasSNS00</t>
+    </r>
+    <phoneticPr fontId="24"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>ユーザーの新規登録</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>ログイン処理を実装する</t>
+    </r>
+    <phoneticPr fontId="24"/>
+  </si>
+  <si>
+    <t>ユーザーの新規登録処理にバリデーション処理を実装する</t>
+    <phoneticPr fontId="24"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>・入力必須
+・</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>5</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>文字以上</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>,40</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>文字以内
+・登録済みメールアドレス使用不可
+・メールアドレスの形式</t>
+    </r>
+    <phoneticPr fontId="24"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>・入力必須
+・</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>文字以上</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>,12</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>文字以内</t>
+    </r>
+    <phoneticPr fontId="24"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>・入力必須
+・英数字のみ
+・</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>8</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>文字以上</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>,20</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>文字以内</t>
+    </r>
+    <phoneticPr fontId="24"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>・入力必須
+・英数字のみ
+・</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>8</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>文字以上</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>,20</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>文字以内
+・</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Password</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>入力欄と一致しているか</t>
+    </r>
+    <phoneticPr fontId="24"/>
+  </si>
+  <si>
+    <t>PasswordConfirm</t>
+    <phoneticPr fontId="24"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>対象画面：</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t xml:space="preserve">トップページ、プロフィール編集ページ、ユーザー検索ページ、フォローリストページ、フォロワーリストページ、相手ユーザーのプロフィールページ
+作業内容：
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Symbol"/>
+        <family val="2"/>
+      </rPr>
+      <t>■</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t xml:space="preserve">対象ページをログイン中のみ表示できるように制限をかける。
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Symbol"/>
+        <family val="2"/>
+      </rPr>
+      <t>■</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t xml:space="preserve">ログアウト中に対象ページを表示しようとした場合、ログインページへ遷移するように設定する。
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Symbol"/>
+        <family val="2"/>
+      </rPr>
+      <t>■</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>今回はミドルウェアを用いて実装する。</t>
+    </r>
+    <phoneticPr fontId="24"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="29" x14ac:knownFonts="1">
+  <fonts count="34" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -1932,6 +2609,45 @@
     <font>
       <sz val="10"/>
       <color theme="1"/>
+      <name val="Arial"/>
+      <family val="3"/>
+      <charset val="128"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="ＭＳ ゴシック"/>
+      <family val="3"/>
+      <charset val="128"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <u/>
+      <sz val="10"/>
+      <color rgb="FF1155CC"/>
+      <name val="ＭＳ ゴシック"/>
+      <family val="3"/>
+      <charset val="128"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Segoe UI Symbol"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="10"/>
+      <color rgb="FF0000FF"/>
       <name val="Arial"/>
       <family val="3"/>
       <charset val="128"/>
@@ -2202,7 +2918,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="85">
+  <cellXfs count="93">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -2358,6 +3074,34 @@
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="13" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="13" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="13" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="13" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="13" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="13" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="28" fillId="13" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="13" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="13" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="13" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -2372,16 +3116,6 @@
     <xf numFmtId="0" fontId="17" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="13" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="13" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="13" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="標準" xfId="0" builtinId="0"/>
@@ -3741,7 +4475,7 @@
     <col min="4" max="4" width="81.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A2" s="1"/>
       <c r="B2" s="2" t="s">
         <v>0</v>
@@ -3771,7 +4505,7 @@
       <c r="Y2" s="1"/>
       <c r="Z2" s="1"/>
     </row>
-    <row r="3" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A3" s="1"/>
       <c r="B3" s="4" t="s">
         <v>1</v>
@@ -3805,71 +4539,71 @@
       <c r="Y3" s="1"/>
       <c r="Z3" s="1"/>
     </row>
-    <row r="4" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="B4" s="81">
+    <row r="4" spans="1:26" ht="66" x14ac:dyDescent="0.25">
+      <c r="B4" s="69">
         <v>1</v>
       </c>
-      <c r="C4" s="82" t="s">
+      <c r="C4" s="70" t="s">
         <v>5</v>
       </c>
-      <c r="D4" s="83" t="s">
-        <v>6</v>
+      <c r="D4" s="72" t="s">
+        <v>323</v>
       </c>
       <c r="F4" s="10"/>
     </row>
-    <row r="5" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="B5" s="7" t="s">
+    <row r="5" spans="1:26" ht="38.25" x14ac:dyDescent="0.2">
+      <c r="B5" s="69">
+        <v>2</v>
+      </c>
+      <c r="C5" s="70" t="s">
         <v>7</v>
       </c>
-      <c r="C5" s="8" t="s">
+      <c r="D5" s="71" t="s">
         <v>8</v>
       </c>
-      <c r="D5" s="9" t="s">
+    </row>
+    <row r="6" spans="1:26" ht="64.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B6" s="69" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="6" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B6" s="7" t="s">
+      <c r="C6" s="70" t="s">
         <v>10</v>
       </c>
-      <c r="C6" s="8" t="s">
+      <c r="D6" s="73" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="7" spans="1:26" ht="54.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B7" s="69" t="s">
         <v>11</v>
       </c>
-      <c r="D6" s="84" t="s">
-        <v>334</v>
-      </c>
-    </row>
-    <row r="7" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="B7" s="7" t="s">
+      <c r="C7" s="74" t="s">
+        <v>324</v>
+      </c>
+      <c r="D7" s="73" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="8" spans="1:26" ht="81" x14ac:dyDescent="0.25">
+      <c r="B8" s="69" t="s">
         <v>12</v>
       </c>
-      <c r="C7" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D7" s="11" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="8" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="B8" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="C8" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="D8" s="11" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="9" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="C8" s="74" t="s">
+        <v>326</v>
+      </c>
+      <c r="D8" s="73" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="9" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="B9" s="12"/>
       <c r="C9" s="13"/>
       <c r="D9" s="13"/>
     </row>
-    <row r="10" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:26" ht="38.25" x14ac:dyDescent="0.2">
       <c r="A10" s="1"/>
       <c r="B10" s="14" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="C10" s="3"/>
       <c r="D10" s="3"/>
@@ -3896,7 +4630,7 @@
       <c r="Y10" s="1"/>
       <c r="Z10" s="1"/>
     </row>
-    <row r="11" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A11" s="1"/>
       <c r="B11" s="4" t="s">
         <v>1</v>
@@ -3930,59 +4664,59 @@
       <c r="Y11" s="1"/>
       <c r="Z11" s="1"/>
     </row>
-    <row r="12" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="B12" s="7" t="s">
+    <row r="12" spans="1:26" ht="78" x14ac:dyDescent="0.2">
+      <c r="B12" s="69" t="s">
         <v>4</v>
       </c>
-      <c r="C12" s="8" t="s">
-        <v>19</v>
-      </c>
-      <c r="D12" s="11" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="13" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="B13" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="C13" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="D13" s="15" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="14" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="B14" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="C14" s="8" t="s">
-        <v>23</v>
-      </c>
-      <c r="D14" s="11" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="15" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="B15" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="C15" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="D15" s="11" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="16" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="C12" s="76" t="s">
+        <v>330</v>
+      </c>
+      <c r="D12" s="73" t="s">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="13" spans="1:26" ht="51" x14ac:dyDescent="0.2">
+      <c r="B13" s="69" t="s">
+        <v>6</v>
+      </c>
+      <c r="C13" s="74" t="s">
+        <v>331</v>
+      </c>
+      <c r="D13" s="80" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="14" spans="1:26" ht="38.25" x14ac:dyDescent="0.2">
+      <c r="B14" s="69" t="s">
+        <v>9</v>
+      </c>
+      <c r="C14" s="70" t="s">
+        <v>15</v>
+      </c>
+      <c r="D14" s="79" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="15" spans="1:26" ht="119.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B15" s="69" t="s">
+        <v>11</v>
+      </c>
+      <c r="C15" s="70" t="s">
+        <v>17</v>
+      </c>
+      <c r="D15" s="73" t="s">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="16" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="B16" s="12"/>
       <c r="C16" s="13"/>
       <c r="D16" s="13"/>
     </row>
-    <row r="17" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:26" ht="38.25" x14ac:dyDescent="0.2">
       <c r="A17" s="1"/>
       <c r="B17" s="14" t="s">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="C17" s="3"/>
       <c r="D17" s="3"/>
@@ -4009,7 +4743,7 @@
       <c r="Y17" s="1"/>
       <c r="Z17" s="1"/>
     </row>
-    <row r="18" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A18" s="1"/>
       <c r="B18" s="4" t="s">
         <v>1</v>
@@ -4043,92 +4777,92 @@
       <c r="Y18" s="1"/>
       <c r="Z18" s="1"/>
     </row>
-    <row r="19" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:26" ht="38.25" x14ac:dyDescent="0.2">
       <c r="B19" s="7" t="s">
         <v>4</v>
       </c>
       <c r="C19" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="D19" s="11" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="20" spans="1:26" ht="76.5" x14ac:dyDescent="0.2">
+      <c r="B20" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="C20" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="D20" s="16" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="21" spans="1:26" ht="63.75" x14ac:dyDescent="0.2">
+      <c r="B21" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="C21" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="D21" s="11" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="22" spans="1:26" ht="38.25" x14ac:dyDescent="0.2">
+      <c r="B22" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="C22" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="D22" s="11" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="23" spans="1:26" ht="38.25" x14ac:dyDescent="0.2">
+      <c r="B23" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="C23" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="D23" s="11" t="s">
         <v>28</v>
       </c>
-      <c r="D19" s="11" t="s">
+    </row>
+    <row r="24" spans="1:26" ht="76.5" x14ac:dyDescent="0.2">
+      <c r="B24" s="7" t="s">
         <v>29</v>
       </c>
-    </row>
-    <row r="20" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="B20" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="C20" s="8" t="s">
+      <c r="C24" s="8" t="s">
         <v>30</v>
       </c>
-      <c r="D20" s="16" t="s">
+      <c r="D24" s="11" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="21" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="B21" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="C21" s="8" t="s">
+    <row r="25" spans="1:26" ht="38.25" x14ac:dyDescent="0.2">
+      <c r="B25" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="D21" s="11" t="s">
+      <c r="C25" s="8" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="22" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="B22" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="C22" s="8" t="s">
+      <c r="D25" s="11" t="s">
         <v>34</v>
       </c>
-      <c r="D22" s="11" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="23" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="B23" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="C23" s="8" t="s">
-        <v>36</v>
-      </c>
-      <c r="D23" s="11" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="24" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="B24" s="7" t="s">
-        <v>38</v>
-      </c>
-      <c r="C24" s="8" t="s">
-        <v>39</v>
-      </c>
-      <c r="D24" s="11" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="25" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="B25" s="7" t="s">
-        <v>41</v>
-      </c>
-      <c r="C25" s="8" t="s">
-        <v>42</v>
-      </c>
-      <c r="D25" s="11" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="26" spans="1:26" x14ac:dyDescent="0.2">
+    </row>
+    <row r="26" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="B26" s="12"/>
       <c r="C26" s="13"/>
       <c r="D26" s="13"/>
     </row>
-    <row r="27" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A27" s="1"/>
       <c r="B27" s="14" t="s">
-        <v>44</v>
+        <v>35</v>
       </c>
       <c r="C27" s="3"/>
       <c r="D27" s="3"/>
@@ -4155,7 +4889,7 @@
       <c r="Y27" s="1"/>
       <c r="Z27" s="1"/>
     </row>
-    <row r="28" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A28" s="1"/>
       <c r="B28" s="4" t="s">
         <v>1</v>
@@ -4189,70 +4923,70 @@
       <c r="Y28" s="1"/>
       <c r="Z28" s="1"/>
     </row>
-    <row r="29" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:26" ht="76.5" x14ac:dyDescent="0.2">
       <c r="B29" s="7" t="s">
         <v>4</v>
       </c>
       <c r="C29" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="D29" s="11" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="30" spans="1:26" ht="63.75" x14ac:dyDescent="0.2">
+      <c r="B30" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="C30" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="D30" s="9" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="31" spans="1:26" ht="76.5" x14ac:dyDescent="0.2">
+      <c r="B31" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="C31" s="8" t="s">
+        <v>40</v>
+      </c>
+      <c r="D31" s="11" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="32" spans="1:26" ht="76.5" x14ac:dyDescent="0.2">
+      <c r="B32" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="C32" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="D32" s="11" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="33" spans="1:26" ht="140.25" x14ac:dyDescent="0.2">
+      <c r="B33" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="C33" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="D33" s="11" t="s">
         <v>45</v>
       </c>
-      <c r="D29" s="11" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="30" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="B30" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="C30" s="8" t="s">
-        <v>47</v>
-      </c>
-      <c r="D30" s="9" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="31" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="B31" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="C31" s="8" t="s">
-        <v>49</v>
-      </c>
-      <c r="D31" s="11" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="32" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="B32" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="C32" s="8" t="s">
-        <v>51</v>
-      </c>
-      <c r="D32" s="11" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="33" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="B33" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="C33" s="8" t="s">
-        <v>53</v>
-      </c>
-      <c r="D33" s="11" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="34" spans="1:26" x14ac:dyDescent="0.2">
+    </row>
+    <row r="34" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="B34" s="12"/>
       <c r="C34" s="13"/>
       <c r="D34" s="13"/>
     </row>
-    <row r="35" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:26" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A35" s="1"/>
       <c r="B35" s="14" t="s">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="C35" s="3"/>
       <c r="D35" s="3"/>
@@ -4279,7 +5013,7 @@
       <c r="Y35" s="1"/>
       <c r="Z35" s="1"/>
     </row>
-    <row r="36" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A36" s="1"/>
       <c r="B36" s="4" t="s">
         <v>1</v>
@@ -4313,70 +5047,70 @@
       <c r="Y36" s="1"/>
       <c r="Z36" s="1"/>
     </row>
-    <row r="37" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:26" ht="63.75" x14ac:dyDescent="0.2">
       <c r="B37" s="7" t="s">
         <v>4</v>
       </c>
       <c r="C37" s="8" t="s">
+        <v>47</v>
+      </c>
+      <c r="D37" s="15" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="38" spans="1:26" ht="127.5" x14ac:dyDescent="0.2">
+      <c r="B38" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="C38" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="D38" s="11" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="39" spans="1:26" ht="38.25" x14ac:dyDescent="0.2">
+      <c r="B39" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="C39" s="8" t="s">
+        <v>51</v>
+      </c>
+      <c r="D39" s="11" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="40" spans="1:26" ht="63.75" x14ac:dyDescent="0.2">
+      <c r="B40" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="C40" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="D40" s="11" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="41" spans="1:26" ht="89.25" x14ac:dyDescent="0.2">
+      <c r="B41" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="C41" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="D41" s="11" t="s">
         <v>56</v>
       </c>
-      <c r="D37" s="15" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="38" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="B38" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="C38" s="8" t="s">
-        <v>58</v>
-      </c>
-      <c r="D38" s="11" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="39" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="B39" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="C39" s="8" t="s">
-        <v>60</v>
-      </c>
-      <c r="D39" s="11" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="40" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="B40" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="C40" s="8" t="s">
-        <v>62</v>
-      </c>
-      <c r="D40" s="11" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="41" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="B41" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="C41" s="8" t="s">
-        <v>64</v>
-      </c>
-      <c r="D41" s="11" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="42" spans="1:26" x14ac:dyDescent="0.2">
+    </row>
+    <row r="42" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="B42" s="12"/>
       <c r="C42" s="13"/>
       <c r="D42" s="13"/>
     </row>
-    <row r="43" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:26" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A43" s="1"/>
       <c r="B43" s="14" t="s">
-        <v>66</v>
+        <v>57</v>
       </c>
       <c r="C43" s="3"/>
       <c r="D43" s="3"/>
@@ -4403,7 +5137,7 @@
       <c r="Y43" s="1"/>
       <c r="Z43" s="1"/>
     </row>
-    <row r="44" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A44" s="1"/>
       <c r="B44" s="4" t="s">
         <v>1</v>
@@ -4437,48 +5171,48 @@
       <c r="Y44" s="1"/>
       <c r="Z44" s="1"/>
     </row>
-    <row r="45" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:26" ht="38.25" x14ac:dyDescent="0.2">
       <c r="B45" s="7" t="s">
         <v>4</v>
       </c>
       <c r="C45" s="8" t="s">
-        <v>67</v>
+        <v>58</v>
       </c>
       <c r="D45" s="11" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="46" spans="1:26" x14ac:dyDescent="0.2">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="46" spans="1:26" ht="102" x14ac:dyDescent="0.2">
       <c r="B46" s="7" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C46" s="8" t="s">
-        <v>69</v>
+        <v>60</v>
       </c>
       <c r="D46" s="11" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="47" spans="1:26" x14ac:dyDescent="0.2">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="47" spans="1:26" ht="51" x14ac:dyDescent="0.2">
       <c r="B47" s="7" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C47" s="8" t="s">
-        <v>71</v>
+        <v>62</v>
       </c>
       <c r="D47" s="11" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="48" spans="1:26" x14ac:dyDescent="0.2">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="48" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="B48" s="12"/>
       <c r="C48" s="13"/>
       <c r="D48" s="13"/>
     </row>
-    <row r="49" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:26" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A49" s="1"/>
       <c r="B49" s="14" t="s">
-        <v>73</v>
+        <v>64</v>
       </c>
       <c r="C49" s="3"/>
       <c r="D49" s="3"/>
@@ -4505,7 +5239,7 @@
       <c r="Y49" s="1"/>
       <c r="Z49" s="1"/>
     </row>
-    <row r="50" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A50" s="1"/>
       <c r="B50" s="4" t="s">
         <v>1</v>
@@ -4539,48 +5273,48 @@
       <c r="Y50" s="1"/>
       <c r="Z50" s="1"/>
     </row>
-    <row r="51" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:26" ht="38.25" x14ac:dyDescent="0.2">
       <c r="B51" s="7" t="s">
         <v>4</v>
       </c>
       <c r="C51" s="8" t="s">
+        <v>58</v>
+      </c>
+      <c r="D51" s="11" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="52" spans="1:26" ht="102" x14ac:dyDescent="0.2">
+      <c r="B52" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="C52" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="D52" s="11" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="53" spans="1:26" ht="51" x14ac:dyDescent="0.2">
+      <c r="B53" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="C53" s="8" t="s">
+        <v>62</v>
+      </c>
+      <c r="D53" s="11" t="s">
         <v>67</v>
       </c>
-      <c r="D51" s="11" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="52" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="B52" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="C52" s="8" t="s">
-        <v>69</v>
-      </c>
-      <c r="D52" s="11" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="53" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="B53" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="C53" s="8" t="s">
-        <v>71</v>
-      </c>
-      <c r="D53" s="11" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="54" spans="1:26" x14ac:dyDescent="0.2">
+    </row>
+    <row r="54" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="B54" s="12"/>
       <c r="C54" s="13"/>
       <c r="D54" s="13"/>
     </row>
-    <row r="55" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:26" ht="38.25" x14ac:dyDescent="0.2">
       <c r="A55" s="1"/>
       <c r="B55" s="14" t="s">
-        <v>77</v>
+        <v>68</v>
       </c>
       <c r="C55" s="3"/>
       <c r="D55" s="3"/>
@@ -4607,7 +5341,7 @@
       <c r="Y55" s="1"/>
       <c r="Z55" s="1"/>
     </row>
-    <row r="56" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A56" s="1"/>
       <c r="B56" s="4" t="s">
         <v>1</v>
@@ -4641,59 +5375,59 @@
       <c r="Y56" s="1"/>
       <c r="Z56" s="1"/>
     </row>
-    <row r="57" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:26" ht="38.25" x14ac:dyDescent="0.2">
       <c r="B57" s="7" t="s">
         <v>4</v>
       </c>
       <c r="C57" s="8" t="s">
-        <v>78</v>
+        <v>69</v>
       </c>
       <c r="D57" s="11" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="58" spans="1:26" x14ac:dyDescent="0.2">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="58" spans="1:26" ht="63.75" x14ac:dyDescent="0.2">
       <c r="B58" s="7" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C58" s="8" t="s">
-        <v>62</v>
+        <v>53</v>
       </c>
       <c r="D58" s="11" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="59" spans="1:26" x14ac:dyDescent="0.2">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="59" spans="1:26" ht="89.25" x14ac:dyDescent="0.2">
       <c r="B59" s="7" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C59" s="8" t="s">
-        <v>64</v>
+        <v>55</v>
       </c>
       <c r="D59" s="11" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="60" spans="1:26" x14ac:dyDescent="0.2">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="60" spans="1:26" ht="102" x14ac:dyDescent="0.2">
       <c r="B60" s="7" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C60" s="8" t="s">
-        <v>69</v>
+        <v>60</v>
       </c>
       <c r="D60" s="11" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="61" spans="1:26" x14ac:dyDescent="0.2">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="61" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="B61" s="12"/>
       <c r="C61" s="13"/>
       <c r="D61" s="13"/>
     </row>
-    <row r="62" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:26" ht="51" x14ac:dyDescent="0.2">
       <c r="A62" s="17"/>
       <c r="B62" s="14" t="s">
-        <v>83</v>
+        <v>74</v>
       </c>
       <c r="C62" s="18"/>
       <c r="D62" s="18"/>
@@ -4720,7 +5454,7 @@
       <c r="Y62" s="17"/>
       <c r="Z62" s="17"/>
     </row>
-    <row r="63" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A63" s="17"/>
       <c r="B63" s="4" t="s">
         <v>1</v>
@@ -4754,48 +5488,48 @@
       <c r="Y63" s="17"/>
       <c r="Z63" s="17"/>
     </row>
-    <row r="64" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:26" ht="63.75" x14ac:dyDescent="0.2">
       <c r="B64" s="7" t="s">
         <v>4</v>
       </c>
       <c r="C64" s="8" t="s">
-        <v>84</v>
+        <v>75</v>
       </c>
       <c r="D64" s="11" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="65" spans="2:4" x14ac:dyDescent="0.2">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="65" spans="2:4" ht="89.25" x14ac:dyDescent="0.2">
       <c r="B65" s="7" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C65" s="8" t="s">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="D65" s="11" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="66" spans="2:4" x14ac:dyDescent="0.2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="66" spans="2:4" ht="51" x14ac:dyDescent="0.2">
       <c r="B66" s="7" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C66" s="8" t="s">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="D66" s="9" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="67" spans="2:4" x14ac:dyDescent="0.2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="67" spans="2:4" ht="38.25" x14ac:dyDescent="0.2">
       <c r="B67" s="7" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C67" s="8" t="s">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="D67" s="11" t="s">
-        <v>91</v>
+        <v>82</v>
       </c>
     </row>
   </sheetData>
@@ -4810,6 +5544,7 @@
     <hyperlink ref="D66" location="'バリデーション設定'!A1" display="対象画面： プロフィール編集ページ_x000a_作業内容：_x000a_■入力値に対してバリデーションを適用し、メッセージを表示させる_x000a_■バリデーションの条件は「簡易基本設計書」を参照" xr:uid="{00000000-0004-0000-0100-000006000000}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId5"/>
 </worksheet>
 </file>
 
@@ -4828,12 +5563,12 @@
   <sheetData>
     <row r="1" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="13" t="s">
-        <v>92</v>
+        <v>83</v>
       </c>
     </row>
     <row r="2" spans="1:26" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="19" t="s">
-        <v>93</v>
+        <v>84</v>
       </c>
       <c r="B2" s="10"/>
       <c r="C2" s="10"/>
@@ -4866,18 +5601,18 @@
     </row>
     <row r="4" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="13" t="s">
-        <v>94</v>
+        <v>85</v>
       </c>
     </row>
     <row r="5" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="69" t="s">
-        <v>95</v>
-      </c>
-      <c r="B5" s="70"/>
-      <c r="C5" s="70"/>
-      <c r="D5" s="70"/>
-      <c r="E5" s="70"/>
-      <c r="F5" s="70"/>
+      <c r="A5" s="81" t="s">
+        <v>86</v>
+      </c>
+      <c r="B5" s="82"/>
+      <c r="C5" s="82"/>
+      <c r="D5" s="82"/>
+      <c r="E5" s="82"/>
+      <c r="F5" s="82"/>
       <c r="K5" s="13"/>
     </row>
     <row r="6" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -4886,19 +5621,19 @@
     </row>
     <row r="7" spans="1:26" ht="56.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="13" t="s">
-        <v>96</v>
+        <v>87</v>
       </c>
       <c r="K7" s="19"/>
     </row>
     <row r="8" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="20" t="s">
-        <v>97</v>
+        <v>88</v>
       </c>
       <c r="K8" s="13"/>
     </row>
     <row r="9" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="13" t="s">
-        <v>98</v>
+      <c r="A9" s="75" t="s">
+        <v>329</v>
       </c>
       <c r="K9" s="21"/>
     </row>
@@ -5937,10 +6672,10 @@
   <sheetData>
     <row r="1" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="23" t="s">
-        <v>99</v>
+        <v>89</v>
       </c>
       <c r="B1" s="24" t="s">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="C1" s="25"/>
       <c r="D1" s="25"/>
@@ -5948,25 +6683,25 @@
     <row r="2" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="25"/>
       <c r="B2" s="26" t="s">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="C2" s="26" t="s">
-        <v>102</v>
+        <v>92</v>
       </c>
       <c r="D2" s="27" t="s">
-        <v>103</v>
+        <v>93</v>
       </c>
     </row>
     <row r="3" spans="1:5" ht="44.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="25"/>
       <c r="B3" s="28" t="s">
-        <v>104</v>
+        <v>94</v>
       </c>
       <c r="C3" s="28" t="s">
-        <v>105</v>
+        <v>95</v>
       </c>
       <c r="D3" s="29" t="s">
-        <v>106</v>
+        <v>96</v>
       </c>
       <c r="E3" s="30"/>
     </row>
@@ -5979,7 +6714,7 @@
     <row r="5" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="25"/>
       <c r="B5" s="24" t="s">
-        <v>107</v>
+        <v>97</v>
       </c>
       <c r="C5" s="25"/>
       <c r="D5" s="32"/>
@@ -5987,25 +6722,25 @@
     <row r="6" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="25"/>
       <c r="B6" s="26" t="s">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="C6" s="26" t="s">
-        <v>102</v>
+        <v>92</v>
       </c>
       <c r="D6" s="27" t="s">
-        <v>103</v>
+        <v>93</v>
       </c>
     </row>
     <row r="7" spans="1:5" ht="46.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="25"/>
       <c r="B7" s="28" t="s">
-        <v>107</v>
+        <v>97</v>
       </c>
       <c r="C7" s="28" t="s">
-        <v>108</v>
+        <v>98</v>
       </c>
       <c r="D7" s="29" t="s">
-        <v>109</v>
+        <v>99</v>
       </c>
     </row>
     <row r="8" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -6017,7 +6752,7 @@
     <row r="9" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="25"/>
       <c r="B9" s="24" t="s">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="C9" s="25"/>
       <c r="D9" s="25"/>
@@ -6025,22 +6760,22 @@
     <row r="10" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="25"/>
       <c r="B10" s="26" t="s">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="C10" s="26" t="s">
-        <v>102</v>
+        <v>92</v>
       </c>
       <c r="D10" s="27" t="s">
-        <v>103</v>
+        <v>93</v>
       </c>
     </row>
     <row r="11" spans="1:5" ht="34.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="25"/>
       <c r="B11" s="28" t="s">
-        <v>111</v>
+        <v>101</v>
       </c>
       <c r="C11" s="28" t="s">
-        <v>112</v>
+        <v>102</v>
       </c>
       <c r="D11" s="29"/>
     </row>
@@ -6053,7 +6788,7 @@
     <row r="13" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="25"/>
       <c r="B13" s="24" t="s">
-        <v>113</v>
+        <v>103</v>
       </c>
       <c r="C13" s="25"/>
       <c r="D13" s="25"/>
@@ -6061,61 +6796,61 @@
     <row r="14" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="25"/>
       <c r="B14" s="26" t="s">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="C14" s="26" t="s">
-        <v>102</v>
+        <v>92</v>
       </c>
       <c r="D14" s="27" t="s">
-        <v>103</v>
+        <v>93</v>
       </c>
     </row>
     <row r="15" spans="1:5" ht="34.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="25"/>
       <c r="B15" s="28" t="s">
-        <v>114</v>
+        <v>104</v>
       </c>
       <c r="C15" s="28" t="s">
-        <v>115</v>
+        <v>105</v>
       </c>
       <c r="D15" s="29" t="s">
-        <v>116</v>
+        <v>106</v>
       </c>
     </row>
     <row r="16" spans="1:5" ht="34.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="25"/>
       <c r="B16" s="28" t="s">
-        <v>117</v>
+        <v>107</v>
       </c>
       <c r="C16" s="28" t="s">
-        <v>118</v>
+        <v>108</v>
       </c>
       <c r="D16" s="29" t="s">
-        <v>119</v>
+        <v>109</v>
       </c>
     </row>
     <row r="17" spans="1:4" ht="34.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="25"/>
       <c r="B17" s="28" t="s">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="C17" s="28" t="s">
-        <v>121</v>
+        <v>111</v>
       </c>
       <c r="D17" s="29" t="s">
-        <v>122</v>
+        <v>112</v>
       </c>
     </row>
     <row r="18" spans="1:4" ht="34.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="25"/>
       <c r="B18" s="28" t="s">
-        <v>123</v>
+        <v>113</v>
       </c>
       <c r="C18" s="28" t="s">
-        <v>124</v>
+        <v>114</v>
       </c>
       <c r="D18" s="29" t="s">
-        <v>116</v>
+        <v>106</v>
       </c>
     </row>
     <row r="19" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -6127,7 +6862,7 @@
     <row r="20" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="25"/>
       <c r="B20" s="24" t="s">
-        <v>125</v>
+        <v>115</v>
       </c>
       <c r="C20" s="25"/>
       <c r="D20" s="25"/>
@@ -6135,25 +6870,25 @@
     <row r="21" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="25"/>
       <c r="B21" s="26" t="s">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="C21" s="26" t="s">
-        <v>102</v>
+        <v>92</v>
       </c>
       <c r="D21" s="27" t="s">
-        <v>103</v>
+        <v>93</v>
       </c>
     </row>
     <row r="22" spans="1:4" ht="43.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="25"/>
       <c r="B22" s="28" t="s">
-        <v>126</v>
+        <v>116</v>
       </c>
       <c r="C22" s="28" t="s">
-        <v>127</v>
+        <v>117</v>
       </c>
       <c r="D22" s="29" t="s">
-        <v>128</v>
+        <v>118</v>
       </c>
     </row>
     <row r="23" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -6165,7 +6900,7 @@
     <row r="24" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="25"/>
       <c r="B24" s="24" t="s">
-        <v>129</v>
+        <v>119</v>
       </c>
       <c r="C24" s="25"/>
       <c r="D24" s="25"/>
@@ -6173,37 +6908,37 @@
     <row r="25" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="25"/>
       <c r="B25" s="26" t="s">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="C25" s="26" t="s">
-        <v>102</v>
+        <v>92</v>
       </c>
       <c r="D25" s="27" t="s">
-        <v>103</v>
+        <v>93</v>
       </c>
     </row>
     <row r="26" spans="1:4" ht="45.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="25"/>
       <c r="B26" s="28" t="s">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="C26" s="28" t="s">
-        <v>131</v>
+        <v>121</v>
       </c>
       <c r="D26" s="29" t="s">
-        <v>132</v>
+        <v>122</v>
       </c>
     </row>
     <row r="27" spans="1:4" ht="45.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="25"/>
       <c r="B27" s="28" t="s">
-        <v>133</v>
+        <v>123</v>
       </c>
       <c r="C27" s="28" t="s">
-        <v>134</v>
+        <v>124</v>
       </c>
       <c r="D27" s="29" t="s">
-        <v>135</v>
+        <v>125</v>
       </c>
     </row>
     <row r="28" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -6215,7 +6950,7 @@
     <row r="29" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="25"/>
       <c r="B29" s="24" t="s">
-        <v>136</v>
+        <v>126</v>
       </c>
       <c r="C29" s="25"/>
       <c r="D29" s="25"/>
@@ -6223,35 +6958,35 @@
     <row r="30" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="25"/>
       <c r="B30" s="26" t="s">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="C30" s="26" t="s">
-        <v>102</v>
+        <v>92</v>
       </c>
       <c r="D30" s="27" t="s">
-        <v>103</v>
+        <v>93</v>
       </c>
     </row>
     <row r="31" spans="1:4" ht="47.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A31" s="25"/>
       <c r="B31" s="28" t="s">
-        <v>137</v>
+        <v>127</v>
       </c>
       <c r="C31" s="28" t="s">
-        <v>138</v>
+        <v>128</v>
       </c>
       <c r="D31" s="29"/>
     </row>
     <row r="32" spans="1:4" ht="47.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A32" s="25"/>
       <c r="B32" s="28" t="s">
-        <v>133</v>
+        <v>123</v>
       </c>
       <c r="C32" s="34" t="s">
-        <v>139</v>
+        <v>129</v>
       </c>
       <c r="D32" s="29" t="s">
-        <v>140</v>
+        <v>130</v>
       </c>
     </row>
     <row r="33" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -6263,7 +6998,7 @@
     <row r="34" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A34" s="25"/>
       <c r="B34" s="24" t="s">
-        <v>141</v>
+        <v>131</v>
       </c>
       <c r="C34" s="25"/>
       <c r="D34" s="25"/>
@@ -6271,37 +7006,37 @@
     <row r="35" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A35" s="25"/>
       <c r="B35" s="26" t="s">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="C35" s="26" t="s">
-        <v>102</v>
+        <v>92</v>
       </c>
       <c r="D35" s="27" t="s">
-        <v>103</v>
+        <v>93</v>
       </c>
     </row>
     <row r="36" spans="1:4" ht="37.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A36" s="25"/>
       <c r="B36" s="28" t="s">
-        <v>142</v>
+        <v>132</v>
       </c>
       <c r="C36" s="28" t="s">
-        <v>143</v>
+        <v>133</v>
       </c>
       <c r="D36" s="29" t="s">
-        <v>144</v>
+        <v>134</v>
       </c>
     </row>
     <row r="37" spans="1:4" ht="37.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A37" s="25"/>
       <c r="B37" s="28" t="s">
-        <v>145</v>
+        <v>135</v>
       </c>
       <c r="C37" s="28" t="s">
-        <v>146</v>
+        <v>136</v>
       </c>
       <c r="D37" s="29" t="s">
-        <v>147</v>
+        <v>137</v>
       </c>
     </row>
     <row r="38" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -6313,7 +7048,7 @@
     <row r="39" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A39" s="25"/>
       <c r="B39" s="24" t="s">
-        <v>148</v>
+        <v>138</v>
       </c>
       <c r="C39" s="25"/>
       <c r="D39" s="25"/>
@@ -6321,37 +7056,37 @@
     <row r="40" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A40" s="25"/>
       <c r="B40" s="26" t="s">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="C40" s="26" t="s">
-        <v>102</v>
+        <v>92</v>
       </c>
       <c r="D40" s="27" t="s">
-        <v>103</v>
+        <v>93</v>
       </c>
     </row>
     <row r="41" spans="1:4" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A41" s="25"/>
       <c r="B41" s="28" t="s">
-        <v>149</v>
+        <v>139</v>
       </c>
       <c r="C41" s="28" t="s">
-        <v>150</v>
+        <v>140</v>
       </c>
       <c r="D41" s="29" t="s">
-        <v>144</v>
+        <v>134</v>
       </c>
     </row>
     <row r="42" spans="1:4" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A42" s="25"/>
       <c r="B42" s="28" t="s">
-        <v>151</v>
+        <v>141</v>
       </c>
       <c r="C42" s="28" t="s">
-        <v>152</v>
+        <v>142</v>
       </c>
       <c r="D42" s="29" t="s">
-        <v>147</v>
+        <v>137</v>
       </c>
     </row>
     <row r="43" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -6363,7 +7098,7 @@
     <row r="44" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A44" s="25"/>
       <c r="B44" s="24" t="s">
-        <v>153</v>
+        <v>143</v>
       </c>
       <c r="C44" s="25"/>
       <c r="D44" s="25"/>
@@ -6371,35 +7106,35 @@
     <row r="45" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A45" s="25"/>
       <c r="B45" s="26" t="s">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="C45" s="26" t="s">
-        <v>102</v>
+        <v>92</v>
       </c>
       <c r="D45" s="27" t="s">
-        <v>103</v>
+        <v>93</v>
       </c>
     </row>
     <row r="46" spans="1:4" ht="39" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A46" s="25"/>
       <c r="B46" s="28" t="s">
-        <v>154</v>
+        <v>144</v>
       </c>
       <c r="C46" s="28" t="s">
-        <v>155</v>
+        <v>145</v>
       </c>
       <c r="D46" s="29"/>
     </row>
     <row r="47" spans="1:4" ht="39" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A47" s="25"/>
       <c r="B47" s="28" t="s">
-        <v>156</v>
+        <v>146</v>
       </c>
       <c r="C47" s="28" t="s">
-        <v>157</v>
+        <v>147</v>
       </c>
       <c r="D47" s="29" t="s">
-        <v>147</v>
+        <v>137</v>
       </c>
     </row>
     <row r="48" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
@@ -7378,24 +8113,24 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="71" t="s">
-        <v>158</v>
-      </c>
-      <c r="B1" s="70"/>
-      <c r="C1" s="70"/>
-      <c r="D1" s="70"/>
-      <c r="E1" s="70"/>
-      <c r="F1" s="70"/>
-      <c r="G1" s="70"/>
-      <c r="H1" s="70"/>
-      <c r="I1" s="70"/>
+      <c r="A1" s="83" t="s">
+        <v>148</v>
+      </c>
+      <c r="B1" s="82"/>
+      <c r="C1" s="82"/>
+      <c r="D1" s="82"/>
+      <c r="E1" s="82"/>
+      <c r="F1" s="82"/>
+      <c r="G1" s="82"/>
+      <c r="H1" s="82"/>
+      <c r="I1" s="82"/>
     </row>
     <row r="2" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="35" t="s">
-        <v>159</v>
+        <v>149</v>
       </c>
       <c r="B2" s="36" t="s">
-        <v>160</v>
+        <v>150</v>
       </c>
       <c r="C2" s="13"/>
       <c r="D2" s="37"/>
@@ -7420,17 +8155,17 @@
     </row>
     <row r="4" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="40" t="s">
-        <v>161</v>
-      </c>
-      <c r="B4" s="72" t="s">
-        <v>162</v>
-      </c>
-      <c r="C4" s="73"/>
-      <c r="D4" s="73"/>
-      <c r="E4" s="73"/>
-      <c r="F4" s="73"/>
-      <c r="G4" s="73"/>
-      <c r="H4" s="74"/>
+        <v>151</v>
+      </c>
+      <c r="B4" s="84" t="s">
+        <v>152</v>
+      </c>
+      <c r="C4" s="85"/>
+      <c r="D4" s="85"/>
+      <c r="E4" s="85"/>
+      <c r="F4" s="85"/>
+      <c r="G4" s="85"/>
+      <c r="H4" s="86"/>
       <c r="I4" s="13"/>
       <c r="J4" s="41"/>
       <c r="K4" s="39"/>
@@ -7438,25 +8173,25 @@
     <row r="5" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="13"/>
       <c r="B5" s="42" t="s">
-        <v>163</v>
+        <v>153</v>
       </c>
       <c r="C5" s="42" t="s">
-        <v>164</v>
+        <v>154</v>
       </c>
       <c r="D5" s="42" t="s">
-        <v>165</v>
+        <v>155</v>
       </c>
       <c r="E5" s="42" t="s">
-        <v>166</v>
+        <v>156</v>
       </c>
       <c r="F5" s="42" t="s">
-        <v>167</v>
+        <v>157</v>
       </c>
       <c r="G5" s="42" t="s">
-        <v>168</v>
+        <v>158</v>
       </c>
       <c r="H5" s="42" t="s">
-        <v>169</v>
+        <v>159</v>
       </c>
       <c r="I5" s="13"/>
       <c r="J5" s="39"/>
@@ -7465,22 +8200,22 @@
     <row r="6" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="13"/>
       <c r="B6" s="43" t="s">
-        <v>170</v>
+        <v>160</v>
       </c>
       <c r="C6" s="43" t="s">
-        <v>171</v>
+        <v>161</v>
       </c>
       <c r="D6" s="43" t="s">
-        <v>172</v>
+        <v>162</v>
       </c>
       <c r="E6" s="43" t="s">
-        <v>173</v>
+        <v>163</v>
       </c>
       <c r="F6" s="43" t="s">
-        <v>174</v>
+        <v>164</v>
       </c>
       <c r="G6" s="43" t="s">
-        <v>175</v>
+        <v>165</v>
       </c>
       <c r="H6" s="43"/>
       <c r="I6" s="13"/>
@@ -7490,20 +8225,20 @@
     <row r="7" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="13"/>
       <c r="B7" s="43" t="s">
-        <v>176</v>
+        <v>166</v>
       </c>
       <c r="C7" s="43" t="s">
-        <v>177</v>
+        <v>167</v>
       </c>
       <c r="D7" s="43" t="s">
-        <v>178</v>
+        <v>168</v>
       </c>
       <c r="E7" s="43" t="s">
-        <v>173</v>
+        <v>163</v>
       </c>
       <c r="F7" s="43"/>
       <c r="G7" s="43" t="s">
-        <v>175</v>
+        <v>165</v>
       </c>
       <c r="H7" s="43"/>
       <c r="I7" s="13"/>
@@ -7513,22 +8248,22 @@
     <row r="8" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="13"/>
       <c r="B8" s="43" t="s">
-        <v>179</v>
+        <v>169</v>
       </c>
       <c r="C8" s="43" t="s">
-        <v>180</v>
+        <v>170</v>
       </c>
       <c r="D8" s="43" t="s">
-        <v>178</v>
+        <v>168</v>
       </c>
       <c r="E8" s="43" t="s">
-        <v>173</v>
+        <v>163</v>
       </c>
       <c r="F8" s="43" t="s">
-        <v>181</v>
+        <v>171</v>
       </c>
       <c r="G8" s="43" t="s">
-        <v>175</v>
+        <v>165</v>
       </c>
       <c r="H8" s="43"/>
       <c r="I8" s="13"/>
@@ -7538,20 +8273,20 @@
     <row r="9" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="13"/>
       <c r="B9" s="43" t="s">
-        <v>182</v>
+        <v>172</v>
       </c>
       <c r="C9" s="43" t="s">
-        <v>183</v>
+        <v>173</v>
       </c>
       <c r="D9" s="43" t="s">
-        <v>178</v>
+        <v>168</v>
       </c>
       <c r="E9" s="43" t="s">
-        <v>173</v>
+        <v>163</v>
       </c>
       <c r="F9" s="43"/>
       <c r="G9" s="43" t="s">
-        <v>175</v>
+        <v>165</v>
       </c>
       <c r="H9" s="43"/>
       <c r="I9" s="13"/>
@@ -7561,20 +8296,20 @@
     <row r="10" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="13"/>
       <c r="B10" s="43" t="s">
-        <v>184</v>
+        <v>174</v>
       </c>
       <c r="C10" s="43" t="s">
-        <v>185</v>
+        <v>175</v>
       </c>
       <c r="D10" s="43" t="s">
-        <v>186</v>
+        <v>176</v>
       </c>
       <c r="E10" s="43" t="s">
-        <v>187</v>
+        <v>177</v>
       </c>
       <c r="F10" s="43"/>
       <c r="G10" s="43" t="s">
-        <v>175</v>
+        <v>165</v>
       </c>
       <c r="H10" s="43"/>
       <c r="I10" s="13"/>
@@ -7584,20 +8319,20 @@
     <row r="11" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="13"/>
       <c r="B11" s="43" t="s">
-        <v>188</v>
+        <v>178</v>
       </c>
       <c r="C11" s="43" t="s">
-        <v>189</v>
+        <v>179</v>
       </c>
       <c r="D11" s="43" t="s">
-        <v>178</v>
+        <v>168</v>
       </c>
       <c r="E11" s="43" t="s">
-        <v>173</v>
+        <v>163</v>
       </c>
       <c r="F11" s="43"/>
       <c r="G11" s="43" t="s">
-        <v>190</v>
+        <v>180</v>
       </c>
       <c r="H11" s="43"/>
       <c r="I11" s="13"/>
@@ -7607,20 +8342,20 @@
     <row r="12" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="13"/>
       <c r="B12" s="43" t="s">
-        <v>191</v>
+        <v>181</v>
       </c>
       <c r="C12" s="43" t="s">
-        <v>192</v>
+        <v>182</v>
       </c>
       <c r="D12" s="43" t="s">
-        <v>193</v>
+        <v>183</v>
       </c>
       <c r="E12" s="43" t="s">
-        <v>173</v>
+        <v>163</v>
       </c>
       <c r="F12" s="43"/>
       <c r="G12" s="43" t="s">
-        <v>194</v>
+        <v>184</v>
       </c>
       <c r="H12" s="43"/>
       <c r="I12" s="13"/>
@@ -7630,23 +8365,23 @@
     <row r="13" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="13"/>
       <c r="B13" s="43" t="s">
-        <v>195</v>
+        <v>185</v>
       </c>
       <c r="C13" s="43" t="s">
-        <v>196</v>
+        <v>186</v>
       </c>
       <c r="D13" s="43" t="s">
-        <v>193</v>
+        <v>183</v>
       </c>
       <c r="E13" s="43" t="s">
-        <v>173</v>
+        <v>163</v>
       </c>
       <c r="F13" s="43"/>
       <c r="G13" s="43" t="s">
-        <v>194</v>
+        <v>184</v>
       </c>
       <c r="H13" s="43" t="s">
-        <v>197</v>
+        <v>187</v>
       </c>
       <c r="I13" s="13"/>
       <c r="J13" s="39"/>
@@ -7667,15 +8402,15 @@
     </row>
     <row r="15" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="13"/>
-      <c r="B15" s="72" t="s">
-        <v>198</v>
-      </c>
-      <c r="C15" s="73"/>
-      <c r="D15" s="73"/>
-      <c r="E15" s="73"/>
-      <c r="F15" s="73"/>
-      <c r="G15" s="73"/>
-      <c r="H15" s="74"/>
+      <c r="B15" s="84" t="s">
+        <v>188</v>
+      </c>
+      <c r="C15" s="85"/>
+      <c r="D15" s="85"/>
+      <c r="E15" s="85"/>
+      <c r="F15" s="85"/>
+      <c r="G15" s="85"/>
+      <c r="H15" s="86"/>
       <c r="I15" s="13"/>
       <c r="J15" s="41"/>
       <c r="K15" s="39"/>
@@ -7683,25 +8418,25 @@
     <row r="16" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="13"/>
       <c r="B16" s="42" t="s">
-        <v>163</v>
+        <v>153</v>
       </c>
       <c r="C16" s="42" t="s">
-        <v>164</v>
+        <v>154</v>
       </c>
       <c r="D16" s="42" t="s">
-        <v>165</v>
+        <v>155</v>
       </c>
       <c r="E16" s="42" t="s">
-        <v>166</v>
+        <v>156</v>
       </c>
       <c r="F16" s="42" t="s">
-        <v>167</v>
+        <v>157</v>
       </c>
       <c r="G16" s="42" t="s">
-        <v>168</v>
+        <v>158</v>
       </c>
       <c r="H16" s="42" t="s">
-        <v>169</v>
+        <v>159</v>
       </c>
       <c r="I16" s="13"/>
       <c r="J16" s="39"/>
@@ -7710,25 +8445,25 @@
     <row r="17" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="13"/>
       <c r="B17" s="43" t="s">
-        <v>170</v>
+        <v>160</v>
       </c>
       <c r="C17" s="43" t="s">
-        <v>171</v>
+        <v>161</v>
       </c>
       <c r="D17" s="43" t="s">
-        <v>172</v>
+        <v>162</v>
       </c>
       <c r="E17" s="43" t="s">
-        <v>173</v>
+        <v>163</v>
       </c>
       <c r="F17" s="43" t="s">
-        <v>174</v>
+        <v>164</v>
       </c>
       <c r="G17" s="43" t="s">
-        <v>175</v>
+        <v>165</v>
       </c>
       <c r="H17" s="43" t="s">
-        <v>199</v>
+        <v>189</v>
       </c>
       <c r="I17" s="13"/>
       <c r="J17" s="39"/>
@@ -7737,22 +8472,22 @@
     <row r="18" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="13"/>
       <c r="B18" s="43" t="s">
-        <v>200</v>
+        <v>190</v>
       </c>
       <c r="C18" s="43" t="s">
-        <v>201</v>
+        <v>191</v>
       </c>
       <c r="D18" s="43" t="s">
-        <v>202</v>
+        <v>192</v>
       </c>
       <c r="E18" s="43" t="s">
-        <v>173</v>
+        <v>163</v>
       </c>
       <c r="F18" s="43" t="s">
-        <v>203</v>
+        <v>193</v>
       </c>
       <c r="G18" s="43" t="s">
-        <v>175</v>
+        <v>165</v>
       </c>
       <c r="H18" s="43"/>
       <c r="I18" s="13"/>
@@ -7762,20 +8497,20 @@
     <row r="19" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="13"/>
       <c r="B19" s="43" t="s">
-        <v>204</v>
+        <v>194</v>
       </c>
       <c r="C19" s="43" t="s">
-        <v>205</v>
+        <v>195</v>
       </c>
       <c r="D19" s="43" t="s">
-        <v>186</v>
+        <v>176</v>
       </c>
       <c r="E19" s="43" t="s">
-        <v>173</v>
+        <v>163</v>
       </c>
       <c r="F19" s="43"/>
       <c r="G19" s="43" t="s">
-        <v>175</v>
+        <v>165</v>
       </c>
       <c r="H19" s="43"/>
       <c r="I19" s="13"/>
@@ -7785,20 +8520,20 @@
     <row r="20" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="13"/>
       <c r="B20" s="43" t="s">
-        <v>191</v>
+        <v>181</v>
       </c>
       <c r="C20" s="43" t="s">
-        <v>192</v>
+        <v>182</v>
       </c>
       <c r="D20" s="43" t="s">
-        <v>193</v>
+        <v>183</v>
       </c>
       <c r="E20" s="43" t="s">
-        <v>173</v>
+        <v>163</v>
       </c>
       <c r="F20" s="43"/>
       <c r="G20" s="43" t="s">
-        <v>194</v>
+        <v>184</v>
       </c>
       <c r="H20" s="43"/>
       <c r="I20" s="13"/>
@@ -7808,23 +8543,23 @@
     <row r="21" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="13"/>
       <c r="B21" s="43" t="s">
-        <v>195</v>
+        <v>185</v>
       </c>
       <c r="C21" s="43" t="s">
-        <v>196</v>
+        <v>186</v>
       </c>
       <c r="D21" s="43" t="s">
-        <v>193</v>
+        <v>183</v>
       </c>
       <c r="E21" s="43" t="s">
-        <v>173</v>
+        <v>163</v>
       </c>
       <c r="F21" s="43"/>
       <c r="G21" s="43" t="s">
-        <v>194</v>
+        <v>184</v>
       </c>
       <c r="H21" s="43" t="s">
-        <v>197</v>
+        <v>187</v>
       </c>
       <c r="I21" s="13"/>
       <c r="J21" s="39"/>
@@ -7845,15 +8580,15 @@
     </row>
     <row r="23" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="13"/>
-      <c r="B23" s="72" t="s">
-        <v>206</v>
-      </c>
-      <c r="C23" s="73"/>
-      <c r="D23" s="73"/>
-      <c r="E23" s="73"/>
-      <c r="F23" s="73"/>
-      <c r="G23" s="73"/>
-      <c r="H23" s="74"/>
+      <c r="B23" s="84" t="s">
+        <v>196</v>
+      </c>
+      <c r="C23" s="85"/>
+      <c r="D23" s="85"/>
+      <c r="E23" s="85"/>
+      <c r="F23" s="85"/>
+      <c r="G23" s="85"/>
+      <c r="H23" s="86"/>
       <c r="I23" s="13"/>
       <c r="J23" s="39"/>
       <c r="K23" s="39"/>
@@ -7861,25 +8596,25 @@
     <row r="24" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="13"/>
       <c r="B24" s="42" t="s">
-        <v>163</v>
+        <v>153</v>
       </c>
       <c r="C24" s="42" t="s">
-        <v>164</v>
+        <v>154</v>
       </c>
       <c r="D24" s="42" t="s">
-        <v>165</v>
+        <v>155</v>
       </c>
       <c r="E24" s="42" t="s">
-        <v>166</v>
+        <v>156</v>
       </c>
       <c r="F24" s="42" t="s">
-        <v>167</v>
+        <v>157</v>
       </c>
       <c r="G24" s="42" t="s">
-        <v>168</v>
+        <v>158</v>
       </c>
       <c r="H24" s="42" t="s">
-        <v>169</v>
+        <v>159</v>
       </c>
       <c r="I24" s="13"/>
       <c r="J24" s="41"/>
@@ -7888,22 +8623,22 @@
     <row r="25" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="13"/>
       <c r="B25" s="43" t="s">
-        <v>170</v>
+        <v>160</v>
       </c>
       <c r="C25" s="43" t="s">
-        <v>171</v>
+        <v>161</v>
       </c>
       <c r="D25" s="43" t="s">
-        <v>172</v>
+        <v>162</v>
       </c>
       <c r="E25" s="43" t="s">
-        <v>173</v>
+        <v>163</v>
       </c>
       <c r="F25" s="43" t="s">
-        <v>174</v>
+        <v>164</v>
       </c>
       <c r="G25" s="43" t="s">
-        <v>175</v>
+        <v>165</v>
       </c>
       <c r="H25" s="43"/>
       <c r="I25" s="13"/>
@@ -7913,20 +8648,20 @@
     <row r="26" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="13"/>
       <c r="B26" s="43" t="s">
-        <v>207</v>
+        <v>197</v>
       </c>
       <c r="C26" s="43" t="s">
-        <v>208</v>
+        <v>198</v>
       </c>
       <c r="D26" s="43" t="s">
-        <v>172</v>
+        <v>162</v>
       </c>
       <c r="E26" s="43" t="s">
-        <v>173</v>
+        <v>163</v>
       </c>
       <c r="F26" s="43"/>
       <c r="G26" s="43" t="s">
-        <v>175</v>
+        <v>165</v>
       </c>
       <c r="H26" s="43"/>
       <c r="I26" s="13"/>
@@ -7936,20 +8671,20 @@
     <row r="27" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="13"/>
       <c r="B27" s="43" t="s">
-        <v>209</v>
+        <v>199</v>
       </c>
       <c r="C27" s="43" t="s">
-        <v>210</v>
+        <v>200</v>
       </c>
       <c r="D27" s="43" t="s">
-        <v>172</v>
+        <v>162</v>
       </c>
       <c r="E27" s="43" t="s">
-        <v>173</v>
+        <v>163</v>
       </c>
       <c r="F27" s="43"/>
       <c r="G27" s="43" t="s">
-        <v>175</v>
+        <v>165</v>
       </c>
       <c r="H27" s="43"/>
       <c r="I27" s="13"/>
@@ -7959,20 +8694,20 @@
     <row r="28" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="13"/>
       <c r="B28" s="43" t="s">
-        <v>191</v>
+        <v>181</v>
       </c>
       <c r="C28" s="43" t="s">
-        <v>192</v>
+        <v>182</v>
       </c>
       <c r="D28" s="43" t="s">
-        <v>193</v>
+        <v>183</v>
       </c>
       <c r="E28" s="43" t="s">
-        <v>173</v>
+        <v>163</v>
       </c>
       <c r="F28" s="43"/>
       <c r="G28" s="43" t="s">
-        <v>194</v>
+        <v>184</v>
       </c>
       <c r="H28" s="43"/>
       <c r="I28" s="13"/>
@@ -7982,23 +8717,23 @@
     <row r="29" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="13"/>
       <c r="B29" s="43" t="s">
-        <v>195</v>
+        <v>185</v>
       </c>
       <c r="C29" s="43" t="s">
-        <v>196</v>
+        <v>186</v>
       </c>
       <c r="D29" s="43" t="s">
-        <v>193</v>
+        <v>183</v>
       </c>
       <c r="E29" s="43" t="s">
-        <v>173</v>
+        <v>163</v>
       </c>
       <c r="F29" s="43"/>
       <c r="G29" s="43" t="s">
-        <v>194</v>
+        <v>184</v>
       </c>
       <c r="H29" s="43" t="s">
-        <v>197</v>
+        <v>187</v>
       </c>
       <c r="I29" s="13"/>
       <c r="J29" s="39"/>
@@ -8016,17 +8751,17 @@
       <c r="I30" s="13"/>
     </row>
     <row r="31" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="71" t="s">
-        <v>211</v>
-      </c>
-      <c r="B31" s="70"/>
-      <c r="C31" s="70"/>
-      <c r="D31" s="70"/>
-      <c r="E31" s="70"/>
-      <c r="F31" s="70"/>
-      <c r="G31" s="70"/>
-      <c r="H31" s="70"/>
-      <c r="I31" s="70"/>
+      <c r="A31" s="83" t="s">
+        <v>201</v>
+      </c>
+      <c r="B31" s="82"/>
+      <c r="C31" s="82"/>
+      <c r="D31" s="82"/>
+      <c r="E31" s="82"/>
+      <c r="F31" s="82"/>
+      <c r="G31" s="82"/>
+      <c r="H31" s="82"/>
+      <c r="I31" s="82"/>
     </row>
     <row r="32" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="33" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
@@ -9027,7 +9762,7 @@
   <sheetData>
     <row r="1" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="25" t="s">
-        <v>212</v>
+        <v>202</v>
       </c>
       <c r="B1" s="25"/>
       <c r="C1" s="13"/>
@@ -9039,79 +9774,79 @@
     </row>
     <row r="3" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B3" s="27" t="s">
-        <v>213</v>
+        <v>203</v>
       </c>
       <c r="C3" s="27" t="s">
-        <v>163</v>
+        <v>153</v>
       </c>
       <c r="D3" s="44" t="s">
-        <v>214</v>
+        <v>204</v>
       </c>
     </row>
     <row r="4" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B4" s="29" t="s">
-        <v>215</v>
+        <v>205</v>
       </c>
       <c r="C4" s="29" t="s">
-        <v>216</v>
+        <v>206</v>
       </c>
       <c r="D4" s="45" t="s">
-        <v>217</v>
+        <v>207</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B5" s="29" t="s">
-        <v>218</v>
+        <v>208</v>
       </c>
       <c r="C5" s="29" t="s">
-        <v>219</v>
+        <v>209</v>
       </c>
       <c r="D5" s="45" t="s">
-        <v>220</v>
+        <v>210</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B6" s="29" t="s">
-        <v>218</v>
+        <v>208</v>
       </c>
       <c r="C6" s="29" t="s">
-        <v>221</v>
+        <v>211</v>
       </c>
       <c r="D6" s="45" t="s">
-        <v>222</v>
+        <v>212</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B7" s="29" t="s">
-        <v>223</v>
+        <v>213</v>
       </c>
       <c r="C7" s="29" t="s">
-        <v>224</v>
+        <v>214</v>
       </c>
       <c r="D7" s="45" t="s">
-        <v>225</v>
+        <v>215</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="39" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B8" s="29" t="s">
-        <v>226</v>
+        <v>216</v>
       </c>
       <c r="C8" s="29" t="s">
-        <v>227</v>
+        <v>217</v>
       </c>
       <c r="D8" s="45" t="s">
-        <v>228</v>
+        <v>218</v>
       </c>
     </row>
     <row r="9" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B9" s="29" t="s">
-        <v>229</v>
+        <v>219</v>
       </c>
       <c r="C9" s="29" t="s">
-        <v>230</v>
+        <v>220</v>
       </c>
       <c r="D9" s="45" t="s">
-        <v>231</v>
+        <v>221</v>
       </c>
     </row>
     <row r="10" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
@@ -10130,11 +10865,11 @@
     </row>
     <row r="2" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="25"/>
-      <c r="B2" s="75" t="s">
-        <v>232</v>
-      </c>
-      <c r="C2" s="76"/>
-      <c r="D2" s="77"/>
+      <c r="B2" s="87" t="s">
+        <v>222</v>
+      </c>
+      <c r="C2" s="88"/>
+      <c r="D2" s="89"/>
       <c r="E2" s="46"/>
       <c r="F2" s="47"/>
       <c r="G2" s="47"/>
@@ -10145,11 +10880,11 @@
     </row>
     <row r="3" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="25"/>
-      <c r="B3" s="78" t="s">
-        <v>233</v>
-      </c>
-      <c r="C3" s="73"/>
-      <c r="D3" s="73"/>
+      <c r="B3" s="90" t="s">
+        <v>223</v>
+      </c>
+      <c r="C3" s="85"/>
+      <c r="D3" s="85"/>
       <c r="E3" s="48"/>
       <c r="F3" s="49"/>
       <c r="G3" s="49"/>
@@ -10160,11 +10895,11 @@
     </row>
     <row r="4" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="25"/>
-      <c r="B4" s="78" t="s">
-        <v>234</v>
-      </c>
-      <c r="C4" s="73"/>
-      <c r="D4" s="73"/>
+      <c r="B4" s="90" t="s">
+        <v>224</v>
+      </c>
+      <c r="C4" s="85"/>
+      <c r="D4" s="85"/>
       <c r="E4" s="48"/>
       <c r="F4" s="49"/>
       <c r="G4" s="49"/>
@@ -10175,11 +10910,11 @@
     </row>
     <row r="5" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="25"/>
-      <c r="B5" s="78" t="s">
-        <v>235</v>
-      </c>
-      <c r="C5" s="73"/>
-      <c r="D5" s="73"/>
+      <c r="B5" s="90" t="s">
+        <v>225</v>
+      </c>
+      <c r="C5" s="85"/>
+      <c r="D5" s="85"/>
       <c r="E5" s="48"/>
       <c r="F5" s="49"/>
       <c r="G5" s="49"/>
@@ -10193,14 +10928,14 @@
     </row>
     <row r="7" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B7" s="50" t="s">
-        <v>236</v>
+        <v>226</v>
       </c>
       <c r="C7" s="51"/>
       <c r="D7" s="25"/>
     </row>
     <row r="8" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B8" s="50" t="s">
-        <v>237</v>
+        <v>227</v>
       </c>
       <c r="C8" s="51"/>
       <c r="D8" s="25"/>
@@ -10212,21 +10947,21 @@
     </row>
     <row r="10" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B10" s="53" t="s">
-        <v>238</v>
+        <v>228</v>
       </c>
       <c r="C10" s="54"/>
       <c r="D10" s="25"/>
     </row>
     <row r="11" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B11" s="55" t="s">
-        <v>239</v>
+        <v>229</v>
       </c>
       <c r="C11" s="56"/>
       <c r="D11" s="25"/>
     </row>
     <row r="12" spans="1:11" ht="53.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B12" s="57" t="s">
-        <v>240</v>
+        <v>230</v>
       </c>
       <c r="C12" s="58" t="b">
         <v>0</v>
@@ -10235,7 +10970,7 @@
     </row>
     <row r="13" spans="1:11" ht="53.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B13" s="57" t="s">
-        <v>241</v>
+        <v>231</v>
       </c>
       <c r="C13" s="59" t="b">
         <v>0</v>
@@ -10244,14 +10979,14 @@
     </row>
     <row r="14" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B14" s="55" t="s">
-        <v>242</v>
+        <v>232</v>
       </c>
       <c r="C14" s="60"/>
       <c r="D14" s="61"/>
     </row>
     <row r="15" spans="1:11" ht="35.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B15" s="57" t="s">
-        <v>243</v>
+        <v>233</v>
       </c>
       <c r="C15" s="62" t="b">
         <v>0</v>
@@ -10260,7 +10995,7 @@
     </row>
     <row r="16" spans="1:11" ht="35.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B16" s="57" t="s">
-        <v>244</v>
+        <v>234</v>
       </c>
       <c r="C16" s="58" t="b">
         <v>0</v>
@@ -10269,7 +11004,7 @@
     </row>
     <row r="17" spans="2:4" ht="42" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B17" s="57" t="s">
-        <v>245</v>
+        <v>235</v>
       </c>
       <c r="C17" s="58" t="b">
         <v>0</v>
@@ -10278,7 +11013,7 @@
     </row>
     <row r="18" spans="2:4" ht="33" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B18" s="57" t="s">
-        <v>246</v>
+        <v>236</v>
       </c>
       <c r="C18" s="58" t="b">
         <v>0</v>
@@ -10287,7 +11022,7 @@
     </row>
     <row r="19" spans="2:4" ht="43.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B19" s="57" t="s">
-        <v>247</v>
+        <v>237</v>
       </c>
       <c r="C19" s="58" t="b">
         <v>0</v>
@@ -10296,7 +11031,7 @@
     </row>
     <row r="20" spans="2:4" ht="35.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B20" s="57" t="s">
-        <v>248</v>
+        <v>238</v>
       </c>
       <c r="C20" s="58" t="b">
         <v>0</v>
@@ -10304,7 +11039,7 @@
     </row>
     <row r="21" spans="2:4" ht="45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B21" s="57" t="s">
-        <v>249</v>
+        <v>239</v>
       </c>
       <c r="C21" s="58" t="b">
         <v>0</v>
@@ -10312,7 +11047,7 @@
     </row>
     <row r="22" spans="2:4" ht="35.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B22" s="57" t="s">
-        <v>250</v>
+        <v>240</v>
       </c>
       <c r="C22" s="58" t="b">
         <v>0</v>
@@ -10320,7 +11055,7 @@
     </row>
     <row r="23" spans="2:4" ht="35.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B23" s="57" t="s">
-        <v>251</v>
+        <v>241</v>
       </c>
       <c r="C23" s="58" t="b">
         <v>0</v>
@@ -10328,7 +11063,7 @@
     </row>
     <row r="24" spans="2:4" ht="35.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B24" s="57" t="s">
-        <v>252</v>
+        <v>242</v>
       </c>
       <c r="C24" s="58" t="b">
         <v>0</v>
@@ -10336,7 +11071,7 @@
     </row>
     <row r="25" spans="2:4" ht="35.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B25" s="57" t="s">
-        <v>253</v>
+        <v>243</v>
       </c>
       <c r="C25" s="58" t="b">
         <v>0</v>
@@ -10344,7 +11079,7 @@
     </row>
     <row r="26" spans="2:4" ht="35.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B26" s="57" t="s">
-        <v>254</v>
+        <v>244</v>
       </c>
       <c r="C26" s="58" t="b">
         <v>0</v>
@@ -10356,13 +11091,13 @@
     </row>
     <row r="28" spans="2:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B28" s="55" t="s">
-        <v>255</v>
+        <v>245</v>
       </c>
       <c r="C28" s="56"/>
     </row>
     <row r="29" spans="2:4" ht="25.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B29" s="57" t="s">
-        <v>256</v>
+        <v>246</v>
       </c>
       <c r="C29" s="62" t="b">
         <v>0</v>
@@ -10370,7 +11105,7 @@
     </row>
     <row r="30" spans="2:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B30" s="57" t="s">
-        <v>257</v>
+        <v>247</v>
       </c>
       <c r="C30" s="58" t="b">
         <v>0</v>
@@ -10378,7 +11113,7 @@
     </row>
     <row r="31" spans="2:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B31" s="57" t="s">
-        <v>258</v>
+        <v>248</v>
       </c>
       <c r="C31" s="58" t="b">
         <v>0</v>
@@ -10386,7 +11121,7 @@
     </row>
     <row r="32" spans="2:4" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B32" s="57" t="s">
-        <v>259</v>
+        <v>249</v>
       </c>
       <c r="C32" s="58" t="b">
         <v>0</v>
@@ -10394,7 +11129,7 @@
     </row>
     <row r="33" spans="2:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B33" s="57" t="s">
-        <v>260</v>
+        <v>250</v>
       </c>
       <c r="C33" s="58" t="b">
         <v>0</v>
@@ -10402,7 +11137,7 @@
     </row>
     <row r="34" spans="2:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B34" s="57" t="s">
-        <v>261</v>
+        <v>251</v>
       </c>
       <c r="C34" s="58" t="b">
         <v>0</v>
@@ -10414,13 +11149,13 @@
     </row>
     <row r="36" spans="2:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B36" s="55" t="s">
-        <v>262</v>
+        <v>252</v>
       </c>
       <c r="C36" s="56"/>
     </row>
     <row r="37" spans="2:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B37" s="57" t="s">
-        <v>263</v>
+        <v>253</v>
       </c>
       <c r="C37" s="62" t="b">
         <v>0</v>
@@ -10428,7 +11163,7 @@
     </row>
     <row r="38" spans="2:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B38" s="57" t="s">
-        <v>264</v>
+        <v>254</v>
       </c>
       <c r="C38" s="58" t="b">
         <v>0</v>
@@ -10436,7 +11171,7 @@
     </row>
     <row r="39" spans="2:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B39" s="57" t="s">
-        <v>265</v>
+        <v>255</v>
       </c>
       <c r="C39" s="58" t="b">
         <v>0</v>
@@ -10444,7 +11179,7 @@
     </row>
     <row r="40" spans="2:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B40" s="57" t="s">
-        <v>266</v>
+        <v>256</v>
       </c>
       <c r="C40" s="58" t="b">
         <v>0</v>
@@ -10452,7 +11187,7 @@
     </row>
     <row r="41" spans="2:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B41" s="57" t="s">
-        <v>267</v>
+        <v>257</v>
       </c>
       <c r="C41" s="58" t="b">
         <v>0</v>
@@ -10460,7 +11195,7 @@
     </row>
     <row r="42" spans="2:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B42" s="57" t="s">
-        <v>268</v>
+        <v>258</v>
       </c>
       <c r="C42" s="58" t="b">
         <v>0</v>
@@ -10468,7 +11203,7 @@
     </row>
     <row r="43" spans="2:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B43" s="57" t="s">
-        <v>269</v>
+        <v>259</v>
       </c>
       <c r="C43" s="58" t="b">
         <v>0</v>
@@ -10476,7 +11211,7 @@
     </row>
     <row r="44" spans="2:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B44" s="57" t="s">
-        <v>270</v>
+        <v>260</v>
       </c>
       <c r="C44" s="58" t="b">
         <v>0</v>
@@ -10484,7 +11219,7 @@
     </row>
     <row r="45" spans="2:3" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B45" s="57" t="s">
-        <v>271</v>
+        <v>261</v>
       </c>
       <c r="C45" s="58" t="b">
         <v>0</v>
@@ -10492,7 +11227,7 @@
     </row>
     <row r="46" spans="2:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B46" s="57" t="s">
-        <v>272</v>
+        <v>262</v>
       </c>
       <c r="C46" s="58" t="b">
         <v>0</v>
@@ -10500,7 +11235,7 @@
     </row>
     <row r="47" spans="2:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B47" s="57" t="s">
-        <v>273</v>
+        <v>263</v>
       </c>
       <c r="C47" s="58" t="b">
         <v>0</v>
@@ -10508,7 +11243,7 @@
     </row>
     <row r="48" spans="2:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B48" s="57" t="s">
-        <v>274</v>
+        <v>264</v>
       </c>
       <c r="C48" s="58" t="b">
         <v>0</v>
@@ -10516,7 +11251,7 @@
     </row>
     <row r="49" spans="2:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B49" s="57" t="s">
-        <v>275</v>
+        <v>265</v>
       </c>
       <c r="C49" s="58" t="b">
         <v>0</v>
@@ -10524,7 +11259,7 @@
     </row>
     <row r="50" spans="2:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B50" s="57" t="s">
-        <v>276</v>
+        <v>266</v>
       </c>
       <c r="C50" s="58" t="b">
         <v>0</v>
@@ -10532,7 +11267,7 @@
     </row>
     <row r="51" spans="2:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B51" s="57" t="s">
-        <v>277</v>
+        <v>267</v>
       </c>
       <c r="C51" s="58" t="b">
         <v>0</v>
@@ -10540,7 +11275,7 @@
     </row>
     <row r="52" spans="2:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B52" s="57" t="s">
-        <v>278</v>
+        <v>268</v>
       </c>
       <c r="C52" s="58" t="b">
         <v>0</v>
@@ -10548,7 +11283,7 @@
     </row>
     <row r="53" spans="2:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B53" s="57" t="s">
-        <v>279</v>
+        <v>269</v>
       </c>
       <c r="C53" s="58" t="b">
         <v>0</v>
@@ -10556,7 +11291,7 @@
     </row>
     <row r="54" spans="2:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B54" s="57" t="s">
-        <v>280</v>
+        <v>270</v>
       </c>
       <c r="C54" s="58" t="b">
         <v>0</v>
@@ -10564,7 +11299,7 @@
     </row>
     <row r="55" spans="2:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B55" s="57" t="s">
-        <v>281</v>
+        <v>271</v>
       </c>
       <c r="C55" s="58" t="b">
         <v>0</v>
@@ -10576,13 +11311,13 @@
     </row>
     <row r="57" spans="2:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B57" s="55" t="s">
-        <v>282</v>
+        <v>272</v>
       </c>
       <c r="C57" s="56"/>
     </row>
     <row r="58" spans="2:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B58" s="57" t="s">
-        <v>264</v>
+        <v>254</v>
       </c>
       <c r="C58" s="62" t="b">
         <v>0</v>
@@ -10590,7 +11325,7 @@
     </row>
     <row r="59" spans="2:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B59" s="57" t="s">
-        <v>283</v>
+        <v>273</v>
       </c>
       <c r="C59" s="58" t="b">
         <v>0</v>
@@ -10598,7 +11333,7 @@
     </row>
     <row r="60" spans="2:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B60" s="57" t="s">
-        <v>284</v>
+        <v>274</v>
       </c>
       <c r="C60" s="58" t="b">
         <v>0</v>
@@ -10606,7 +11341,7 @@
     </row>
     <row r="61" spans="2:3" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B61" s="57" t="s">
-        <v>285</v>
+        <v>275</v>
       </c>
       <c r="C61" s="58" t="b">
         <v>0</v>
@@ -10614,7 +11349,7 @@
     </row>
     <row r="62" spans="2:3" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B62" s="57" t="s">
-        <v>286</v>
+        <v>276</v>
       </c>
       <c r="C62" s="58" t="b">
         <v>0</v>
@@ -10622,7 +11357,7 @@
     </row>
     <row r="63" spans="2:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B63" s="57" t="s">
-        <v>287</v>
+        <v>277</v>
       </c>
       <c r="C63" s="58" t="b">
         <v>0</v>
@@ -10630,7 +11365,7 @@
     </row>
     <row r="64" spans="2:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B64" s="57" t="s">
-        <v>288</v>
+        <v>278</v>
       </c>
       <c r="C64" s="58" t="b">
         <v>0</v>
@@ -10638,7 +11373,7 @@
     </row>
     <row r="65" spans="2:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B65" s="57" t="s">
-        <v>289</v>
+        <v>279</v>
       </c>
       <c r="C65" s="58" t="b">
         <v>0</v>
@@ -10646,7 +11381,7 @@
     </row>
     <row r="66" spans="2:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B66" s="57" t="s">
-        <v>290</v>
+        <v>280</v>
       </c>
       <c r="C66" s="58" t="b">
         <v>0</v>
@@ -10654,7 +11389,7 @@
     </row>
     <row r="67" spans="2:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B67" s="57" t="s">
-        <v>291</v>
+        <v>281</v>
       </c>
       <c r="C67" s="58" t="b">
         <v>0</v>
@@ -10666,13 +11401,13 @@
     </row>
     <row r="69" spans="2:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B69" s="55" t="s">
-        <v>229</v>
+        <v>219</v>
       </c>
       <c r="C69" s="56"/>
     </row>
     <row r="70" spans="2:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B70" s="57" t="s">
-        <v>292</v>
+        <v>282</v>
       </c>
       <c r="C70" s="62" t="b">
         <v>0</v>
@@ -10684,13 +11419,13 @@
     </row>
     <row r="72" spans="2:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B72" s="55" t="s">
-        <v>293</v>
+        <v>283</v>
       </c>
       <c r="C72" s="56"/>
     </row>
     <row r="73" spans="2:3" ht="26.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B73" s="57" t="s">
-        <v>294</v>
+        <v>284</v>
       </c>
       <c r="C73" s="62" t="b">
         <v>0</v>
@@ -10698,7 +11433,7 @@
     </row>
     <row r="74" spans="2:3" ht="26.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B74" s="57" t="s">
-        <v>295</v>
+        <v>285</v>
       </c>
       <c r="C74" s="58" t="b">
         <v>0</v>
@@ -10706,7 +11441,7 @@
     </row>
     <row r="75" spans="2:3" ht="26.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B75" s="57" t="s">
-        <v>296</v>
+        <v>286</v>
       </c>
       <c r="C75" s="58" t="b">
         <v>0</v>
@@ -10714,7 +11449,7 @@
     </row>
     <row r="76" spans="2:3" ht="26.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B76" s="57" t="s">
-        <v>297</v>
+        <v>287</v>
       </c>
       <c r="C76" s="58" t="b">
         <v>0</v>
@@ -10722,7 +11457,7 @@
     </row>
     <row r="77" spans="2:3" ht="26.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B77" s="57" t="s">
-        <v>298</v>
+        <v>288</v>
       </c>
       <c r="C77" s="58" t="b">
         <v>0</v>
@@ -10730,7 +11465,7 @@
     </row>
     <row r="78" spans="2:3" ht="33.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B78" s="57" t="s">
-        <v>299</v>
+        <v>289</v>
       </c>
       <c r="C78" s="58" t="b">
         <v>0</v>
@@ -10738,7 +11473,7 @@
     </row>
     <row r="79" spans="2:3" ht="26.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B79" s="57" t="s">
-        <v>300</v>
+        <v>290</v>
       </c>
       <c r="C79" s="58" t="b">
         <v>0</v>
@@ -10746,7 +11481,7 @@
     </row>
     <row r="80" spans="2:3" ht="26.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B80" s="57" t="s">
-        <v>301</v>
+        <v>291</v>
       </c>
       <c r="C80" s="58" t="b">
         <v>0</v>
@@ -10754,7 +11489,7 @@
     </row>
     <row r="81" spans="2:3" ht="26.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B81" s="57" t="s">
-        <v>302</v>
+        <v>292</v>
       </c>
       <c r="C81" s="58" t="b">
         <v>0</v>
@@ -10762,7 +11497,7 @@
     </row>
     <row r="82" spans="2:3" ht="26.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B82" s="57" t="s">
-        <v>303</v>
+        <v>293</v>
       </c>
       <c r="C82" s="58" t="b">
         <v>0</v>
@@ -10770,7 +11505,7 @@
     </row>
     <row r="83" spans="2:3" ht="26.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B83" s="57" t="s">
-        <v>304</v>
+        <v>294</v>
       </c>
       <c r="C83" s="58" t="b">
         <v>0</v>
@@ -10778,7 +11513,7 @@
     </row>
     <row r="84" spans="2:3" ht="26.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B84" s="57" t="s">
-        <v>305</v>
+        <v>295</v>
       </c>
       <c r="C84" s="58" t="b">
         <v>0</v>
@@ -10786,7 +11521,7 @@
     </row>
     <row r="85" spans="2:3" ht="26.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B85" s="57" t="s">
-        <v>306</v>
+        <v>296</v>
       </c>
       <c r="C85" s="58" t="b">
         <v>0</v>
@@ -10794,7 +11529,7 @@
     </row>
     <row r="86" spans="2:3" ht="26.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B86" s="57" t="s">
-        <v>307</v>
+        <v>297</v>
       </c>
       <c r="C86" s="58" t="b">
         <v>0</v>
@@ -11754,7 +12489,7 @@
     <row r="2" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="25"/>
       <c r="B2" s="13" t="s">
-        <v>308</v>
+        <v>298</v>
       </c>
       <c r="C2" s="13"/>
       <c r="D2" s="13"/>
@@ -11777,34 +12512,34 @@
       <c r="L3" s="13"/>
     </row>
     <row r="4" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B4" s="79" t="s">
-        <v>309</v>
-      </c>
-      <c r="C4" s="70"/>
+      <c r="B4" s="91" t="s">
+        <v>299</v>
+      </c>
+      <c r="C4" s="82"/>
       <c r="D4" s="13"/>
-      <c r="E4" s="79" t="s">
-        <v>104</v>
-      </c>
-      <c r="F4" s="70"/>
-      <c r="H4" s="80"/>
-      <c r="I4" s="70"/>
+      <c r="E4" s="91" t="s">
+        <v>94</v>
+      </c>
+      <c r="F4" s="82"/>
+      <c r="H4" s="92"/>
+      <c r="I4" s="82"/>
       <c r="J4" s="37"/>
-      <c r="K4" s="80"/>
-      <c r="L4" s="70"/>
+      <c r="K4" s="92"/>
+      <c r="L4" s="82"/>
     </row>
     <row r="5" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B5" s="63" t="s">
-        <v>310</v>
+        <v>300</v>
       </c>
       <c r="C5" s="63" t="s">
-        <v>311</v>
+        <v>301</v>
       </c>
       <c r="D5" s="13"/>
       <c r="E5" s="63" t="s">
-        <v>312</v>
+        <v>302</v>
       </c>
       <c r="F5" s="64" t="s">
-        <v>311</v>
+        <v>301</v>
       </c>
       <c r="H5" s="65"/>
       <c r="I5" s="66"/>
@@ -11814,17 +12549,17 @@
     </row>
     <row r="6" spans="1:12" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B6" s="29" t="s">
-        <v>313</v>
-      </c>
-      <c r="C6" s="29" t="s">
-        <v>314</v>
+        <v>303</v>
+      </c>
+      <c r="C6" s="77" t="s">
+        <v>333</v>
       </c>
       <c r="D6" s="13"/>
       <c r="E6" s="29" t="s">
-        <v>315</v>
+        <v>305</v>
       </c>
       <c r="F6" s="29" t="s">
-        <v>316</v>
+        <v>306</v>
       </c>
       <c r="H6" s="67"/>
       <c r="I6" s="67"/>
@@ -11832,19 +12567,19 @@
       <c r="K6" s="67"/>
       <c r="L6" s="67"/>
     </row>
-    <row r="7" spans="1:12" ht="50.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:12" ht="76.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B7" s="29" t="s">
-        <v>315</v>
-      </c>
-      <c r="C7" s="29" t="s">
-        <v>317</v>
+        <v>305</v>
+      </c>
+      <c r="C7" s="77" t="s">
+        <v>332</v>
       </c>
       <c r="D7" s="13"/>
       <c r="E7" s="29" t="s">
-        <v>318</v>
+        <v>307</v>
       </c>
       <c r="F7" s="29" t="s">
-        <v>319</v>
+        <v>308</v>
       </c>
       <c r="H7" s="67"/>
       <c r="I7" s="67"/>
@@ -11852,16 +12587,16 @@
       <c r="K7" s="67"/>
       <c r="L7" s="67"/>
     </row>
-    <row r="8" spans="1:12" ht="40.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:12" ht="69" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B8" s="29" t="s">
-        <v>318</v>
-      </c>
-      <c r="C8" s="29" t="s">
-        <v>320</v>
+        <v>307</v>
+      </c>
+      <c r="C8" s="77" t="s">
+        <v>334</v>
       </c>
       <c r="D8" s="13"/>
       <c r="E8" s="68" t="s">
-        <v>321</v>
+        <v>310</v>
       </c>
       <c r="F8" s="25"/>
       <c r="H8" s="67"/>
@@ -11870,12 +12605,12 @@
       <c r="K8" s="67"/>
       <c r="L8" s="67"/>
     </row>
-    <row r="9" spans="1:12" ht="54" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B9" s="29" t="s">
-        <v>322</v>
-      </c>
-      <c r="C9" s="29" t="s">
-        <v>323</v>
+    <row r="9" spans="1:12" ht="80.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B9" s="78" t="s">
+        <v>336</v>
+      </c>
+      <c r="C9" s="77" t="s">
+        <v>335</v>
       </c>
       <c r="D9" s="13"/>
       <c r="E9" s="25"/>
@@ -11899,92 +12634,92 @@
       <c r="L10" s="67"/>
     </row>
     <row r="11" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B11" s="79" t="s">
-        <v>324</v>
-      </c>
-      <c r="C11" s="70"/>
+      <c r="B11" s="91" t="s">
+        <v>312</v>
+      </c>
+      <c r="C11" s="82"/>
       <c r="D11" s="13"/>
-      <c r="E11" s="79" t="s">
-        <v>126</v>
-      </c>
-      <c r="F11" s="70"/>
+      <c r="E11" s="91" t="s">
+        <v>116</v>
+      </c>
+      <c r="F11" s="82"/>
     </row>
     <row r="12" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B12" s="63" t="s">
-        <v>312</v>
+        <v>302</v>
       </c>
       <c r="C12" s="64" t="s">
-        <v>311</v>
+        <v>301</v>
       </c>
       <c r="E12" s="63" t="s">
-        <v>312</v>
+        <v>302</v>
       </c>
       <c r="F12" s="64" t="s">
-        <v>311</v>
+        <v>301</v>
       </c>
     </row>
     <row r="13" spans="1:12" ht="29.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B13" s="29" t="s">
-        <v>325</v>
+        <v>313</v>
       </c>
       <c r="C13" s="29" t="s">
-        <v>326</v>
+        <v>314</v>
       </c>
       <c r="E13" s="29" t="s">
-        <v>313</v>
+        <v>303</v>
       </c>
       <c r="F13" s="29" t="s">
-        <v>314</v>
+        <v>304</v>
       </c>
     </row>
     <row r="14" spans="1:12" ht="56.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B14" s="25"/>
       <c r="C14" s="25"/>
       <c r="E14" s="29" t="s">
+        <v>305</v>
+      </c>
+      <c r="F14" s="29" t="s">
         <v>315</v>
-      </c>
-      <c r="F14" s="29" t="s">
-        <v>327</v>
       </c>
     </row>
     <row r="15" spans="1:12" ht="44.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B15" s="25"/>
       <c r="C15" s="25"/>
       <c r="E15" s="29" t="s">
-        <v>328</v>
+        <v>316</v>
       </c>
       <c r="F15" s="29" t="s">
-        <v>320</v>
+        <v>309</v>
       </c>
     </row>
     <row r="16" spans="1:12" ht="58.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B16" s="25"/>
       <c r="C16" s="25"/>
       <c r="E16" s="29" t="s">
-        <v>329</v>
+        <v>317</v>
       </c>
       <c r="F16" s="29" t="s">
-        <v>323</v>
+        <v>311</v>
       </c>
     </row>
     <row r="17" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B17" s="25"/>
       <c r="C17" s="25"/>
       <c r="E17" s="29" t="s">
-        <v>330</v>
+        <v>318</v>
       </c>
       <c r="F17" s="29" t="s">
-        <v>331</v>
+        <v>319</v>
       </c>
     </row>
     <row r="18" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B18" s="25"/>
       <c r="C18" s="25"/>
       <c r="E18" s="29" t="s">
-        <v>332</v>
+        <v>320</v>
       </c>
       <c r="F18" s="29" t="s">
-        <v>333</v>
+        <v>321</v>
       </c>
     </row>
     <row r="19" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>

--- a/簡易基本設計書【Laravel9】.xlsx
+++ b/簡易基本設計書【Laravel9】.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\daiki\Desktop\Atlas\AtlasSNS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{136070F9-DFF9-495E-BAA1-FA7BCD6F74D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F3C1729D-B39B-45AB-AF59-6EF8544DEC91}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -146,97 +146,7 @@
     <t>【ヘッダー】Atlasロゴにトップページへ遷移するリンクを設置する</t>
   </si>
   <si>
-    <t>対象画面： 共通ヘッダー
-作業内容：
-■ヘッダー内にあるAtlasのロゴにトップページへ遷移するリンクを設置する。</t>
-  </si>
-  <si>
     <t>【ヘッダー】アコーディオンメニューを設置する</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <u/>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-      </rPr>
-      <t>対象画面： 共通ヘッダー
-作業内容：
-■ヘッダー内にある</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <u/>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-      </rPr>
-      <t>「HOME」「プロフィール編集」「ログアウト」</t>
-    </r>
-    <r>
-      <rPr>
-        <u/>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-      </rPr>
-      <t>のページ遷移リンクにアコーディオンメニューを実装する。
-■アコーディオンメニューには矢印をつけ、クリックすると上下が反転するようにする。
-■レイアウトは</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <u/>
-        <sz val="10"/>
-        <color rgb="FF1155CC"/>
-        <rFont val="Arial"/>
-      </rPr>
-      <t>ページ遷移のプロトタイプ</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-      </rPr>
-      <t>を参照。</t>
-    </r>
-  </si>
-  <si>
-    <t>【ヘッダー】アコーディオンメニュー内にトップ/プロフィール編集ページへ遷移するリンクを設置する</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-      </rPr>
-      <t>対象画面： 共通ヘッダー
-作業内容：
-■</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-      </rPr>
-      <t>「HOME」「プロフィール編集」</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-      </rPr>
-      <t>のボタンに下記ページへ遷移するリンクを設置する。
-・HOME：トップページ
-・プロフィール編集：プロフィール編集ページ</t>
-    </r>
-  </si>
-  <si>
-    <t>【ヘッダー】アコーディオンメニュー内にログアウト機能を実装する</t>
   </si>
   <si>
     <r>
@@ -1661,7 +1571,7 @@
       </rPr>
       <t>環境構築手順書を参照。</t>
     </r>
-    <phoneticPr fontId="24"/>
+    <phoneticPr fontId="21"/>
   </si>
   <si>
     <r>
@@ -1823,11 +1733,11 @@
       </rPr>
       <t>を参照。</t>
     </r>
-    <phoneticPr fontId="24"/>
+    <phoneticPr fontId="21"/>
   </si>
   <si>
     <t>マイグレーションでテーブルを作成する</t>
-    <phoneticPr fontId="24"/>
+    <phoneticPr fontId="21"/>
   </si>
   <si>
     <r>
@@ -1860,11 +1770,11 @@
       </rPr>
       <t>課題フォルダ内に用意されたマイグレーションファイルを使いテーブルを作成する。</t>
     </r>
-    <phoneticPr fontId="24"/>
+    <phoneticPr fontId="21"/>
   </si>
   <si>
     <t>シードで初期ユーザーのデータを作成する</t>
-    <phoneticPr fontId="24"/>
+    <phoneticPr fontId="21"/>
   </si>
   <si>
     <r>
@@ -1976,7 +1886,7 @@
       </rPr>
       <t>「パスワード」は暗号化処理を行って登録する。</t>
     </r>
-    <phoneticPr fontId="24"/>
+    <phoneticPr fontId="21"/>
   </si>
   <si>
     <r>
@@ -2051,7 +1961,7 @@
       <t>ログインページ：
 ・ルーティングを確認して正しく処理されるように記述する。</t>
     </r>
-    <phoneticPr fontId="24"/>
+    <phoneticPr fontId="21"/>
   </si>
   <si>
     <r>
@@ -2073,7 +1983,7 @@
       </rPr>
       <t>AtlasSNS00</t>
     </r>
-    <phoneticPr fontId="24"/>
+    <phoneticPr fontId="21"/>
   </si>
   <si>
     <r>
@@ -2105,11 +2015,11 @@
       </rPr>
       <t>ログイン処理を実装する</t>
     </r>
-    <phoneticPr fontId="24"/>
+    <phoneticPr fontId="21"/>
   </si>
   <si>
     <t>ユーザーの新規登録処理にバリデーション処理を実装する</t>
-    <phoneticPr fontId="24"/>
+    <phoneticPr fontId="21"/>
   </si>
   <si>
     <r>
@@ -2163,7 +2073,7 @@
 ・登録済みメールアドレス使用不可
 ・メールアドレスの形式</t>
     </r>
-    <phoneticPr fontId="24"/>
+    <phoneticPr fontId="21"/>
   </si>
   <si>
     <r>
@@ -2215,7 +2125,7 @@
       </rPr>
       <t>文字以内</t>
     </r>
-    <phoneticPr fontId="24"/>
+    <phoneticPr fontId="21"/>
   </si>
   <si>
     <r>
@@ -2268,7 +2178,7 @@
       </rPr>
       <t>文字以内</t>
     </r>
-    <phoneticPr fontId="24"/>
+    <phoneticPr fontId="21"/>
   </si>
   <si>
     <r>
@@ -2341,11 +2251,11 @@
       </rPr>
       <t>入力欄と一致しているか</t>
     </r>
-    <phoneticPr fontId="24"/>
+    <phoneticPr fontId="21"/>
   </si>
   <si>
     <t>PasswordConfirm</t>
-    <phoneticPr fontId="24"/>
+    <phoneticPr fontId="21"/>
   </si>
   <si>
     <r>
@@ -2438,14 +2348,384 @@
       </rPr>
       <t>今回はミドルウェアを用いて実装する。</t>
     </r>
-    <phoneticPr fontId="24"/>
+    <phoneticPr fontId="21"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>対象画面：</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t xml:space="preserve">共通ヘッダー
+作業内容：
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Symbol"/>
+        <family val="2"/>
+      </rPr>
+      <t>■</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>ヘッダー内にある</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Atlas</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>のロゴにトップページへ遷移するリンクを設置する。</t>
+    </r>
+    <phoneticPr fontId="21"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="10"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>対象画面：</t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="10"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t xml:space="preserve">共通ヘッダー
+作業内容：
+</t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="10"/>
+        <rFont val="Segoe UI Symbol"/>
+        <family val="2"/>
+      </rPr>
+      <t>■</t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="10"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>ヘッダー内にある</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <u/>
+        <sz val="10"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>「</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <u/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>HOME</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <u/>
+        <sz val="10"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>」「プロフィール編集」「ログアウト」</t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="10"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t xml:space="preserve">のページ遷移リンクにアコーディオンメニューを実装する。
+</t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="10"/>
+        <rFont val="Segoe UI Symbol"/>
+        <family val="2"/>
+      </rPr>
+      <t>■</t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="10"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t xml:space="preserve">アコーディオンメニューには矢印をつけ、クリックすると上下が反転するようにする。
+</t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="10"/>
+        <rFont val="Segoe UI Symbol"/>
+        <family val="2"/>
+      </rPr>
+      <t>■</t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="10"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>レイアウトは</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <u/>
+        <sz val="10"/>
+        <color rgb="FF1155CC"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>ページ遷移のプロトタイプ</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>を参照。</t>
+    </r>
+    <phoneticPr fontId="21"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>対象画面：</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t xml:space="preserve">共通ヘッダー
+作業内容：
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Symbol"/>
+        <family val="2"/>
+      </rPr>
+      <t>■</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>「</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>HOME</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>」「プロフィール編集」</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>のボタンに下記ページへ遷移するリンクを設置する。
+・</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>HOME</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>：トップページ
+・プロフィール編集：プロフィール編集ページ</t>
+    </r>
+    <phoneticPr fontId="21"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>【ヘッダー】アコーディオンメニュー内にトップ</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>プロフィール編集ページへ遷移するリンクを設置する</t>
+    </r>
+    <phoneticPr fontId="21"/>
+  </si>
+  <si>
+    <t>【ヘッダー】アコーディオンメニュー内にログアウト機能を実装する</t>
+    <phoneticPr fontId="21"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="34" x14ac:knownFonts="1">
+  <fonts count="40" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -2483,11 +2763,6 @@
     </font>
     <font>
       <u/>
-      <sz val="10"/>
-      <color rgb="FF0000FF"/>
-      <name val="Arial"/>
-    </font>
-    <font>
       <sz val="10"/>
       <color rgb="FF0000FF"/>
       <name val="Arial"/>
@@ -2570,17 +2845,6 @@
       <name val="Arial"/>
     </font>
     <font>
-      <u/>
-      <sz val="10"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <b/>
-      <u/>
-      <sz val="10"/>
-      <name val="Arial"/>
-    </font>
-    <font>
       <sz val="6"/>
       <name val="Arial"/>
       <family val="3"/>
@@ -2651,6 +2915,68 @@
       <name val="Arial"/>
       <family val="3"/>
       <charset val="128"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="10"/>
+      <name val="ＭＳ ゴシック"/>
+      <family val="3"/>
+      <charset val="128"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <u/>
+      <sz val="10"/>
+      <name val="ＭＳ ゴシック"/>
+      <family val="3"/>
+      <charset val="128"/>
+    </font>
+    <font>
+      <b/>
+      <u/>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="ＭＳ ゴシック"/>
+      <family val="3"/>
+      <charset val="128"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="10"/>
+      <name val="Segoe UI Symbol"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF0000FF"/>
+      <name val="Arial"/>
+      <family val="3"/>
+      <charset val="128"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="ＭＳ ゴシック"/>
+      <family val="3"/>
+      <charset val="128"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="14">
@@ -2918,7 +3244,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="93">
+  <cellXfs count="94">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -2957,21 +3283,18 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
@@ -3003,13 +3326,13 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="14" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="14" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -3017,32 +3340,32 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="7" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -3064,14 +3387,14 @@
     <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="19" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="18" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="13" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -3081,19 +3404,19 @@
     <xf numFmtId="0" fontId="4" fillId="13" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="33" fillId="13" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="30" fillId="13" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="13" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="25" fillId="13" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="22" fillId="13" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="25" fillId="13" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="28" fillId="13" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="13" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -3102,20 +3425,24 @@
     <xf numFmtId="0" fontId="6" fillId="13" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="37" fillId="13" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="10" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="16" fillId="11" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="13" fillId="10" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="11" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="標準" xfId="0" builtinId="0"/>
@@ -4455,7 +4782,7 @@
     <row r="999" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="1000" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
   </sheetData>
-  <phoneticPr fontId="24"/>
+  <phoneticPr fontId="21"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
 </worksheet>
@@ -4540,59 +4867,59 @@
       <c r="Z3" s="1"/>
     </row>
     <row r="4" spans="1:26" ht="66" x14ac:dyDescent="0.25">
-      <c r="B4" s="69">
+      <c r="B4" s="68">
         <v>1</v>
       </c>
-      <c r="C4" s="70" t="s">
+      <c r="C4" s="69" t="s">
         <v>5</v>
       </c>
-      <c r="D4" s="72" t="s">
-        <v>323</v>
+      <c r="D4" s="71" t="s">
+        <v>318</v>
       </c>
       <c r="F4" s="10"/>
     </row>
     <row r="5" spans="1:26" ht="38.25" x14ac:dyDescent="0.2">
-      <c r="B5" s="69">
+      <c r="B5" s="68">
         <v>2</v>
       </c>
-      <c r="C5" s="70" t="s">
+      <c r="C5" s="69" t="s">
         <v>7</v>
       </c>
-      <c r="D5" s="71" t="s">
+      <c r="D5" s="70" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="6" spans="1:26" ht="64.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B6" s="69" t="s">
+      <c r="B6" s="68" t="s">
         <v>9</v>
       </c>
-      <c r="C6" s="70" t="s">
+      <c r="C6" s="69" t="s">
         <v>10</v>
       </c>
-      <c r="D6" s="73" t="s">
+      <c r="D6" s="72" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="7" spans="1:26" ht="54.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B7" s="68" t="s">
+        <v>11</v>
+      </c>
+      <c r="C7" s="73" t="s">
+        <v>319</v>
+      </c>
+      <c r="D7" s="72" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="8" spans="1:26" ht="81" x14ac:dyDescent="0.25">
+      <c r="B8" s="68" t="s">
+        <v>12</v>
+      </c>
+      <c r="C8" s="73" t="s">
+        <v>321</v>
+      </c>
+      <c r="D8" s="72" t="s">
         <v>322</v>
-      </c>
-    </row>
-    <row r="7" spans="1:26" ht="54.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B7" s="69" t="s">
-        <v>11</v>
-      </c>
-      <c r="C7" s="74" t="s">
-        <v>324</v>
-      </c>
-      <c r="D7" s="73" t="s">
-        <v>325</v>
-      </c>
-    </row>
-    <row r="8" spans="1:26" ht="81" x14ac:dyDescent="0.25">
-      <c r="B8" s="69" t="s">
-        <v>12</v>
-      </c>
-      <c r="C8" s="74" t="s">
-        <v>326</v>
-      </c>
-      <c r="D8" s="73" t="s">
-        <v>327</v>
       </c>
     </row>
     <row r="9" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
@@ -4665,47 +4992,47 @@
       <c r="Z11" s="1"/>
     </row>
     <row r="12" spans="1:26" ht="78" x14ac:dyDescent="0.2">
-      <c r="B12" s="69" t="s">
+      <c r="B12" s="68" t="s">
         <v>4</v>
       </c>
-      <c r="C12" s="76" t="s">
-        <v>330</v>
-      </c>
-      <c r="D12" s="73" t="s">
-        <v>328</v>
+      <c r="C12" s="75" t="s">
+        <v>325</v>
+      </c>
+      <c r="D12" s="72" t="s">
+        <v>323</v>
       </c>
     </row>
     <row r="13" spans="1:26" ht="51" x14ac:dyDescent="0.2">
-      <c r="B13" s="69" t="s">
+      <c r="B13" s="68" t="s">
         <v>6</v>
       </c>
-      <c r="C13" s="74" t="s">
-        <v>331</v>
-      </c>
-      <c r="D13" s="80" t="s">
+      <c r="C13" s="73" t="s">
+        <v>326</v>
+      </c>
+      <c r="D13" s="79" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="14" spans="1:26" ht="38.25" x14ac:dyDescent="0.2">
-      <c r="B14" s="69" t="s">
+      <c r="B14" s="68" t="s">
         <v>9</v>
       </c>
-      <c r="C14" s="70" t="s">
+      <c r="C14" s="69" t="s">
         <v>15</v>
       </c>
-      <c r="D14" s="79" t="s">
+      <c r="D14" s="78" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="15" spans="1:26" ht="119.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B15" s="69" t="s">
+      <c r="B15" s="68" t="s">
         <v>11</v>
       </c>
-      <c r="C15" s="70" t="s">
+      <c r="C15" s="69" t="s">
         <v>17</v>
       </c>
-      <c r="D15" s="73" t="s">
-        <v>337</v>
+      <c r="D15" s="72" t="s">
+        <v>332</v>
       </c>
     </row>
     <row r="16" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
@@ -4777,48 +5104,48 @@
       <c r="Y18" s="1"/>
       <c r="Z18" s="1"/>
     </row>
-    <row r="19" spans="1:26" ht="38.25" x14ac:dyDescent="0.2">
-      <c r="B19" s="7" t="s">
+    <row r="19" spans="1:26" ht="39" x14ac:dyDescent="0.25">
+      <c r="B19" s="68" t="s">
         <v>4</v>
       </c>
-      <c r="C19" s="8" t="s">
+      <c r="C19" s="69" t="s">
         <v>19</v>
       </c>
-      <c r="D19" s="11" t="s">
+      <c r="D19" s="72" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="20" spans="1:26" ht="79.5" x14ac:dyDescent="0.25">
+      <c r="B20" s="68" t="s">
+        <v>6</v>
+      </c>
+      <c r="C20" s="69" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="20" spans="1:26" ht="76.5" x14ac:dyDescent="0.2">
-      <c r="B20" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="C20" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="D20" s="16" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="21" spans="1:26" ht="63.75" x14ac:dyDescent="0.2">
-      <c r="B21" s="7" t="s">
+      <c r="D20" s="80" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="21" spans="1:26" ht="64.5" x14ac:dyDescent="0.2">
+      <c r="B21" s="68" t="s">
         <v>9</v>
       </c>
-      <c r="C21" s="8" t="s">
-        <v>23</v>
-      </c>
-      <c r="D21" s="11" t="s">
-        <v>24</v>
+      <c r="C21" s="75" t="s">
+        <v>336</v>
+      </c>
+      <c r="D21" s="72" t="s">
+        <v>335</v>
       </c>
     </row>
     <row r="22" spans="1:26" ht="38.25" x14ac:dyDescent="0.2">
       <c r="B22" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="C22" s="8" t="s">
-        <v>25</v>
+      <c r="C22" s="93" t="s">
+        <v>337</v>
       </c>
       <c r="D22" s="11" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
     </row>
     <row r="23" spans="1:26" ht="38.25" x14ac:dyDescent="0.2">
@@ -4826,32 +5153,32 @@
         <v>12</v>
       </c>
       <c r="C23" s="8" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="D23" s="11" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
     </row>
     <row r="24" spans="1:26" ht="76.5" x14ac:dyDescent="0.2">
       <c r="B24" s="7" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="C24" s="8" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="D24" s="11" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
     </row>
     <row r="25" spans="1:26" ht="38.25" x14ac:dyDescent="0.2">
       <c r="B25" s="7" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="C25" s="8" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="D25" s="11" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
     </row>
     <row r="26" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
@@ -4862,7 +5189,7 @@
     <row r="27" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A27" s="1"/>
       <c r="B27" s="14" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="C27" s="3"/>
       <c r="D27" s="3"/>
@@ -4928,10 +5255,10 @@
         <v>4</v>
       </c>
       <c r="C29" s="8" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="D29" s="11" t="s">
-        <v>37</v>
+        <v>32</v>
       </c>
     </row>
     <row r="30" spans="1:26" ht="63.75" x14ac:dyDescent="0.2">
@@ -4939,10 +5266,10 @@
         <v>6</v>
       </c>
       <c r="C30" s="8" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="D30" s="9" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
     </row>
     <row r="31" spans="1:26" ht="76.5" x14ac:dyDescent="0.2">
@@ -4950,10 +5277,10 @@
         <v>9</v>
       </c>
       <c r="C31" s="8" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="D31" s="11" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
     </row>
     <row r="32" spans="1:26" ht="76.5" x14ac:dyDescent="0.2">
@@ -4961,10 +5288,10 @@
         <v>11</v>
       </c>
       <c r="C32" s="8" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="D32" s="11" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
     </row>
     <row r="33" spans="1:26" ht="140.25" x14ac:dyDescent="0.2">
@@ -4972,10 +5299,10 @@
         <v>12</v>
       </c>
       <c r="C33" s="8" t="s">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="D33" s="11" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
     </row>
     <row r="34" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
@@ -4986,7 +5313,7 @@
     <row r="35" spans="1:26" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A35" s="1"/>
       <c r="B35" s="14" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="C35" s="3"/>
       <c r="D35" s="3"/>
@@ -5052,10 +5379,10 @@
         <v>4</v>
       </c>
       <c r="C37" s="8" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="D37" s="15" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
     </row>
     <row r="38" spans="1:26" ht="127.5" x14ac:dyDescent="0.2">
@@ -5063,10 +5390,10 @@
         <v>6</v>
       </c>
       <c r="C38" s="8" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="D38" s="11" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
     </row>
     <row r="39" spans="1:26" ht="38.25" x14ac:dyDescent="0.2">
@@ -5074,10 +5401,10 @@
         <v>9</v>
       </c>
       <c r="C39" s="8" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="D39" s="11" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
     </row>
     <row r="40" spans="1:26" ht="63.75" x14ac:dyDescent="0.2">
@@ -5085,10 +5412,10 @@
         <v>11</v>
       </c>
       <c r="C40" s="8" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="D40" s="11" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
     </row>
     <row r="41" spans="1:26" ht="89.25" x14ac:dyDescent="0.2">
@@ -5096,10 +5423,10 @@
         <v>12</v>
       </c>
       <c r="C41" s="8" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="D41" s="11" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
     </row>
     <row r="42" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
@@ -5110,7 +5437,7 @@
     <row r="43" spans="1:26" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A43" s="1"/>
       <c r="B43" s="14" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="C43" s="3"/>
       <c r="D43" s="3"/>
@@ -5176,10 +5503,10 @@
         <v>4</v>
       </c>
       <c r="C45" s="8" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="D45" s="11" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
     </row>
     <row r="46" spans="1:26" ht="102" x14ac:dyDescent="0.2">
@@ -5187,10 +5514,10 @@
         <v>6</v>
       </c>
       <c r="C46" s="8" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="D46" s="11" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
     </row>
     <row r="47" spans="1:26" ht="51" x14ac:dyDescent="0.2">
@@ -5198,10 +5525,10 @@
         <v>9</v>
       </c>
       <c r="C47" s="8" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="D47" s="11" t="s">
-        <v>63</v>
+        <v>58</v>
       </c>
     </row>
     <row r="48" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
@@ -5212,7 +5539,7 @@
     <row r="49" spans="1:26" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A49" s="1"/>
       <c r="B49" s="14" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="C49" s="3"/>
       <c r="D49" s="3"/>
@@ -5278,10 +5605,10 @@
         <v>4</v>
       </c>
       <c r="C51" s="8" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="D51" s="11" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
     </row>
     <row r="52" spans="1:26" ht="102" x14ac:dyDescent="0.2">
@@ -5289,10 +5616,10 @@
         <v>6</v>
       </c>
       <c r="C52" s="8" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="D52" s="11" t="s">
-        <v>66</v>
+        <v>61</v>
       </c>
     </row>
     <row r="53" spans="1:26" ht="51" x14ac:dyDescent="0.2">
@@ -5300,10 +5627,10 @@
         <v>9</v>
       </c>
       <c r="C53" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="D53" s="11" t="s">
         <v>62</v>
-      </c>
-      <c r="D53" s="11" t="s">
-        <v>67</v>
       </c>
     </row>
     <row r="54" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
@@ -5314,7 +5641,7 @@
     <row r="55" spans="1:26" ht="38.25" x14ac:dyDescent="0.2">
       <c r="A55" s="1"/>
       <c r="B55" s="14" t="s">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="C55" s="3"/>
       <c r="D55" s="3"/>
@@ -5380,10 +5707,10 @@
         <v>4</v>
       </c>
       <c r="C57" s="8" t="s">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="D57" s="11" t="s">
-        <v>70</v>
+        <v>65</v>
       </c>
     </row>
     <row r="58" spans="1:26" ht="63.75" x14ac:dyDescent="0.2">
@@ -5391,10 +5718,10 @@
         <v>6</v>
       </c>
       <c r="C58" s="8" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="D58" s="11" t="s">
-        <v>71</v>
+        <v>66</v>
       </c>
     </row>
     <row r="59" spans="1:26" ht="89.25" x14ac:dyDescent="0.2">
@@ -5402,10 +5729,10 @@
         <v>9</v>
       </c>
       <c r="C59" s="8" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="D59" s="11" t="s">
-        <v>72</v>
+        <v>67</v>
       </c>
     </row>
     <row r="60" spans="1:26" ht="102" x14ac:dyDescent="0.2">
@@ -5413,10 +5740,10 @@
         <v>11</v>
       </c>
       <c r="C60" s="8" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="D60" s="11" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
     </row>
     <row r="61" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
@@ -5425,37 +5752,37 @@
       <c r="D61" s="13"/>
     </row>
     <row r="62" spans="1:26" ht="51" x14ac:dyDescent="0.2">
-      <c r="A62" s="17"/>
+      <c r="A62" s="16"/>
       <c r="B62" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="C62" s="18"/>
-      <c r="D62" s="18"/>
-      <c r="E62" s="17"/>
-      <c r="F62" s="17"/>
-      <c r="G62" s="17"/>
-      <c r="H62" s="17"/>
-      <c r="I62" s="17"/>
-      <c r="J62" s="17"/>
-      <c r="K62" s="17"/>
-      <c r="L62" s="17"/>
-      <c r="M62" s="17"/>
-      <c r="N62" s="17"/>
-      <c r="O62" s="17"/>
-      <c r="P62" s="17"/>
-      <c r="Q62" s="17"/>
-      <c r="R62" s="17"/>
-      <c r="S62" s="17"/>
-      <c r="T62" s="17"/>
-      <c r="U62" s="17"/>
-      <c r="V62" s="17"/>
-      <c r="W62" s="17"/>
-      <c r="X62" s="17"/>
-      <c r="Y62" s="17"/>
-      <c r="Z62" s="17"/>
+        <v>69</v>
+      </c>
+      <c r="C62" s="17"/>
+      <c r="D62" s="17"/>
+      <c r="E62" s="16"/>
+      <c r="F62" s="16"/>
+      <c r="G62" s="16"/>
+      <c r="H62" s="16"/>
+      <c r="I62" s="16"/>
+      <c r="J62" s="16"/>
+      <c r="K62" s="16"/>
+      <c r="L62" s="16"/>
+      <c r="M62" s="16"/>
+      <c r="N62" s="16"/>
+      <c r="O62" s="16"/>
+      <c r="P62" s="16"/>
+      <c r="Q62" s="16"/>
+      <c r="R62" s="16"/>
+      <c r="S62" s="16"/>
+      <c r="T62" s="16"/>
+      <c r="U62" s="16"/>
+      <c r="V62" s="16"/>
+      <c r="W62" s="16"/>
+      <c r="X62" s="16"/>
+      <c r="Y62" s="16"/>
+      <c r="Z62" s="16"/>
     </row>
     <row r="63" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A63" s="17"/>
+      <c r="A63" s="16"/>
       <c r="B63" s="4" t="s">
         <v>1</v>
       </c>
@@ -5465,38 +5792,38 @@
       <c r="D63" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="E63" s="17"/>
-      <c r="F63" s="17"/>
-      <c r="G63" s="17"/>
-      <c r="H63" s="17"/>
-      <c r="I63" s="17"/>
-      <c r="J63" s="17"/>
-      <c r="K63" s="17"/>
-      <c r="L63" s="17"/>
-      <c r="M63" s="17"/>
-      <c r="N63" s="17"/>
-      <c r="O63" s="17"/>
-      <c r="P63" s="17"/>
-      <c r="Q63" s="17"/>
-      <c r="R63" s="17"/>
-      <c r="S63" s="17"/>
-      <c r="T63" s="17"/>
-      <c r="U63" s="17"/>
-      <c r="V63" s="17"/>
-      <c r="W63" s="17"/>
-      <c r="X63" s="17"/>
-      <c r="Y63" s="17"/>
-      <c r="Z63" s="17"/>
+      <c r="E63" s="16"/>
+      <c r="F63" s="16"/>
+      <c r="G63" s="16"/>
+      <c r="H63" s="16"/>
+      <c r="I63" s="16"/>
+      <c r="J63" s="16"/>
+      <c r="K63" s="16"/>
+      <c r="L63" s="16"/>
+      <c r="M63" s="16"/>
+      <c r="N63" s="16"/>
+      <c r="O63" s="16"/>
+      <c r="P63" s="16"/>
+      <c r="Q63" s="16"/>
+      <c r="R63" s="16"/>
+      <c r="S63" s="16"/>
+      <c r="T63" s="16"/>
+      <c r="U63" s="16"/>
+      <c r="V63" s="16"/>
+      <c r="W63" s="16"/>
+      <c r="X63" s="16"/>
+      <c r="Y63" s="16"/>
+      <c r="Z63" s="16"/>
     </row>
     <row r="64" spans="1:26" ht="63.75" x14ac:dyDescent="0.2">
       <c r="B64" s="7" t="s">
         <v>4</v>
       </c>
       <c r="C64" s="8" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="D64" s="11" t="s">
-        <v>76</v>
+        <v>71</v>
       </c>
     </row>
     <row r="65" spans="2:4" ht="89.25" x14ac:dyDescent="0.2">
@@ -5504,10 +5831,10 @@
         <v>6</v>
       </c>
       <c r="C65" s="8" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="D65" s="11" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
     </row>
     <row r="66" spans="2:4" ht="51" x14ac:dyDescent="0.2">
@@ -5515,10 +5842,10 @@
         <v>9</v>
       </c>
       <c r="C66" s="8" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="D66" s="9" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
     </row>
     <row r="67" spans="2:4" ht="38.25" x14ac:dyDescent="0.2">
@@ -5526,14 +5853,14 @@
         <v>11</v>
       </c>
       <c r="C67" s="8" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="D67" s="11" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="24"/>
+  <phoneticPr fontId="21"/>
   <hyperlinks>
     <hyperlink ref="D4" r:id="rId1" location="heading=h.1c7inwl4nhdn" xr:uid="{00000000-0004-0000-0100-000000000000}"/>
     <hyperlink ref="D5" r:id="rId2" location="section2" xr:uid="{00000000-0004-0000-0100-000001000000}"/>
@@ -5563,12 +5890,12 @@
   <sheetData>
     <row r="1" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="13" t="s">
-        <v>83</v>
+        <v>78</v>
       </c>
     </row>
     <row r="2" spans="1:26" ht="27" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="19" t="s">
-        <v>84</v>
+      <c r="A2" s="18" t="s">
+        <v>79</v>
       </c>
       <c r="B2" s="10"/>
       <c r="C2" s="10"/>
@@ -5601,12 +5928,12 @@
     </row>
     <row r="4" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="13" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
     </row>
     <row r="5" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="81" t="s">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="B5" s="82"/>
       <c r="C5" s="82"/>
@@ -5621,21 +5948,21 @@
     </row>
     <row r="7" spans="1:26" ht="56.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="13" t="s">
-        <v>87</v>
-      </c>
-      <c r="K7" s="19"/>
+        <v>82</v>
+      </c>
+      <c r="K7" s="18"/>
     </row>
     <row r="8" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="20" t="s">
-        <v>88</v>
+      <c r="A8" s="19" t="s">
+        <v>83</v>
       </c>
       <c r="K8" s="13"/>
     </row>
     <row r="9" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="75" t="s">
-        <v>329</v>
-      </c>
-      <c r="K9" s="21"/>
+      <c r="A9" s="74" t="s">
+        <v>324</v>
+      </c>
+      <c r="K9" s="20"/>
     </row>
     <row r="10" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="K10" s="13"/>
@@ -5644,7 +5971,7 @@
       <c r="K11" s="13"/>
     </row>
     <row r="12" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="K12" s="22"/>
+      <c r="K12" s="21"/>
     </row>
     <row r="13" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="K13" s="13"/>
@@ -5656,7 +5983,7 @@
       <c r="K15" s="13"/>
     </row>
     <row r="16" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="K16" s="22"/>
+      <c r="K16" s="21"/>
     </row>
     <row r="17" spans="11:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="K17" s="13"/>
@@ -6648,7 +6975,7 @@
   <mergeCells count="1">
     <mergeCell ref="A5:F5"/>
   </mergeCells>
-  <phoneticPr fontId="24"/>
+  <phoneticPr fontId="21"/>
   <hyperlinks>
     <hyperlink ref="A8" r:id="rId1" xr:uid="{00000000-0004-0000-0200-000000000000}"/>
   </hyperlinks>
@@ -6671,470 +6998,470 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="23" t="s">
+      <c r="A1" s="22" t="s">
+        <v>84</v>
+      </c>
+      <c r="B1" s="23" t="s">
+        <v>85</v>
+      </c>
+      <c r="C1" s="24"/>
+      <c r="D1" s="24"/>
+    </row>
+    <row r="2" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2" s="24"/>
+      <c r="B2" s="25" t="s">
+        <v>86</v>
+      </c>
+      <c r="C2" s="25" t="s">
+        <v>87</v>
+      </c>
+      <c r="D2" s="26" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" ht="44.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A3" s="24"/>
+      <c r="B3" s="27" t="s">
         <v>89</v>
       </c>
-      <c r="B1" s="24" t="s">
+      <c r="C3" s="27" t="s">
         <v>90</v>
       </c>
-      <c r="C1" s="25"/>
-      <c r="D1" s="25"/>
-    </row>
-    <row r="2" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="25"/>
-      <c r="B2" s="26" t="s">
+      <c r="D3" s="28" t="s">
         <v>91</v>
       </c>
-      <c r="C2" s="26" t="s">
+      <c r="E3" s="29"/>
+    </row>
+    <row r="4" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A4" s="24"/>
+      <c r="B4" s="24"/>
+      <c r="C4" s="24"/>
+      <c r="D4" s="30"/>
+    </row>
+    <row r="5" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A5" s="24"/>
+      <c r="B5" s="23" t="s">
         <v>92</v>
       </c>
-      <c r="D2" s="27" t="s">
+      <c r="C5" s="24"/>
+      <c r="D5" s="31"/>
+    </row>
+    <row r="6" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A6" s="24"/>
+      <c r="B6" s="25" t="s">
+        <v>86</v>
+      </c>
+      <c r="C6" s="25" t="s">
+        <v>87</v>
+      </c>
+      <c r="D6" s="26" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" ht="46.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A7" s="24"/>
+      <c r="B7" s="27" t="s">
+        <v>92</v>
+      </c>
+      <c r="C7" s="27" t="s">
         <v>93</v>
       </c>
-    </row>
-    <row r="3" spans="1:5" ht="44.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="25"/>
-      <c r="B3" s="28" t="s">
+      <c r="D7" s="28" t="s">
         <v>94</v>
       </c>
-      <c r="C3" s="28" t="s">
+    </row>
+    <row r="8" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A8" s="24"/>
+      <c r="B8" s="32"/>
+      <c r="C8" s="32"/>
+      <c r="D8" s="24"/>
+    </row>
+    <row r="9" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A9" s="24"/>
+      <c r="B9" s="23" t="s">
         <v>95</v>
       </c>
-      <c r="D3" s="29" t="s">
+      <c r="C9" s="24"/>
+      <c r="D9" s="24"/>
+    </row>
+    <row r="10" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A10" s="24"/>
+      <c r="B10" s="25" t="s">
+        <v>86</v>
+      </c>
+      <c r="C10" s="25" t="s">
+        <v>87</v>
+      </c>
+      <c r="D10" s="26" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" ht="34.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A11" s="24"/>
+      <c r="B11" s="27" t="s">
         <v>96</v>
       </c>
-      <c r="E3" s="30"/>
-    </row>
-    <row r="4" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="25"/>
-      <c r="B4" s="25"/>
-      <c r="C4" s="25"/>
-      <c r="D4" s="31"/>
-    </row>
-    <row r="5" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="25"/>
-      <c r="B5" s="24" t="s">
+      <c r="C11" s="27" t="s">
         <v>97</v>
       </c>
-      <c r="C5" s="25"/>
-      <c r="D5" s="32"/>
-    </row>
-    <row r="6" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="25"/>
-      <c r="B6" s="26" t="s">
-        <v>91</v>
-      </c>
-      <c r="C6" s="26" t="s">
-        <v>92</v>
-      </c>
-      <c r="D6" s="27" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" ht="46.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="25"/>
-      <c r="B7" s="28" t="s">
-        <v>97</v>
-      </c>
-      <c r="C7" s="28" t="s">
+      <c r="D11" s="28"/>
+    </row>
+    <row r="12" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A12" s="24"/>
+      <c r="B12" s="24"/>
+      <c r="C12" s="24"/>
+      <c r="D12" s="24"/>
+    </row>
+    <row r="13" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A13" s="24"/>
+      <c r="B13" s="23" t="s">
         <v>98</v>
       </c>
-      <c r="D7" s="29" t="s">
+      <c r="C13" s="24"/>
+      <c r="D13" s="24"/>
+    </row>
+    <row r="14" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A14" s="24"/>
+      <c r="B14" s="25" t="s">
+        <v>86</v>
+      </c>
+      <c r="C14" s="25" t="s">
+        <v>87</v>
+      </c>
+      <c r="D14" s="26" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" ht="34.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A15" s="24"/>
+      <c r="B15" s="27" t="s">
         <v>99</v>
       </c>
-    </row>
-    <row r="8" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="25"/>
-      <c r="B8" s="33"/>
-      <c r="C8" s="33"/>
-      <c r="D8" s="25"/>
-    </row>
-    <row r="9" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="25"/>
-      <c r="B9" s="24" t="s">
+      <c r="C15" s="27" t="s">
         <v>100</v>
       </c>
-      <c r="C9" s="25"/>
-      <c r="D9" s="25"/>
-    </row>
-    <row r="10" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="25"/>
-      <c r="B10" s="26" t="s">
-        <v>91</v>
-      </c>
-      <c r="C10" s="26" t="s">
-        <v>92</v>
-      </c>
-      <c r="D10" s="27" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" ht="34.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="25"/>
-      <c r="B11" s="28" t="s">
+      <c r="D15" s="28" t="s">
         <v>101</v>
       </c>
-      <c r="C11" s="28" t="s">
+    </row>
+    <row r="16" spans="1:5" ht="34.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A16" s="24"/>
+      <c r="B16" s="27" t="s">
         <v>102</v>
       </c>
-      <c r="D11" s="29"/>
-    </row>
-    <row r="12" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="25"/>
-      <c r="B12" s="25"/>
-      <c r="C12" s="25"/>
-      <c r="D12" s="25"/>
-    </row>
-    <row r="13" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="25"/>
-      <c r="B13" s="24" t="s">
+      <c r="C16" s="27" t="s">
         <v>103</v>
       </c>
-      <c r="C13" s="25"/>
-      <c r="D13" s="25"/>
-    </row>
-    <row r="14" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="25"/>
-      <c r="B14" s="26" t="s">
-        <v>91</v>
-      </c>
-      <c r="C14" s="26" t="s">
-        <v>92</v>
-      </c>
-      <c r="D14" s="27" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5" ht="34.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="25"/>
-      <c r="B15" s="28" t="s">
+      <c r="D16" s="28" t="s">
         <v>104</v>
       </c>
-      <c r="C15" s="28" t="s">
+    </row>
+    <row r="17" spans="1:4" ht="34.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A17" s="24"/>
+      <c r="B17" s="27" t="s">
         <v>105</v>
       </c>
-      <c r="D15" s="29" t="s">
+      <c r="C17" s="27" t="s">
         <v>106</v>
       </c>
-    </row>
-    <row r="16" spans="1:5" ht="34.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="25"/>
-      <c r="B16" s="28" t="s">
+      <c r="D17" s="28" t="s">
         <v>107</v>
       </c>
-      <c r="C16" s="28" t="s">
+    </row>
+    <row r="18" spans="1:4" ht="34.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A18" s="24"/>
+      <c r="B18" s="27" t="s">
         <v>108</v>
       </c>
-      <c r="D16" s="29" t="s">
+      <c r="C18" s="27" t="s">
         <v>109</v>
       </c>
-    </row>
-    <row r="17" spans="1:4" ht="34.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="25"/>
-      <c r="B17" s="28" t="s">
+      <c r="D18" s="28" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A19" s="24"/>
+      <c r="B19" s="24"/>
+      <c r="C19" s="24"/>
+      <c r="D19" s="24"/>
+    </row>
+    <row r="20" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A20" s="24"/>
+      <c r="B20" s="23" t="s">
         <v>110</v>
       </c>
-      <c r="C17" s="28" t="s">
+      <c r="C20" s="24"/>
+      <c r="D20" s="24"/>
+    </row>
+    <row r="21" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A21" s="24"/>
+      <c r="B21" s="25" t="s">
+        <v>86</v>
+      </c>
+      <c r="C21" s="25" t="s">
+        <v>87</v>
+      </c>
+      <c r="D21" s="26" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" ht="43.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A22" s="24"/>
+      <c r="B22" s="27" t="s">
         <v>111</v>
       </c>
-      <c r="D17" s="29" t="s">
+      <c r="C22" s="27" t="s">
         <v>112</v>
       </c>
-    </row>
-    <row r="18" spans="1:4" ht="34.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="25"/>
-      <c r="B18" s="28" t="s">
+      <c r="D22" s="28" t="s">
         <v>113</v>
       </c>
-      <c r="C18" s="28" t="s">
+    </row>
+    <row r="23" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A23" s="24"/>
+      <c r="B23" s="24"/>
+      <c r="C23" s="24"/>
+      <c r="D23" s="24"/>
+    </row>
+    <row r="24" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A24" s="24"/>
+      <c r="B24" s="23" t="s">
         <v>114</v>
       </c>
-      <c r="D18" s="29" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="25"/>
-      <c r="B19" s="25"/>
-      <c r="C19" s="25"/>
-      <c r="D19" s="25"/>
-    </row>
-    <row r="20" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="25"/>
-      <c r="B20" s="24" t="s">
+      <c r="C24" s="24"/>
+      <c r="D24" s="24"/>
+    </row>
+    <row r="25" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A25" s="24"/>
+      <c r="B25" s="25" t="s">
+        <v>86</v>
+      </c>
+      <c r="C25" s="25" t="s">
+        <v>87</v>
+      </c>
+      <c r="D25" s="26" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" ht="45.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A26" s="24"/>
+      <c r="B26" s="27" t="s">
         <v>115</v>
       </c>
-      <c r="C20" s="25"/>
-      <c r="D20" s="25"/>
-    </row>
-    <row r="21" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A21" s="25"/>
-      <c r="B21" s="26" t="s">
-        <v>91</v>
-      </c>
-      <c r="C21" s="26" t="s">
-        <v>92</v>
-      </c>
-      <c r="D21" s="27" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="22" spans="1:4" ht="43.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="25"/>
-      <c r="B22" s="28" t="s">
+      <c r="C26" s="27" t="s">
         <v>116</v>
       </c>
-      <c r="C22" s="28" t="s">
+      <c r="D26" s="28" t="s">
         <v>117</v>
       </c>
-      <c r="D22" s="29" t="s">
+    </row>
+    <row r="27" spans="1:4" ht="45.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A27" s="24"/>
+      <c r="B27" s="27" t="s">
         <v>118</v>
       </c>
-    </row>
-    <row r="23" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="25"/>
-      <c r="B23" s="25"/>
-      <c r="C23" s="25"/>
-      <c r="D23" s="25"/>
-    </row>
-    <row r="24" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A24" s="25"/>
-      <c r="B24" s="24" t="s">
+      <c r="C27" s="27" t="s">
         <v>119</v>
       </c>
-      <c r="C24" s="25"/>
-      <c r="D24" s="25"/>
-    </row>
-    <row r="25" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="25"/>
-      <c r="B25" s="26" t="s">
-        <v>91</v>
-      </c>
-      <c r="C25" s="26" t="s">
-        <v>92</v>
-      </c>
-      <c r="D25" s="27" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="26" spans="1:4" ht="45.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A26" s="25"/>
-      <c r="B26" s="28" t="s">
+      <c r="D27" s="28" t="s">
         <v>120</v>
       </c>
-      <c r="C26" s="28" t="s">
+    </row>
+    <row r="28" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A28" s="24"/>
+      <c r="B28" s="32"/>
+      <c r="C28" s="32"/>
+      <c r="D28" s="24"/>
+    </row>
+    <row r="29" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A29" s="24"/>
+      <c r="B29" s="23" t="s">
         <v>121</v>
       </c>
-      <c r="D26" s="29" t="s">
+      <c r="C29" s="24"/>
+      <c r="D29" s="24"/>
+    </row>
+    <row r="30" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A30" s="24"/>
+      <c r="B30" s="25" t="s">
+        <v>86</v>
+      </c>
+      <c r="C30" s="25" t="s">
+        <v>87</v>
+      </c>
+      <c r="D30" s="26" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" ht="47.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A31" s="24"/>
+      <c r="B31" s="27" t="s">
         <v>122</v>
       </c>
-    </row>
-    <row r="27" spans="1:4" ht="45.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A27" s="25"/>
-      <c r="B27" s="28" t="s">
+      <c r="C31" s="27" t="s">
         <v>123</v>
       </c>
-      <c r="C27" s="28" t="s">
+      <c r="D31" s="28"/>
+    </row>
+    <row r="32" spans="1:4" ht="47.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A32" s="24"/>
+      <c r="B32" s="27" t="s">
+        <v>118</v>
+      </c>
+      <c r="C32" s="33" t="s">
         <v>124</v>
       </c>
-      <c r="D27" s="29" t="s">
+      <c r="D32" s="28" t="s">
         <v>125</v>
       </c>
     </row>
-    <row r="28" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A28" s="25"/>
-      <c r="B28" s="33"/>
-      <c r="C28" s="33"/>
-      <c r="D28" s="25"/>
-    </row>
-    <row r="29" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A29" s="25"/>
-      <c r="B29" s="24" t="s">
+    <row r="33" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A33" s="24"/>
+      <c r="B33" s="32"/>
+      <c r="C33" s="24"/>
+      <c r="D33" s="24"/>
+    </row>
+    <row r="34" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A34" s="24"/>
+      <c r="B34" s="23" t="s">
         <v>126</v>
       </c>
-      <c r="C29" s="25"/>
-      <c r="D29" s="25"/>
-    </row>
-    <row r="30" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A30" s="25"/>
-      <c r="B30" s="26" t="s">
-        <v>91</v>
-      </c>
-      <c r="C30" s="26" t="s">
-        <v>92</v>
-      </c>
-      <c r="D30" s="27" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="31" spans="1:4" ht="47.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A31" s="25"/>
-      <c r="B31" s="28" t="s">
+      <c r="C34" s="24"/>
+      <c r="D34" s="24"/>
+    </row>
+    <row r="35" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A35" s="24"/>
+      <c r="B35" s="25" t="s">
+        <v>86</v>
+      </c>
+      <c r="C35" s="25" t="s">
+        <v>87</v>
+      </c>
+      <c r="D35" s="26" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4" ht="37.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A36" s="24"/>
+      <c r="B36" s="27" t="s">
         <v>127</v>
       </c>
-      <c r="C31" s="28" t="s">
+      <c r="C36" s="27" t="s">
         <v>128</v>
       </c>
-      <c r="D31" s="29"/>
-    </row>
-    <row r="32" spans="1:4" ht="47.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A32" s="25"/>
-      <c r="B32" s="28" t="s">
-        <v>123</v>
-      </c>
-      <c r="C32" s="34" t="s">
+      <c r="D36" s="28" t="s">
         <v>129</v>
       </c>
-      <c r="D32" s="29" t="s">
+    </row>
+    <row r="37" spans="1:4" ht="37.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A37" s="24"/>
+      <c r="B37" s="27" t="s">
         <v>130</v>
       </c>
-    </row>
-    <row r="33" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A33" s="25"/>
-      <c r="B33" s="33"/>
-      <c r="C33" s="25"/>
-      <c r="D33" s="25"/>
-    </row>
-    <row r="34" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A34" s="25"/>
-      <c r="B34" s="24" t="s">
+      <c r="C37" s="27" t="s">
         <v>131</v>
       </c>
-      <c r="C34" s="25"/>
-      <c r="D34" s="25"/>
-    </row>
-    <row r="35" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A35" s="25"/>
-      <c r="B35" s="26" t="s">
-        <v>91</v>
-      </c>
-      <c r="C35" s="26" t="s">
-        <v>92</v>
-      </c>
-      <c r="D35" s="27" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="36" spans="1:4" ht="37.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A36" s="25"/>
-      <c r="B36" s="28" t="s">
+      <c r="D37" s="28" t="s">
         <v>132</v>
       </c>
-      <c r="C36" s="28" t="s">
+    </row>
+    <row r="38" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A38" s="24"/>
+      <c r="B38" s="32"/>
+      <c r="C38" s="24"/>
+      <c r="D38" s="24"/>
+    </row>
+    <row r="39" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A39" s="24"/>
+      <c r="B39" s="23" t="s">
         <v>133</v>
       </c>
-      <c r="D36" s="29" t="s">
+      <c r="C39" s="24"/>
+      <c r="D39" s="24"/>
+    </row>
+    <row r="40" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A40" s="24"/>
+      <c r="B40" s="25" t="s">
+        <v>86</v>
+      </c>
+      <c r="C40" s="25" t="s">
+        <v>87</v>
+      </c>
+      <c r="D40" s="26" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A41" s="24"/>
+      <c r="B41" s="27" t="s">
         <v>134</v>
       </c>
-    </row>
-    <row r="37" spans="1:4" ht="37.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A37" s="25"/>
-      <c r="B37" s="28" t="s">
+      <c r="C41" s="27" t="s">
         <v>135</v>
       </c>
-      <c r="C37" s="28" t="s">
+      <c r="D41" s="28" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A42" s="24"/>
+      <c r="B42" s="27" t="s">
         <v>136</v>
       </c>
-      <c r="D37" s="29" t="s">
+      <c r="C42" s="27" t="s">
         <v>137</v>
       </c>
-    </row>
-    <row r="38" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A38" s="25"/>
-      <c r="B38" s="33"/>
-      <c r="C38" s="25"/>
-      <c r="D38" s="25"/>
-    </row>
-    <row r="39" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A39" s="25"/>
-      <c r="B39" s="24" t="s">
+      <c r="D42" s="28" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A43" s="24"/>
+      <c r="B43" s="32"/>
+      <c r="C43" s="24"/>
+      <c r="D43" s="24"/>
+    </row>
+    <row r="44" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A44" s="24"/>
+      <c r="B44" s="23" t="s">
         <v>138</v>
       </c>
-      <c r="C39" s="25"/>
-      <c r="D39" s="25"/>
-    </row>
-    <row r="40" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A40" s="25"/>
-      <c r="B40" s="26" t="s">
-        <v>91</v>
-      </c>
-      <c r="C40" s="26" t="s">
-        <v>92</v>
-      </c>
-      <c r="D40" s="27" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="41" spans="1:4" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A41" s="25"/>
-      <c r="B41" s="28" t="s">
+      <c r="C44" s="24"/>
+      <c r="D44" s="24"/>
+    </row>
+    <row r="45" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A45" s="24"/>
+      <c r="B45" s="25" t="s">
+        <v>86</v>
+      </c>
+      <c r="C45" s="25" t="s">
+        <v>87</v>
+      </c>
+      <c r="D45" s="26" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="46" spans="1:4" ht="39" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A46" s="24"/>
+      <c r="B46" s="27" t="s">
         <v>139</v>
       </c>
-      <c r="C41" s="28" t="s">
+      <c r="C46" s="27" t="s">
         <v>140</v>
       </c>
-      <c r="D41" s="29" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="42" spans="1:4" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A42" s="25"/>
-      <c r="B42" s="28" t="s">
+      <c r="D46" s="28"/>
+    </row>
+    <row r="47" spans="1:4" ht="39" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A47" s="24"/>
+      <c r="B47" s="27" t="s">
         <v>141</v>
       </c>
-      <c r="C42" s="28" t="s">
+      <c r="C47" s="27" t="s">
         <v>142</v>
       </c>
-      <c r="D42" s="29" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="43" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A43" s="25"/>
-      <c r="B43" s="33"/>
-      <c r="C43" s="25"/>
-      <c r="D43" s="25"/>
-    </row>
-    <row r="44" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A44" s="25"/>
-      <c r="B44" s="24" t="s">
-        <v>143</v>
-      </c>
-      <c r="C44" s="25"/>
-      <c r="D44" s="25"/>
-    </row>
-    <row r="45" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A45" s="25"/>
-      <c r="B45" s="26" t="s">
-        <v>91</v>
-      </c>
-      <c r="C45" s="26" t="s">
-        <v>92</v>
-      </c>
-      <c r="D45" s="27" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="46" spans="1:4" ht="39" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A46" s="25"/>
-      <c r="B46" s="28" t="s">
-        <v>144</v>
-      </c>
-      <c r="C46" s="28" t="s">
-        <v>145</v>
-      </c>
-      <c r="D46" s="29"/>
-    </row>
-    <row r="47" spans="1:4" ht="39" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A47" s="25"/>
-      <c r="B47" s="28" t="s">
-        <v>146</v>
-      </c>
-      <c r="C47" s="28" t="s">
-        <v>147</v>
-      </c>
-      <c r="D47" s="29" t="s">
-        <v>137</v>
+      <c r="D47" s="28" t="s">
+        <v>132</v>
       </c>
     </row>
     <row r="48" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
@@ -8091,7 +8418,7 @@
     <row r="999" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="1000" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
   </sheetData>
-  <phoneticPr fontId="24"/>
+  <phoneticPr fontId="21"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -8114,7 +8441,7 @@
   <sheetData>
     <row r="1" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="83" t="s">
-        <v>148</v>
+        <v>143</v>
       </c>
       <c r="B1" s="82"/>
       <c r="C1" s="82"/>
@@ -8126,16 +8453,16 @@
       <c r="I1" s="82"/>
     </row>
     <row r="2" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="35" t="s">
-        <v>149</v>
-      </c>
-      <c r="B2" s="36" t="s">
-        <v>150</v>
+      <c r="A2" s="34" t="s">
+        <v>144</v>
+      </c>
+      <c r="B2" s="35" t="s">
+        <v>145</v>
       </c>
       <c r="C2" s="13"/>
-      <c r="D2" s="37"/>
-      <c r="E2" s="38"/>
-      <c r="F2" s="37"/>
+      <c r="D2" s="36"/>
+      <c r="E2" s="37"/>
+      <c r="F2" s="36"/>
       <c r="G2" s="13"/>
       <c r="H2" s="13"/>
       <c r="I2" s="13"/>
@@ -8150,15 +8477,15 @@
       <c r="G3" s="13"/>
       <c r="H3" s="13"/>
       <c r="I3" s="13"/>
-      <c r="J3" s="39"/>
-      <c r="K3" s="39"/>
+      <c r="J3" s="38"/>
+      <c r="K3" s="38"/>
     </row>
     <row r="4" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="40" t="s">
-        <v>151</v>
+      <c r="A4" s="39" t="s">
+        <v>146</v>
       </c>
       <c r="B4" s="84" t="s">
-        <v>152</v>
+        <v>147</v>
       </c>
       <c r="C4" s="85"/>
       <c r="D4" s="85"/>
@@ -8167,225 +8494,225 @@
       <c r="G4" s="85"/>
       <c r="H4" s="86"/>
       <c r="I4" s="13"/>
-      <c r="J4" s="41"/>
-      <c r="K4" s="39"/>
+      <c r="J4" s="40"/>
+      <c r="K4" s="38"/>
     </row>
     <row r="5" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="13"/>
-      <c r="B5" s="42" t="s">
+      <c r="B5" s="41" t="s">
+        <v>148</v>
+      </c>
+      <c r="C5" s="41" t="s">
+        <v>149</v>
+      </c>
+      <c r="D5" s="41" t="s">
+        <v>150</v>
+      </c>
+      <c r="E5" s="41" t="s">
+        <v>151</v>
+      </c>
+      <c r="F5" s="41" t="s">
+        <v>152</v>
+      </c>
+      <c r="G5" s="41" t="s">
         <v>153</v>
       </c>
-      <c r="C5" s="42" t="s">
+      <c r="H5" s="41" t="s">
         <v>154</v>
       </c>
-      <c r="D5" s="42" t="s">
-        <v>155</v>
-      </c>
-      <c r="E5" s="42" t="s">
-        <v>156</v>
-      </c>
-      <c r="F5" s="42" t="s">
-        <v>157</v>
-      </c>
-      <c r="G5" s="42" t="s">
-        <v>158</v>
-      </c>
-      <c r="H5" s="42" t="s">
-        <v>159</v>
-      </c>
       <c r="I5" s="13"/>
-      <c r="J5" s="39"/>
-      <c r="K5" s="41"/>
+      <c r="J5" s="38"/>
+      <c r="K5" s="40"/>
     </row>
     <row r="6" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="13"/>
-      <c r="B6" s="43" t="s">
+      <c r="B6" s="42" t="s">
+        <v>155</v>
+      </c>
+      <c r="C6" s="42" t="s">
+        <v>156</v>
+      </c>
+      <c r="D6" s="42" t="s">
+        <v>157</v>
+      </c>
+      <c r="E6" s="42" t="s">
+        <v>158</v>
+      </c>
+      <c r="F6" s="42" t="s">
+        <v>159</v>
+      </c>
+      <c r="G6" s="42" t="s">
         <v>160</v>
       </c>
-      <c r="C6" s="43" t="s">
-        <v>161</v>
-      </c>
-      <c r="D6" s="43" t="s">
-        <v>162</v>
-      </c>
-      <c r="E6" s="43" t="s">
-        <v>163</v>
-      </c>
-      <c r="F6" s="43" t="s">
-        <v>164</v>
-      </c>
-      <c r="G6" s="43" t="s">
-        <v>165</v>
-      </c>
-      <c r="H6" s="43"/>
+      <c r="H6" s="42"/>
       <c r="I6" s="13"/>
-      <c r="J6" s="39"/>
-      <c r="K6" s="39"/>
+      <c r="J6" s="38"/>
+      <c r="K6" s="38"/>
     </row>
     <row r="7" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="13"/>
-      <c r="B7" s="43" t="s">
-        <v>166</v>
-      </c>
-      <c r="C7" s="43" t="s">
-        <v>167</v>
-      </c>
-      <c r="D7" s="43" t="s">
-        <v>168</v>
-      </c>
-      <c r="E7" s="43" t="s">
+      <c r="B7" s="42" t="s">
+        <v>161</v>
+      </c>
+      <c r="C7" s="42" t="s">
+        <v>162</v>
+      </c>
+      <c r="D7" s="42" t="s">
         <v>163</v>
       </c>
-      <c r="F7" s="43"/>
-      <c r="G7" s="43" t="s">
-        <v>165</v>
-      </c>
-      <c r="H7" s="43"/>
+      <c r="E7" s="42" t="s">
+        <v>158</v>
+      </c>
+      <c r="F7" s="42"/>
+      <c r="G7" s="42" t="s">
+        <v>160</v>
+      </c>
+      <c r="H7" s="42"/>
       <c r="I7" s="13"/>
-      <c r="J7" s="39"/>
-      <c r="K7" s="39"/>
+      <c r="J7" s="38"/>
+      <c r="K7" s="38"/>
     </row>
     <row r="8" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="13"/>
-      <c r="B8" s="43" t="s">
-        <v>169</v>
-      </c>
-      <c r="C8" s="43" t="s">
-        <v>170</v>
-      </c>
-      <c r="D8" s="43" t="s">
-        <v>168</v>
-      </c>
-      <c r="E8" s="43" t="s">
+      <c r="B8" s="42" t="s">
+        <v>164</v>
+      </c>
+      <c r="C8" s="42" t="s">
+        <v>165</v>
+      </c>
+      <c r="D8" s="42" t="s">
         <v>163</v>
       </c>
-      <c r="F8" s="43" t="s">
-        <v>171</v>
-      </c>
-      <c r="G8" s="43" t="s">
-        <v>165</v>
-      </c>
-      <c r="H8" s="43"/>
+      <c r="E8" s="42" t="s">
+        <v>158</v>
+      </c>
+      <c r="F8" s="42" t="s">
+        <v>166</v>
+      </c>
+      <c r="G8" s="42" t="s">
+        <v>160</v>
+      </c>
+      <c r="H8" s="42"/>
       <c r="I8" s="13"/>
-      <c r="J8" s="39"/>
-      <c r="K8" s="39"/>
+      <c r="J8" s="38"/>
+      <c r="K8" s="38"/>
     </row>
     <row r="9" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="13"/>
-      <c r="B9" s="43" t="s">
-        <v>172</v>
-      </c>
-      <c r="C9" s="43" t="s">
-        <v>173</v>
-      </c>
-      <c r="D9" s="43" t="s">
+      <c r="B9" s="42" t="s">
+        <v>167</v>
+      </c>
+      <c r="C9" s="42" t="s">
         <v>168</v>
       </c>
-      <c r="E9" s="43" t="s">
+      <c r="D9" s="42" t="s">
         <v>163</v>
       </c>
-      <c r="F9" s="43"/>
-      <c r="G9" s="43" t="s">
-        <v>165</v>
-      </c>
-      <c r="H9" s="43"/>
+      <c r="E9" s="42" t="s">
+        <v>158</v>
+      </c>
+      <c r="F9" s="42"/>
+      <c r="G9" s="42" t="s">
+        <v>160</v>
+      </c>
+      <c r="H9" s="42"/>
       <c r="I9" s="13"/>
-      <c r="J9" s="39"/>
-      <c r="K9" s="39"/>
+      <c r="J9" s="38"/>
+      <c r="K9" s="38"/>
     </row>
     <row r="10" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="13"/>
-      <c r="B10" s="43" t="s">
-        <v>174</v>
-      </c>
-      <c r="C10" s="43" t="s">
-        <v>175</v>
-      </c>
-      <c r="D10" s="43" t="s">
-        <v>176</v>
-      </c>
-      <c r="E10" s="43" t="s">
-        <v>177</v>
-      </c>
-      <c r="F10" s="43"/>
-      <c r="G10" s="43" t="s">
-        <v>165</v>
-      </c>
-      <c r="H10" s="43"/>
+      <c r="B10" s="42" t="s">
+        <v>169</v>
+      </c>
+      <c r="C10" s="42" t="s">
+        <v>170</v>
+      </c>
+      <c r="D10" s="42" t="s">
+        <v>171</v>
+      </c>
+      <c r="E10" s="42" t="s">
+        <v>172</v>
+      </c>
+      <c r="F10" s="42"/>
+      <c r="G10" s="42" t="s">
+        <v>160</v>
+      </c>
+      <c r="H10" s="42"/>
       <c r="I10" s="13"/>
-      <c r="J10" s="39"/>
-      <c r="K10" s="39"/>
+      <c r="J10" s="38"/>
+      <c r="K10" s="38"/>
     </row>
     <row r="11" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="13"/>
-      <c r="B11" s="43" t="s">
-        <v>178</v>
-      </c>
-      <c r="C11" s="43" t="s">
-        <v>179</v>
-      </c>
-      <c r="D11" s="43" t="s">
-        <v>168</v>
-      </c>
-      <c r="E11" s="43" t="s">
+      <c r="B11" s="42" t="s">
+        <v>173</v>
+      </c>
+      <c r="C11" s="42" t="s">
+        <v>174</v>
+      </c>
+      <c r="D11" s="42" t="s">
         <v>163</v>
       </c>
-      <c r="F11" s="43"/>
-      <c r="G11" s="43" t="s">
-        <v>180</v>
-      </c>
-      <c r="H11" s="43"/>
+      <c r="E11" s="42" t="s">
+        <v>158</v>
+      </c>
+      <c r="F11" s="42"/>
+      <c r="G11" s="42" t="s">
+        <v>175</v>
+      </c>
+      <c r="H11" s="42"/>
       <c r="I11" s="13"/>
-      <c r="J11" s="39"/>
-      <c r="K11" s="39"/>
+      <c r="J11" s="38"/>
+      <c r="K11" s="38"/>
     </row>
     <row r="12" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="13"/>
-      <c r="B12" s="43" t="s">
-        <v>181</v>
-      </c>
-      <c r="C12" s="43" t="s">
-        <v>182</v>
-      </c>
-      <c r="D12" s="43" t="s">
-        <v>183</v>
-      </c>
-      <c r="E12" s="43" t="s">
-        <v>163</v>
-      </c>
-      <c r="F12" s="43"/>
-      <c r="G12" s="43" t="s">
-        <v>184</v>
-      </c>
-      <c r="H12" s="43"/>
+      <c r="B12" s="42" t="s">
+        <v>176</v>
+      </c>
+      <c r="C12" s="42" t="s">
+        <v>177</v>
+      </c>
+      <c r="D12" s="42" t="s">
+        <v>178</v>
+      </c>
+      <c r="E12" s="42" t="s">
+        <v>158</v>
+      </c>
+      <c r="F12" s="42"/>
+      <c r="G12" s="42" t="s">
+        <v>179</v>
+      </c>
+      <c r="H12" s="42"/>
       <c r="I12" s="13"/>
-      <c r="J12" s="39"/>
-      <c r="K12" s="39"/>
+      <c r="J12" s="38"/>
+      <c r="K12" s="38"/>
     </row>
     <row r="13" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="13"/>
-      <c r="B13" s="43" t="s">
-        <v>185</v>
-      </c>
-      <c r="C13" s="43" t="s">
-        <v>186</v>
-      </c>
-      <c r="D13" s="43" t="s">
-        <v>183</v>
-      </c>
-      <c r="E13" s="43" t="s">
-        <v>163</v>
-      </c>
-      <c r="F13" s="43"/>
-      <c r="G13" s="43" t="s">
-        <v>184</v>
-      </c>
-      <c r="H13" s="43" t="s">
-        <v>187</v>
+      <c r="B13" s="42" t="s">
+        <v>180</v>
+      </c>
+      <c r="C13" s="42" t="s">
+        <v>181</v>
+      </c>
+      <c r="D13" s="42" t="s">
+        <v>178</v>
+      </c>
+      <c r="E13" s="42" t="s">
+        <v>158</v>
+      </c>
+      <c r="F13" s="42"/>
+      <c r="G13" s="42" t="s">
+        <v>179</v>
+      </c>
+      <c r="H13" s="42" t="s">
+        <v>182</v>
       </c>
       <c r="I13" s="13"/>
-      <c r="J13" s="39"/>
-      <c r="K13" s="39"/>
+      <c r="J13" s="38"/>
+      <c r="K13" s="38"/>
     </row>
     <row r="14" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="13"/>
@@ -8397,13 +8724,13 @@
       <c r="G14" s="13"/>
       <c r="H14" s="13"/>
       <c r="I14" s="13"/>
-      <c r="J14" s="39"/>
-      <c r="K14" s="39"/>
+      <c r="J14" s="38"/>
+      <c r="K14" s="38"/>
     </row>
     <row r="15" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="13"/>
       <c r="B15" s="84" t="s">
-        <v>188</v>
+        <v>183</v>
       </c>
       <c r="C15" s="85"/>
       <c r="D15" s="85"/>
@@ -8412,158 +8739,158 @@
       <c r="G15" s="85"/>
       <c r="H15" s="86"/>
       <c r="I15" s="13"/>
-      <c r="J15" s="41"/>
-      <c r="K15" s="39"/>
+      <c r="J15" s="40"/>
+      <c r="K15" s="38"/>
     </row>
     <row r="16" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="13"/>
-      <c r="B16" s="42" t="s">
+      <c r="B16" s="41" t="s">
+        <v>148</v>
+      </c>
+      <c r="C16" s="41" t="s">
+        <v>149</v>
+      </c>
+      <c r="D16" s="41" t="s">
+        <v>150</v>
+      </c>
+      <c r="E16" s="41" t="s">
+        <v>151</v>
+      </c>
+      <c r="F16" s="41" t="s">
+        <v>152</v>
+      </c>
+      <c r="G16" s="41" t="s">
         <v>153</v>
       </c>
-      <c r="C16" s="42" t="s">
+      <c r="H16" s="41" t="s">
         <v>154</v>
       </c>
-      <c r="D16" s="42" t="s">
-        <v>155</v>
-      </c>
-      <c r="E16" s="42" t="s">
-        <v>156</v>
-      </c>
-      <c r="F16" s="42" t="s">
-        <v>157</v>
-      </c>
-      <c r="G16" s="42" t="s">
-        <v>158</v>
-      </c>
-      <c r="H16" s="42" t="s">
-        <v>159</v>
-      </c>
       <c r="I16" s="13"/>
-      <c r="J16" s="39"/>
-      <c r="K16" s="39"/>
+      <c r="J16" s="38"/>
+      <c r="K16" s="38"/>
     </row>
     <row r="17" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="13"/>
-      <c r="B17" s="43" t="s">
+      <c r="B17" s="42" t="s">
+        <v>155</v>
+      </c>
+      <c r="C17" s="42" t="s">
+        <v>156</v>
+      </c>
+      <c r="D17" s="42" t="s">
+        <v>157</v>
+      </c>
+      <c r="E17" s="42" t="s">
+        <v>158</v>
+      </c>
+      <c r="F17" s="42" t="s">
+        <v>159</v>
+      </c>
+      <c r="G17" s="42" t="s">
         <v>160</v>
       </c>
-      <c r="C17" s="43" t="s">
-        <v>161</v>
-      </c>
-      <c r="D17" s="43" t="s">
-        <v>162</v>
-      </c>
-      <c r="E17" s="43" t="s">
-        <v>163</v>
-      </c>
-      <c r="F17" s="43" t="s">
-        <v>164</v>
-      </c>
-      <c r="G17" s="43" t="s">
-        <v>165</v>
-      </c>
-      <c r="H17" s="43" t="s">
-        <v>189</v>
+      <c r="H17" s="42" t="s">
+        <v>184</v>
       </c>
       <c r="I17" s="13"/>
-      <c r="J17" s="39"/>
-      <c r="K17" s="39"/>
+      <c r="J17" s="38"/>
+      <c r="K17" s="38"/>
     </row>
     <row r="18" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="13"/>
-      <c r="B18" s="43" t="s">
-        <v>190</v>
-      </c>
-      <c r="C18" s="43" t="s">
-        <v>191</v>
-      </c>
-      <c r="D18" s="43" t="s">
-        <v>192</v>
-      </c>
-      <c r="E18" s="43" t="s">
-        <v>163</v>
-      </c>
-      <c r="F18" s="43" t="s">
-        <v>193</v>
-      </c>
-      <c r="G18" s="43" t="s">
-        <v>165</v>
-      </c>
-      <c r="H18" s="43"/>
+      <c r="B18" s="42" t="s">
+        <v>185</v>
+      </c>
+      <c r="C18" s="42" t="s">
+        <v>186</v>
+      </c>
+      <c r="D18" s="42" t="s">
+        <v>187</v>
+      </c>
+      <c r="E18" s="42" t="s">
+        <v>158</v>
+      </c>
+      <c r="F18" s="42" t="s">
+        <v>188</v>
+      </c>
+      <c r="G18" s="42" t="s">
+        <v>160</v>
+      </c>
+      <c r="H18" s="42"/>
       <c r="I18" s="13"/>
-      <c r="J18" s="39"/>
-      <c r="K18" s="39"/>
+      <c r="J18" s="38"/>
+      <c r="K18" s="38"/>
     </row>
     <row r="19" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="13"/>
-      <c r="B19" s="43" t="s">
-        <v>194</v>
-      </c>
-      <c r="C19" s="43" t="s">
-        <v>195</v>
-      </c>
-      <c r="D19" s="43" t="s">
-        <v>176</v>
-      </c>
-      <c r="E19" s="43" t="s">
-        <v>163</v>
-      </c>
-      <c r="F19" s="43"/>
-      <c r="G19" s="43" t="s">
-        <v>165</v>
-      </c>
-      <c r="H19" s="43"/>
+      <c r="B19" s="42" t="s">
+        <v>189</v>
+      </c>
+      <c r="C19" s="42" t="s">
+        <v>190</v>
+      </c>
+      <c r="D19" s="42" t="s">
+        <v>171</v>
+      </c>
+      <c r="E19" s="42" t="s">
+        <v>158</v>
+      </c>
+      <c r="F19" s="42"/>
+      <c r="G19" s="42" t="s">
+        <v>160</v>
+      </c>
+      <c r="H19" s="42"/>
       <c r="I19" s="13"/>
-      <c r="J19" s="39"/>
-      <c r="K19" s="39"/>
+      <c r="J19" s="38"/>
+      <c r="K19" s="38"/>
     </row>
     <row r="20" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="13"/>
-      <c r="B20" s="43" t="s">
-        <v>181</v>
-      </c>
-      <c r="C20" s="43" t="s">
-        <v>182</v>
-      </c>
-      <c r="D20" s="43" t="s">
-        <v>183</v>
-      </c>
-      <c r="E20" s="43" t="s">
-        <v>163</v>
-      </c>
-      <c r="F20" s="43"/>
-      <c r="G20" s="43" t="s">
-        <v>184</v>
-      </c>
-      <c r="H20" s="43"/>
+      <c r="B20" s="42" t="s">
+        <v>176</v>
+      </c>
+      <c r="C20" s="42" t="s">
+        <v>177</v>
+      </c>
+      <c r="D20" s="42" t="s">
+        <v>178</v>
+      </c>
+      <c r="E20" s="42" t="s">
+        <v>158</v>
+      </c>
+      <c r="F20" s="42"/>
+      <c r="G20" s="42" t="s">
+        <v>179</v>
+      </c>
+      <c r="H20" s="42"/>
       <c r="I20" s="13"/>
-      <c r="J20" s="39"/>
-      <c r="K20" s="39"/>
+      <c r="J20" s="38"/>
+      <c r="K20" s="38"/>
     </row>
     <row r="21" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="13"/>
-      <c r="B21" s="43" t="s">
-        <v>185</v>
-      </c>
-      <c r="C21" s="43" t="s">
-        <v>186</v>
-      </c>
-      <c r="D21" s="43" t="s">
-        <v>183</v>
-      </c>
-      <c r="E21" s="43" t="s">
-        <v>163</v>
-      </c>
-      <c r="F21" s="43"/>
-      <c r="G21" s="43" t="s">
-        <v>184</v>
-      </c>
-      <c r="H21" s="43" t="s">
-        <v>187</v>
+      <c r="B21" s="42" t="s">
+        <v>180</v>
+      </c>
+      <c r="C21" s="42" t="s">
+        <v>181</v>
+      </c>
+      <c r="D21" s="42" t="s">
+        <v>178</v>
+      </c>
+      <c r="E21" s="42" t="s">
+        <v>158</v>
+      </c>
+      <c r="F21" s="42"/>
+      <c r="G21" s="42" t="s">
+        <v>179</v>
+      </c>
+      <c r="H21" s="42" t="s">
+        <v>182</v>
       </c>
       <c r="I21" s="13"/>
-      <c r="J21" s="39"/>
-      <c r="K21" s="39"/>
+      <c r="J21" s="38"/>
+      <c r="K21" s="38"/>
     </row>
     <row r="22" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="13"/>
@@ -8575,13 +8902,13 @@
       <c r="G22" s="13"/>
       <c r="H22" s="13"/>
       <c r="I22" s="13"/>
-      <c r="J22" s="39"/>
-      <c r="K22" s="39"/>
+      <c r="J22" s="38"/>
+      <c r="K22" s="38"/>
     </row>
     <row r="23" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="13"/>
       <c r="B23" s="84" t="s">
-        <v>196</v>
+        <v>191</v>
       </c>
       <c r="C23" s="85"/>
       <c r="D23" s="85"/>
@@ -8590,154 +8917,154 @@
       <c r="G23" s="85"/>
       <c r="H23" s="86"/>
       <c r="I23" s="13"/>
-      <c r="J23" s="39"/>
-      <c r="K23" s="39"/>
+      <c r="J23" s="38"/>
+      <c r="K23" s="38"/>
     </row>
     <row r="24" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="13"/>
-      <c r="B24" s="42" t="s">
+      <c r="B24" s="41" t="s">
+        <v>148</v>
+      </c>
+      <c r="C24" s="41" t="s">
+        <v>149</v>
+      </c>
+      <c r="D24" s="41" t="s">
+        <v>150</v>
+      </c>
+      <c r="E24" s="41" t="s">
+        <v>151</v>
+      </c>
+      <c r="F24" s="41" t="s">
+        <v>152</v>
+      </c>
+      <c r="G24" s="41" t="s">
         <v>153</v>
       </c>
-      <c r="C24" s="42" t="s">
+      <c r="H24" s="41" t="s">
         <v>154</v>
       </c>
-      <c r="D24" s="42" t="s">
-        <v>155</v>
-      </c>
-      <c r="E24" s="42" t="s">
-        <v>156</v>
-      </c>
-      <c r="F24" s="42" t="s">
-        <v>157</v>
-      </c>
-      <c r="G24" s="42" t="s">
-        <v>158</v>
-      </c>
-      <c r="H24" s="42" t="s">
-        <v>159</v>
-      </c>
       <c r="I24" s="13"/>
-      <c r="J24" s="41"/>
-      <c r="K24" s="39"/>
+      <c r="J24" s="40"/>
+      <c r="K24" s="38"/>
     </row>
     <row r="25" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="13"/>
-      <c r="B25" s="43" t="s">
+      <c r="B25" s="42" t="s">
+        <v>155</v>
+      </c>
+      <c r="C25" s="42" t="s">
+        <v>156</v>
+      </c>
+      <c r="D25" s="42" t="s">
+        <v>157</v>
+      </c>
+      <c r="E25" s="42" t="s">
+        <v>158</v>
+      </c>
+      <c r="F25" s="42" t="s">
+        <v>159</v>
+      </c>
+      <c r="G25" s="42" t="s">
         <v>160</v>
       </c>
-      <c r="C25" s="43" t="s">
-        <v>161</v>
-      </c>
-      <c r="D25" s="43" t="s">
-        <v>162</v>
-      </c>
-      <c r="E25" s="43" t="s">
-        <v>163</v>
-      </c>
-      <c r="F25" s="43" t="s">
-        <v>164</v>
-      </c>
-      <c r="G25" s="43" t="s">
-        <v>165</v>
-      </c>
-      <c r="H25" s="43"/>
+      <c r="H25" s="42"/>
       <c r="I25" s="13"/>
-      <c r="J25" s="39"/>
-      <c r="K25" s="39"/>
+      <c r="J25" s="38"/>
+      <c r="K25" s="38"/>
     </row>
     <row r="26" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="13"/>
-      <c r="B26" s="43" t="s">
-        <v>197</v>
-      </c>
-      <c r="C26" s="43" t="s">
-        <v>198</v>
-      </c>
-      <c r="D26" s="43" t="s">
-        <v>162</v>
-      </c>
-      <c r="E26" s="43" t="s">
-        <v>163</v>
-      </c>
-      <c r="F26" s="43"/>
-      <c r="G26" s="43" t="s">
-        <v>165</v>
-      </c>
-      <c r="H26" s="43"/>
+      <c r="B26" s="42" t="s">
+        <v>192</v>
+      </c>
+      <c r="C26" s="42" t="s">
+        <v>193</v>
+      </c>
+      <c r="D26" s="42" t="s">
+        <v>157</v>
+      </c>
+      <c r="E26" s="42" t="s">
+        <v>158</v>
+      </c>
+      <c r="F26" s="42"/>
+      <c r="G26" s="42" t="s">
+        <v>160</v>
+      </c>
+      <c r="H26" s="42"/>
       <c r="I26" s="13"/>
-      <c r="J26" s="39"/>
-      <c r="K26" s="39"/>
+      <c r="J26" s="38"/>
+      <c r="K26" s="38"/>
     </row>
     <row r="27" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="13"/>
-      <c r="B27" s="43" t="s">
-        <v>199</v>
-      </c>
-      <c r="C27" s="43" t="s">
-        <v>200</v>
-      </c>
-      <c r="D27" s="43" t="s">
-        <v>162</v>
-      </c>
-      <c r="E27" s="43" t="s">
-        <v>163</v>
-      </c>
-      <c r="F27" s="43"/>
-      <c r="G27" s="43" t="s">
-        <v>165</v>
-      </c>
-      <c r="H27" s="43"/>
+      <c r="B27" s="42" t="s">
+        <v>194</v>
+      </c>
+      <c r="C27" s="42" t="s">
+        <v>195</v>
+      </c>
+      <c r="D27" s="42" t="s">
+        <v>157</v>
+      </c>
+      <c r="E27" s="42" t="s">
+        <v>158</v>
+      </c>
+      <c r="F27" s="42"/>
+      <c r="G27" s="42" t="s">
+        <v>160</v>
+      </c>
+      <c r="H27" s="42"/>
       <c r="I27" s="13"/>
-      <c r="J27" s="39"/>
-      <c r="K27" s="39"/>
+      <c r="J27" s="38"/>
+      <c r="K27" s="38"/>
     </row>
     <row r="28" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="13"/>
-      <c r="B28" s="43" t="s">
-        <v>181</v>
-      </c>
-      <c r="C28" s="43" t="s">
-        <v>182</v>
-      </c>
-      <c r="D28" s="43" t="s">
-        <v>183</v>
-      </c>
-      <c r="E28" s="43" t="s">
-        <v>163</v>
-      </c>
-      <c r="F28" s="43"/>
-      <c r="G28" s="43" t="s">
-        <v>184</v>
-      </c>
-      <c r="H28" s="43"/>
+      <c r="B28" s="42" t="s">
+        <v>176</v>
+      </c>
+      <c r="C28" s="42" t="s">
+        <v>177</v>
+      </c>
+      <c r="D28" s="42" t="s">
+        <v>178</v>
+      </c>
+      <c r="E28" s="42" t="s">
+        <v>158</v>
+      </c>
+      <c r="F28" s="42"/>
+      <c r="G28" s="42" t="s">
+        <v>179</v>
+      </c>
+      <c r="H28" s="42"/>
       <c r="I28" s="13"/>
-      <c r="J28" s="39"/>
-      <c r="K28" s="39"/>
+      <c r="J28" s="38"/>
+      <c r="K28" s="38"/>
     </row>
     <row r="29" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="13"/>
-      <c r="B29" s="43" t="s">
-        <v>185</v>
-      </c>
-      <c r="C29" s="43" t="s">
-        <v>186</v>
-      </c>
-      <c r="D29" s="43" t="s">
-        <v>183</v>
-      </c>
-      <c r="E29" s="43" t="s">
-        <v>163</v>
-      </c>
-      <c r="F29" s="43"/>
-      <c r="G29" s="43" t="s">
-        <v>184</v>
-      </c>
-      <c r="H29" s="43" t="s">
-        <v>187</v>
+      <c r="B29" s="42" t="s">
+        <v>180</v>
+      </c>
+      <c r="C29" s="42" t="s">
+        <v>181</v>
+      </c>
+      <c r="D29" s="42" t="s">
+        <v>178</v>
+      </c>
+      <c r="E29" s="42" t="s">
+        <v>158</v>
+      </c>
+      <c r="F29" s="42"/>
+      <c r="G29" s="42" t="s">
+        <v>179</v>
+      </c>
+      <c r="H29" s="42" t="s">
+        <v>182</v>
       </c>
       <c r="I29" s="13"/>
-      <c r="J29" s="39"/>
-      <c r="K29" s="39"/>
+      <c r="J29" s="38"/>
+      <c r="K29" s="38"/>
     </row>
     <row r="30" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="13"/>
@@ -8752,7 +9079,7 @@
     </row>
     <row r="31" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="83" t="s">
-        <v>201</v>
+        <v>196</v>
       </c>
       <c r="B31" s="82"/>
       <c r="C31" s="82"/>
@@ -9740,7 +10067,7 @@
     <mergeCell ref="B23:H23"/>
     <mergeCell ref="A31:I31"/>
   </mergeCells>
-  <phoneticPr fontId="24"/>
+  <phoneticPr fontId="21"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
 </worksheet>
@@ -9761,92 +10088,92 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="25" t="s">
+      <c r="A1" s="24" t="s">
+        <v>197</v>
+      </c>
+      <c r="B1" s="24"/>
+      <c r="C1" s="13"/>
+    </row>
+    <row r="2" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2" s="24"/>
+      <c r="B2" s="24"/>
+      <c r="C2" s="13"/>
+    </row>
+    <row r="3" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B3" s="26" t="s">
+        <v>198</v>
+      </c>
+      <c r="C3" s="26" t="s">
+        <v>148</v>
+      </c>
+      <c r="D3" s="43" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B4" s="28" t="s">
+        <v>200</v>
+      </c>
+      <c r="C4" s="28" t="s">
+        <v>201</v>
+      </c>
+      <c r="D4" s="44" t="s">
         <v>202</v>
       </c>
-      <c r="B1" s="25"/>
-      <c r="C1" s="13"/>
-    </row>
-    <row r="2" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="25"/>
-      <c r="B2" s="25"/>
-      <c r="C2" s="13"/>
-    </row>
-    <row r="3" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B3" s="27" t="s">
+    </row>
+    <row r="5" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B5" s="28" t="s">
         <v>203</v>
       </c>
-      <c r="C3" s="27" t="s">
-        <v>153</v>
-      </c>
-      <c r="D3" s="44" t="s">
+      <c r="C5" s="28" t="s">
         <v>204</v>
       </c>
-    </row>
-    <row r="4" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B4" s="29" t="s">
+      <c r="D5" s="44" t="s">
         <v>205</v>
       </c>
-      <c r="C4" s="29" t="s">
+    </row>
+    <row r="6" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B6" s="28" t="s">
+        <v>203</v>
+      </c>
+      <c r="C6" s="28" t="s">
         <v>206</v>
       </c>
-      <c r="D4" s="45" t="s">
+      <c r="D6" s="44" t="s">
         <v>207</v>
       </c>
     </row>
-    <row r="5" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B5" s="29" t="s">
+    <row r="7" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B7" s="28" t="s">
         <v>208</v>
       </c>
-      <c r="C5" s="29" t="s">
+      <c r="C7" s="28" t="s">
         <v>209</v>
       </c>
-      <c r="D5" s="45" t="s">
+      <c r="D7" s="44" t="s">
         <v>210</v>
       </c>
     </row>
-    <row r="6" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B6" s="29" t="s">
-        <v>208</v>
-      </c>
-      <c r="C6" s="29" t="s">
+    <row r="8" spans="1:4" ht="39" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B8" s="28" t="s">
         <v>211</v>
       </c>
-      <c r="D6" s="45" t="s">
+      <c r="C8" s="28" t="s">
         <v>212</v>
       </c>
-    </row>
-    <row r="7" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B7" s="29" t="s">
+      <c r="D8" s="44" t="s">
         <v>213</v>
       </c>
-      <c r="C7" s="29" t="s">
+    </row>
+    <row r="9" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B9" s="28" t="s">
         <v>214</v>
       </c>
-      <c r="D7" s="45" t="s">
+      <c r="C9" s="28" t="s">
         <v>215</v>
       </c>
-    </row>
-    <row r="8" spans="1:4" ht="39" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B8" s="29" t="s">
+      <c r="D9" s="44" t="s">
         <v>216</v>
-      </c>
-      <c r="C8" s="29" t="s">
-        <v>217</v>
-      </c>
-      <c r="D8" s="45" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B9" s="29" t="s">
-        <v>219</v>
-      </c>
-      <c r="C9" s="29" t="s">
-        <v>220</v>
-      </c>
-      <c r="D9" s="45" t="s">
-        <v>221</v>
       </c>
     </row>
     <row r="10" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
@@ -10841,7 +11168,7 @@
     <row r="999" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="1000" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
   </sheetData>
-  <phoneticPr fontId="24"/>
+  <phoneticPr fontId="21"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -10861,677 +11188,677 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="25"/>
+      <c r="A1" s="24"/>
     </row>
     <row r="2" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="25"/>
+      <c r="A2" s="24"/>
       <c r="B2" s="87" t="s">
-        <v>222</v>
+        <v>217</v>
       </c>
       <c r="C2" s="88"/>
       <c r="D2" s="89"/>
-      <c r="E2" s="46"/>
-      <c r="F2" s="47"/>
-      <c r="G2" s="47"/>
-      <c r="H2" s="47"/>
-      <c r="I2" s="47"/>
-      <c r="J2" s="47"/>
-      <c r="K2" s="47"/>
+      <c r="E2" s="45"/>
+      <c r="F2" s="46"/>
+      <c r="G2" s="46"/>
+      <c r="H2" s="46"/>
+      <c r="I2" s="46"/>
+      <c r="J2" s="46"/>
+      <c r="K2" s="46"/>
     </row>
     <row r="3" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="25"/>
+      <c r="A3" s="24"/>
       <c r="B3" s="90" t="s">
-        <v>223</v>
+        <v>218</v>
       </c>
       <c r="C3" s="85"/>
       <c r="D3" s="85"/>
-      <c r="E3" s="48"/>
-      <c r="F3" s="49"/>
-      <c r="G3" s="49"/>
-      <c r="H3" s="49"/>
-      <c r="I3" s="49"/>
-      <c r="J3" s="49"/>
-      <c r="K3" s="49"/>
+      <c r="E3" s="47"/>
+      <c r="F3" s="48"/>
+      <c r="G3" s="48"/>
+      <c r="H3" s="48"/>
+      <c r="I3" s="48"/>
+      <c r="J3" s="48"/>
+      <c r="K3" s="48"/>
     </row>
     <row r="4" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="25"/>
+      <c r="A4" s="24"/>
       <c r="B4" s="90" t="s">
-        <v>224</v>
+        <v>219</v>
       </c>
       <c r="C4" s="85"/>
       <c r="D4" s="85"/>
-      <c r="E4" s="48"/>
-      <c r="F4" s="49"/>
-      <c r="G4" s="49"/>
-      <c r="H4" s="49"/>
-      <c r="I4" s="49"/>
-      <c r="J4" s="49"/>
-      <c r="K4" s="49"/>
+      <c r="E4" s="47"/>
+      <c r="F4" s="48"/>
+      <c r="G4" s="48"/>
+      <c r="H4" s="48"/>
+      <c r="I4" s="48"/>
+      <c r="J4" s="48"/>
+      <c r="K4" s="48"/>
     </row>
     <row r="5" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="25"/>
+      <c r="A5" s="24"/>
       <c r="B5" s="90" t="s">
-        <v>225</v>
+        <v>220</v>
       </c>
       <c r="C5" s="85"/>
       <c r="D5" s="85"/>
-      <c r="E5" s="48"/>
-      <c r="F5" s="49"/>
-      <c r="G5" s="49"/>
-      <c r="H5" s="49"/>
-      <c r="I5" s="49"/>
-      <c r="J5" s="49"/>
-      <c r="K5" s="49"/>
+      <c r="E5" s="47"/>
+      <c r="F5" s="48"/>
+      <c r="G5" s="48"/>
+      <c r="H5" s="48"/>
+      <c r="I5" s="48"/>
+      <c r="J5" s="48"/>
+      <c r="K5" s="48"/>
     </row>
     <row r="6" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="25"/>
+      <c r="A6" s="24"/>
     </row>
     <row r="7" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B7" s="50" t="s">
+      <c r="B7" s="49" t="s">
+        <v>221</v>
+      </c>
+      <c r="C7" s="50"/>
+      <c r="D7" s="24"/>
+    </row>
+    <row r="8" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B8" s="49" t="s">
+        <v>222</v>
+      </c>
+      <c r="C8" s="50"/>
+      <c r="D8" s="24"/>
+    </row>
+    <row r="9" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B9" s="51"/>
+      <c r="C9" s="13"/>
+      <c r="D9" s="24"/>
+    </row>
+    <row r="10" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B10" s="52" t="s">
+        <v>223</v>
+      </c>
+      <c r="C10" s="53"/>
+      <c r="D10" s="24"/>
+    </row>
+    <row r="11" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B11" s="54" t="s">
+        <v>224</v>
+      </c>
+      <c r="C11" s="55"/>
+      <c r="D11" s="24"/>
+    </row>
+    <row r="12" spans="1:11" ht="53.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B12" s="56" t="s">
+        <v>225</v>
+      </c>
+      <c r="C12" s="57" t="b">
+        <v>0</v>
+      </c>
+      <c r="D12" s="24"/>
+    </row>
+    <row r="13" spans="1:11" ht="53.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B13" s="56" t="s">
         <v>226</v>
       </c>
-      <c r="C7" s="51"/>
-      <c r="D7" s="25"/>
-    </row>
-    <row r="8" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B8" s="50" t="s">
+      <c r="C13" s="58" t="b">
+        <v>0</v>
+      </c>
+      <c r="D13" s="24"/>
+    </row>
+    <row r="14" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B14" s="54" t="s">
         <v>227</v>
       </c>
-      <c r="C8" s="51"/>
-      <c r="D8" s="25"/>
-    </row>
-    <row r="9" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B9" s="52"/>
-      <c r="C9" s="13"/>
-      <c r="D9" s="25"/>
-    </row>
-    <row r="10" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B10" s="53" t="s">
+      <c r="C14" s="59"/>
+      <c r="D14" s="60"/>
+    </row>
+    <row r="15" spans="1:11" ht="35.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B15" s="56" t="s">
         <v>228</v>
       </c>
-      <c r="C10" s="54"/>
-      <c r="D10" s="25"/>
-    </row>
-    <row r="11" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B11" s="55" t="s">
+      <c r="C15" s="61" t="b">
+        <v>0</v>
+      </c>
+      <c r="D15" s="24"/>
+    </row>
+    <row r="16" spans="1:11" ht="35.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B16" s="56" t="s">
         <v>229</v>
       </c>
-      <c r="C11" s="56"/>
-      <c r="D11" s="25"/>
-    </row>
-    <row r="12" spans="1:11" ht="53.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B12" s="57" t="s">
+      <c r="C16" s="57" t="b">
+        <v>0</v>
+      </c>
+      <c r="D16" s="24"/>
+    </row>
+    <row r="17" spans="2:4" ht="42" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B17" s="56" t="s">
         <v>230</v>
       </c>
-      <c r="C12" s="58" t="b">
+      <c r="C17" s="57" t="b">
         <v>0</v>
       </c>
-      <c r="D12" s="25"/>
-    </row>
-    <row r="13" spans="1:11" ht="53.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B13" s="57" t="s">
+      <c r="D17" s="24"/>
+    </row>
+    <row r="18" spans="2:4" ht="33" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B18" s="56" t="s">
         <v>231</v>
       </c>
-      <c r="C13" s="59" t="b">
+      <c r="C18" s="57" t="b">
         <v>0</v>
       </c>
-      <c r="D13" s="25"/>
-    </row>
-    <row r="14" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B14" s="55" t="s">
+      <c r="D18" s="24"/>
+    </row>
+    <row r="19" spans="2:4" ht="43.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B19" s="56" t="s">
         <v>232</v>
       </c>
-      <c r="C14" s="60"/>
-      <c r="D14" s="61"/>
-    </row>
-    <row r="15" spans="1:11" ht="35.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B15" s="57" t="s">
+      <c r="C19" s="57" t="b">
+        <v>0</v>
+      </c>
+      <c r="D19" s="24"/>
+    </row>
+    <row r="20" spans="2:4" ht="35.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B20" s="56" t="s">
         <v>233</v>
       </c>
-      <c r="C15" s="62" t="b">
+      <c r="C20" s="57" t="b">
         <v>0</v>
       </c>
-      <c r="D15" s="25"/>
-    </row>
-    <row r="16" spans="1:11" ht="35.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B16" s="57" t="s">
+    </row>
+    <row r="21" spans="2:4" ht="45" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B21" s="56" t="s">
         <v>234</v>
       </c>
-      <c r="C16" s="58" t="b">
+      <c r="C21" s="57" t="b">
         <v>0</v>
       </c>
-      <c r="D16" s="25"/>
-    </row>
-    <row r="17" spans="2:4" ht="42" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B17" s="57" t="s">
+    </row>
+    <row r="22" spans="2:4" ht="35.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B22" s="56" t="s">
         <v>235</v>
       </c>
-      <c r="C17" s="58" t="b">
+      <c r="C22" s="57" t="b">
         <v>0</v>
       </c>
-      <c r="D17" s="25"/>
-    </row>
-    <row r="18" spans="2:4" ht="33" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B18" s="57" t="s">
+    </row>
+    <row r="23" spans="2:4" ht="35.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B23" s="56" t="s">
         <v>236</v>
       </c>
-      <c r="C18" s="58" t="b">
+      <c r="C23" s="57" t="b">
         <v>0</v>
       </c>
-      <c r="D18" s="25"/>
-    </row>
-    <row r="19" spans="2:4" ht="43.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B19" s="57" t="s">
+    </row>
+    <row r="24" spans="2:4" ht="35.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B24" s="56" t="s">
         <v>237</v>
       </c>
-      <c r="C19" s="58" t="b">
+      <c r="C24" s="57" t="b">
         <v>0</v>
       </c>
-      <c r="D19" s="25"/>
-    </row>
-    <row r="20" spans="2:4" ht="35.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B20" s="57" t="s">
+    </row>
+    <row r="25" spans="2:4" ht="35.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B25" s="56" t="s">
         <v>238</v>
       </c>
-      <c r="C20" s="58" t="b">
+      <c r="C25" s="57" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="2:4" ht="45" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B21" s="57" t="s">
+    <row r="26" spans="2:4" ht="35.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B26" s="56" t="s">
         <v>239</v>
       </c>
-      <c r="C21" s="58" t="b">
+      <c r="C26" s="57" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="2:4" ht="35.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B22" s="57" t="s">
+    <row r="27" spans="2:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B27" s="44"/>
+      <c r="C27" s="53"/>
+    </row>
+    <row r="28" spans="2:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B28" s="54" t="s">
         <v>240</v>
       </c>
-      <c r="C22" s="58" t="b">
+      <c r="C28" s="55"/>
+    </row>
+    <row r="29" spans="2:4" ht="25.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B29" s="56" t="s">
+        <v>241</v>
+      </c>
+      <c r="C29" s="61" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="2:4" ht="35.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B23" s="57" t="s">
-        <v>241</v>
-      </c>
-      <c r="C23" s="58" t="b">
+    <row r="30" spans="2:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B30" s="56" t="s">
+        <v>242</v>
+      </c>
+      <c r="C30" s="57" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="2:4" ht="35.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B24" s="57" t="s">
-        <v>242</v>
-      </c>
-      <c r="C24" s="58" t="b">
+    <row r="31" spans="2:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B31" s="56" t="s">
+        <v>243</v>
+      </c>
+      <c r="C31" s="57" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="2:4" ht="35.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B25" s="57" t="s">
-        <v>243</v>
-      </c>
-      <c r="C25" s="58" t="b">
+    <row r="32" spans="2:4" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B32" s="56" t="s">
+        <v>244</v>
+      </c>
+      <c r="C32" s="57" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="2:4" ht="35.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B26" s="57" t="s">
-        <v>244</v>
-      </c>
-      <c r="C26" s="58" t="b">
+    <row r="33" spans="2:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B33" s="56" t="s">
+        <v>245</v>
+      </c>
+      <c r="C33" s="57" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="2:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B27" s="45"/>
-      <c r="C27" s="54"/>
-    </row>
-    <row r="28" spans="2:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B28" s="55" t="s">
-        <v>245</v>
-      </c>
-      <c r="C28" s="56"/>
-    </row>
-    <row r="29" spans="2:4" ht="25.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B29" s="57" t="s">
+    <row r="34" spans="2:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B34" s="56" t="s">
         <v>246</v>
       </c>
-      <c r="C29" s="62" t="b">
+      <c r="C34" s="57" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="2:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B30" s="57" t="s">
+    <row r="35" spans="2:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B35" s="44"/>
+      <c r="C35" s="53"/>
+    </row>
+    <row r="36" spans="2:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B36" s="54" t="s">
         <v>247</v>
       </c>
-      <c r="C30" s="58" t="b">
+      <c r="C36" s="55"/>
+    </row>
+    <row r="37" spans="2:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B37" s="56" t="s">
+        <v>248</v>
+      </c>
+      <c r="C37" s="61" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="2:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B31" s="57" t="s">
-        <v>248</v>
-      </c>
-      <c r="C31" s="58" t="b">
+    <row r="38" spans="2:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B38" s="56" t="s">
+        <v>249</v>
+      </c>
+      <c r="C38" s="57" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="2:4" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B32" s="57" t="s">
+    <row r="39" spans="2:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B39" s="56" t="s">
+        <v>250</v>
+      </c>
+      <c r="C39" s="57" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40" spans="2:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B40" s="56" t="s">
+        <v>251</v>
+      </c>
+      <c r="C40" s="57" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41" spans="2:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B41" s="56" t="s">
+        <v>252</v>
+      </c>
+      <c r="C41" s="57" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" spans="2:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B42" s="56" t="s">
+        <v>253</v>
+      </c>
+      <c r="C42" s="57" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B43" s="56" t="s">
+        <v>254</v>
+      </c>
+      <c r="C43" s="57" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B44" s="56" t="s">
+        <v>255</v>
+      </c>
+      <c r="C44" s="57" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:3" ht="27" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B45" s="56" t="s">
+        <v>256</v>
+      </c>
+      <c r="C45" s="57" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="2:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B46" s="56" t="s">
+        <v>257</v>
+      </c>
+      <c r="C46" s="57" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="2:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B47" s="56" t="s">
+        <v>258</v>
+      </c>
+      <c r="C47" s="57" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B48" s="56" t="s">
+        <v>259</v>
+      </c>
+      <c r="C48" s="57" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="2:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B49" s="56" t="s">
+        <v>260</v>
+      </c>
+      <c r="C49" s="57" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="2:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B50" s="56" t="s">
+        <v>261</v>
+      </c>
+      <c r="C50" s="57" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="2:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B51" s="56" t="s">
+        <v>262</v>
+      </c>
+      <c r="C51" s="57" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="2:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B52" s="56" t="s">
+        <v>263</v>
+      </c>
+      <c r="C52" s="57" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="2:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B53" s="56" t="s">
+        <v>264</v>
+      </c>
+      <c r="C53" s="57" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="2:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B54" s="56" t="s">
+        <v>265</v>
+      </c>
+      <c r="C54" s="57" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55" spans="2:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B55" s="56" t="s">
+        <v>266</v>
+      </c>
+      <c r="C55" s="57" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56" spans="2:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B56" s="44"/>
+      <c r="C56" s="53"/>
+    </row>
+    <row r="57" spans="2:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B57" s="54" t="s">
+        <v>267</v>
+      </c>
+      <c r="C57" s="55"/>
+    </row>
+    <row r="58" spans="2:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B58" s="56" t="s">
         <v>249</v>
       </c>
-      <c r="C32" s="58" t="b">
+      <c r="C58" s="61" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="2:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B33" s="57" t="s">
-        <v>250</v>
-      </c>
-      <c r="C33" s="58" t="b">
+    <row r="59" spans="2:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B59" s="56" t="s">
+        <v>268</v>
+      </c>
+      <c r="C59" s="57" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="2:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B34" s="57" t="s">
-        <v>251</v>
-      </c>
-      <c r="C34" s="58" t="b">
+    <row r="60" spans="2:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B60" s="56" t="s">
+        <v>269</v>
+      </c>
+      <c r="C60" s="57" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="2:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B35" s="45"/>
-      <c r="C35" s="54"/>
-    </row>
-    <row r="36" spans="2:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B36" s="55" t="s">
-        <v>252</v>
-      </c>
-      <c r="C36" s="56"/>
-    </row>
-    <row r="37" spans="2:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B37" s="57" t="s">
-        <v>253</v>
-      </c>
-      <c r="C37" s="62" t="b">
+    <row r="61" spans="2:3" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B61" s="56" t="s">
+        <v>270</v>
+      </c>
+      <c r="C61" s="57" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="2:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B38" s="57" t="s">
-        <v>254</v>
-      </c>
-      <c r="C38" s="58" t="b">
+    <row r="62" spans="2:3" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B62" s="56" t="s">
+        <v>271</v>
+      </c>
+      <c r="C62" s="57" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="2:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B39" s="57" t="s">
-        <v>255</v>
-      </c>
-      <c r="C39" s="58" t="b">
+    <row r="63" spans="2:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B63" s="56" t="s">
+        <v>272</v>
+      </c>
+      <c r="C63" s="57" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="2:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B40" s="57" t="s">
-        <v>256</v>
-      </c>
-      <c r="C40" s="58" t="b">
+    <row r="64" spans="2:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B64" s="56" t="s">
+        <v>273</v>
+      </c>
+      <c r="C64" s="57" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="2:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B41" s="57" t="s">
-        <v>257</v>
-      </c>
-      <c r="C41" s="58" t="b">
+    <row r="65" spans="2:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B65" s="56" t="s">
+        <v>274</v>
+      </c>
+      <c r="C65" s="57" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="2:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B42" s="57" t="s">
-        <v>258</v>
-      </c>
-      <c r="C42" s="58" t="b">
+    <row r="66" spans="2:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B66" s="56" t="s">
+        <v>275</v>
+      </c>
+      <c r="C66" s="57" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="43" spans="2:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B43" s="57" t="s">
-        <v>259</v>
-      </c>
-      <c r="C43" s="58" t="b">
+    <row r="67" spans="2:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B67" s="56" t="s">
+        <v>276</v>
+      </c>
+      <c r="C67" s="57" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="2:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B44" s="57" t="s">
-        <v>260</v>
-      </c>
-      <c r="C44" s="58" t="b">
+    <row r="68" spans="2:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B68" s="44"/>
+      <c r="C68" s="53"/>
+    </row>
+    <row r="69" spans="2:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B69" s="54" t="s">
+        <v>214</v>
+      </c>
+      <c r="C69" s="55"/>
+    </row>
+    <row r="70" spans="2:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B70" s="56" t="s">
+        <v>277</v>
+      </c>
+      <c r="C70" s="61" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="2:3" ht="27" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B45" s="57" t="s">
-        <v>261</v>
-      </c>
-      <c r="C45" s="58" t="b">
+    <row r="71" spans="2:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B71" s="44"/>
+      <c r="C71" s="53"/>
+    </row>
+    <row r="72" spans="2:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B72" s="54" t="s">
+        <v>278</v>
+      </c>
+      <c r="C72" s="55"/>
+    </row>
+    <row r="73" spans="2:3" ht="26.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B73" s="56" t="s">
+        <v>279</v>
+      </c>
+      <c r="C73" s="61" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="2:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B46" s="57" t="s">
-        <v>262</v>
-      </c>
-      <c r="C46" s="58" t="b">
+    <row r="74" spans="2:3" ht="26.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B74" s="56" t="s">
+        <v>280</v>
+      </c>
+      <c r="C74" s="57" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="2:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B47" s="57" t="s">
-        <v>263</v>
-      </c>
-      <c r="C47" s="58" t="b">
+    <row r="75" spans="2:3" ht="26.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B75" s="56" t="s">
+        <v>281</v>
+      </c>
+      <c r="C75" s="57" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="2:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B48" s="57" t="s">
-        <v>264</v>
-      </c>
-      <c r="C48" s="58" t="b">
+    <row r="76" spans="2:3" ht="26.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B76" s="56" t="s">
+        <v>282</v>
+      </c>
+      <c r="C76" s="57" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="2:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B49" s="57" t="s">
-        <v>265</v>
-      </c>
-      <c r="C49" s="58" t="b">
+    <row r="77" spans="2:3" ht="26.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B77" s="56" t="s">
+        <v>283</v>
+      </c>
+      <c r="C77" s="57" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="2:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B50" s="57" t="s">
-        <v>266</v>
-      </c>
-      <c r="C50" s="58" t="b">
+    <row r="78" spans="2:3" ht="33.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B78" s="56" t="s">
+        <v>284</v>
+      </c>
+      <c r="C78" s="57" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="51" spans="2:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B51" s="57" t="s">
-        <v>267</v>
-      </c>
-      <c r="C51" s="58" t="b">
+    <row r="79" spans="2:3" ht="26.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B79" s="56" t="s">
+        <v>285</v>
+      </c>
+      <c r="C79" s="57" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="52" spans="2:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B52" s="57" t="s">
-        <v>268</v>
-      </c>
-      <c r="C52" s="58" t="b">
+    <row r="80" spans="2:3" ht="26.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B80" s="56" t="s">
+        <v>286</v>
+      </c>
+      <c r="C80" s="57" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="53" spans="2:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B53" s="57" t="s">
-        <v>269</v>
-      </c>
-      <c r="C53" s="58" t="b">
+    <row r="81" spans="2:3" ht="26.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B81" s="56" t="s">
+        <v>287</v>
+      </c>
+      <c r="C81" s="57" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="54" spans="2:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B54" s="57" t="s">
-        <v>270</v>
-      </c>
-      <c r="C54" s="58" t="b">
+    <row r="82" spans="2:3" ht="26.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B82" s="56" t="s">
+        <v>288</v>
+      </c>
+      <c r="C82" s="57" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="55" spans="2:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B55" s="57" t="s">
-        <v>271</v>
-      </c>
-      <c r="C55" s="58" t="b">
+    <row r="83" spans="2:3" ht="26.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B83" s="56" t="s">
+        <v>289</v>
+      </c>
+      <c r="C83" s="57" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="56" spans="2:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B56" s="45"/>
-      <c r="C56" s="54"/>
-    </row>
-    <row r="57" spans="2:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B57" s="55" t="s">
-        <v>272</v>
-      </c>
-      <c r="C57" s="56"/>
-    </row>
-    <row r="58" spans="2:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B58" s="57" t="s">
-        <v>254</v>
-      </c>
-      <c r="C58" s="62" t="b">
+    <row r="84" spans="2:3" ht="26.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B84" s="56" t="s">
+        <v>290</v>
+      </c>
+      <c r="C84" s="57" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="59" spans="2:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B59" s="57" t="s">
-        <v>273</v>
-      </c>
-      <c r="C59" s="58" t="b">
+    <row r="85" spans="2:3" ht="26.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B85" s="56" t="s">
+        <v>291</v>
+      </c>
+      <c r="C85" s="57" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="60" spans="2:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B60" s="57" t="s">
-        <v>274</v>
-      </c>
-      <c r="C60" s="58" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="61" spans="2:3" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B61" s="57" t="s">
-        <v>275</v>
-      </c>
-      <c r="C61" s="58" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="62" spans="2:3" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B62" s="57" t="s">
-        <v>276</v>
-      </c>
-      <c r="C62" s="58" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="63" spans="2:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B63" s="57" t="s">
-        <v>277</v>
-      </c>
-      <c r="C63" s="58" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="64" spans="2:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B64" s="57" t="s">
-        <v>278</v>
-      </c>
-      <c r="C64" s="58" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="65" spans="2:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B65" s="57" t="s">
-        <v>279</v>
-      </c>
-      <c r="C65" s="58" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="66" spans="2:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B66" s="57" t="s">
-        <v>280</v>
-      </c>
-      <c r="C66" s="58" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="67" spans="2:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B67" s="57" t="s">
-        <v>281</v>
-      </c>
-      <c r="C67" s="58" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="68" spans="2:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B68" s="45"/>
-      <c r="C68" s="54"/>
-    </row>
-    <row r="69" spans="2:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B69" s="55" t="s">
-        <v>219</v>
-      </c>
-      <c r="C69" s="56"/>
-    </row>
-    <row r="70" spans="2:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B70" s="57" t="s">
-        <v>282</v>
-      </c>
-      <c r="C70" s="62" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="71" spans="2:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B71" s="45"/>
-      <c r="C71" s="54"/>
-    </row>
-    <row r="72" spans="2:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B72" s="55" t="s">
-        <v>283</v>
-      </c>
-      <c r="C72" s="56"/>
-    </row>
-    <row r="73" spans="2:3" ht="26.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B73" s="57" t="s">
-        <v>284</v>
-      </c>
-      <c r="C73" s="62" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="74" spans="2:3" ht="26.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B74" s="57" t="s">
-        <v>285</v>
-      </c>
-      <c r="C74" s="58" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="75" spans="2:3" ht="26.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B75" s="57" t="s">
-        <v>286</v>
-      </c>
-      <c r="C75" s="58" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="76" spans="2:3" ht="26.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B76" s="57" t="s">
-        <v>287</v>
-      </c>
-      <c r="C76" s="58" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="77" spans="2:3" ht="26.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B77" s="57" t="s">
-        <v>288</v>
-      </c>
-      <c r="C77" s="58" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="78" spans="2:3" ht="33.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B78" s="57" t="s">
-        <v>289</v>
-      </c>
-      <c r="C78" s="58" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="79" spans="2:3" ht="26.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B79" s="57" t="s">
-        <v>290</v>
-      </c>
-      <c r="C79" s="58" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="80" spans="2:3" ht="26.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B80" s="57" t="s">
-        <v>291</v>
-      </c>
-      <c r="C80" s="58" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="81" spans="2:3" ht="26.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B81" s="57" t="s">
+    <row r="86" spans="2:3" ht="26.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B86" s="56" t="s">
         <v>292</v>
       </c>
-      <c r="C81" s="58" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="82" spans="2:3" ht="26.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B82" s="57" t="s">
-        <v>293</v>
-      </c>
-      <c r="C82" s="58" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="83" spans="2:3" ht="26.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B83" s="57" t="s">
-        <v>294</v>
-      </c>
-      <c r="C83" s="58" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="84" spans="2:3" ht="26.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B84" s="57" t="s">
-        <v>295</v>
-      </c>
-      <c r="C84" s="58" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="85" spans="2:3" ht="26.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B85" s="57" t="s">
-        <v>296</v>
-      </c>
-      <c r="C85" s="58" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="86" spans="2:3" ht="26.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B86" s="57" t="s">
-        <v>297</v>
-      </c>
-      <c r="C86" s="58" t="b">
+      <c r="C86" s="57" t="b">
         <v>0</v>
       </c>
     </row>
@@ -12461,7 +12788,7 @@
     <mergeCell ref="B4:D4"/>
     <mergeCell ref="B5:D5"/>
   </mergeCells>
-  <phoneticPr fontId="24"/>
+  <phoneticPr fontId="21"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -12484,12 +12811,12 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="25"/>
+      <c r="A1" s="24"/>
     </row>
     <row r="2" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="25"/>
+      <c r="A2" s="24"/>
       <c r="B2" s="13" t="s">
-        <v>298</v>
+        <v>293</v>
       </c>
       <c r="C2" s="13"/>
       <c r="D2" s="13"/>
@@ -12513,213 +12840,213 @@
     </row>
     <row r="4" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B4" s="91" t="s">
-        <v>299</v>
+        <v>294</v>
       </c>
       <c r="C4" s="82"/>
       <c r="D4" s="13"/>
       <c r="E4" s="91" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="F4" s="82"/>
       <c r="H4" s="92"/>
       <c r="I4" s="82"/>
-      <c r="J4" s="37"/>
+      <c r="J4" s="36"/>
       <c r="K4" s="92"/>
       <c r="L4" s="82"/>
     </row>
     <row r="5" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B5" s="63" t="s">
+      <c r="B5" s="62" t="s">
+        <v>295</v>
+      </c>
+      <c r="C5" s="62" t="s">
+        <v>296</v>
+      </c>
+      <c r="D5" s="13"/>
+      <c r="E5" s="62" t="s">
+        <v>297</v>
+      </c>
+      <c r="F5" s="63" t="s">
+        <v>296</v>
+      </c>
+      <c r="H5" s="64"/>
+      <c r="I5" s="65"/>
+      <c r="J5" s="36"/>
+      <c r="K5" s="64"/>
+      <c r="L5" s="65"/>
+    </row>
+    <row r="6" spans="1:12" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B6" s="28" t="s">
+        <v>298</v>
+      </c>
+      <c r="C6" s="76" t="s">
+        <v>328</v>
+      </c>
+      <c r="D6" s="13"/>
+      <c r="E6" s="28" t="s">
         <v>300</v>
       </c>
-      <c r="C5" s="63" t="s">
+      <c r="F6" s="28" t="s">
         <v>301</v>
       </c>
-      <c r="D5" s="13"/>
-      <c r="E5" s="63" t="s">
+      <c r="H6" s="66"/>
+      <c r="I6" s="66"/>
+      <c r="J6" s="36"/>
+      <c r="K6" s="66"/>
+      <c r="L6" s="66"/>
+    </row>
+    <row r="7" spans="1:12" ht="76.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B7" s="28" t="s">
+        <v>300</v>
+      </c>
+      <c r="C7" s="76" t="s">
+        <v>327</v>
+      </c>
+      <c r="D7" s="13"/>
+      <c r="E7" s="28" t="s">
         <v>302</v>
       </c>
-      <c r="F5" s="64" t="s">
-        <v>301</v>
-      </c>
-      <c r="H5" s="65"/>
-      <c r="I5" s="66"/>
-      <c r="J5" s="37"/>
-      <c r="K5" s="65"/>
-      <c r="L5" s="66"/>
-    </row>
-    <row r="6" spans="1:12" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B6" s="29" t="s">
+      <c r="F7" s="28" t="s">
         <v>303</v>
       </c>
-      <c r="C6" s="77" t="s">
-        <v>333</v>
-      </c>
-      <c r="D6" s="13"/>
-      <c r="E6" s="29" t="s">
+      <c r="H7" s="66"/>
+      <c r="I7" s="66"/>
+      <c r="J7" s="36"/>
+      <c r="K7" s="66"/>
+      <c r="L7" s="66"/>
+    </row>
+    <row r="8" spans="1:12" ht="69" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B8" s="28" t="s">
+        <v>302</v>
+      </c>
+      <c r="C8" s="76" t="s">
+        <v>329</v>
+      </c>
+      <c r="D8" s="13"/>
+      <c r="E8" s="67" t="s">
         <v>305</v>
       </c>
-      <c r="F6" s="29" t="s">
-        <v>306</v>
-      </c>
-      <c r="H6" s="67"/>
-      <c r="I6" s="67"/>
-      <c r="J6" s="37"/>
-      <c r="K6" s="67"/>
-      <c r="L6" s="67"/>
-    </row>
-    <row r="7" spans="1:12" ht="76.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B7" s="29" t="s">
-        <v>305</v>
-      </c>
-      <c r="C7" s="77" t="s">
-        <v>332</v>
-      </c>
-      <c r="D7" s="13"/>
-      <c r="E7" s="29" t="s">
-        <v>307</v>
-      </c>
-      <c r="F7" s="29" t="s">
-        <v>308</v>
-      </c>
-      <c r="H7" s="67"/>
-      <c r="I7" s="67"/>
-      <c r="J7" s="37"/>
-      <c r="K7" s="67"/>
-      <c r="L7" s="67"/>
-    </row>
-    <row r="8" spans="1:12" ht="69" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B8" s="29" t="s">
-        <v>307</v>
-      </c>
-      <c r="C8" s="77" t="s">
-        <v>334</v>
-      </c>
-      <c r="D8" s="13"/>
-      <c r="E8" s="68" t="s">
-        <v>310</v>
-      </c>
-      <c r="F8" s="25"/>
-      <c r="H8" s="67"/>
-      <c r="I8" s="67"/>
-      <c r="J8" s="37"/>
-      <c r="K8" s="67"/>
-      <c r="L8" s="67"/>
+      <c r="F8" s="24"/>
+      <c r="H8" s="66"/>
+      <c r="I8" s="66"/>
+      <c r="J8" s="36"/>
+      <c r="K8" s="66"/>
+      <c r="L8" s="66"/>
     </row>
     <row r="9" spans="1:12" ht="80.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B9" s="78" t="s">
-        <v>336</v>
-      </c>
-      <c r="C9" s="77" t="s">
-        <v>335</v>
+      <c r="B9" s="77" t="s">
+        <v>331</v>
+      </c>
+      <c r="C9" s="76" t="s">
+        <v>330</v>
       </c>
       <c r="D9" s="13"/>
-      <c r="E9" s="25"/>
-      <c r="F9" s="25"/>
-      <c r="H9" s="67"/>
-      <c r="I9" s="67"/>
-      <c r="J9" s="37"/>
-      <c r="K9" s="67"/>
-      <c r="L9" s="67"/>
+      <c r="E9" s="24"/>
+      <c r="F9" s="24"/>
+      <c r="H9" s="66"/>
+      <c r="I9" s="66"/>
+      <c r="J9" s="36"/>
+      <c r="K9" s="66"/>
+      <c r="L9" s="66"/>
     </row>
     <row r="10" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B10" s="13"/>
       <c r="C10" s="13"/>
       <c r="D10" s="13"/>
-      <c r="E10" s="25"/>
-      <c r="F10" s="25"/>
-      <c r="H10" s="67"/>
-      <c r="I10" s="67"/>
-      <c r="J10" s="37"/>
-      <c r="K10" s="67"/>
-      <c r="L10" s="67"/>
+      <c r="E10" s="24"/>
+      <c r="F10" s="24"/>
+      <c r="H10" s="66"/>
+      <c r="I10" s="66"/>
+      <c r="J10" s="36"/>
+      <c r="K10" s="66"/>
+      <c r="L10" s="66"/>
     </row>
     <row r="11" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B11" s="91" t="s">
-        <v>312</v>
+        <v>307</v>
       </c>
       <c r="C11" s="82"/>
       <c r="D11" s="13"/>
       <c r="E11" s="91" t="s">
-        <v>116</v>
+        <v>111</v>
       </c>
       <c r="F11" s="82"/>
     </row>
     <row r="12" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B12" s="63" t="s">
-        <v>302</v>
-      </c>
-      <c r="C12" s="64" t="s">
-        <v>301</v>
-      </c>
-      <c r="E12" s="63" t="s">
-        <v>302</v>
-      </c>
-      <c r="F12" s="64" t="s">
-        <v>301</v>
+      <c r="B12" s="62" t="s">
+        <v>297</v>
+      </c>
+      <c r="C12" s="63" t="s">
+        <v>296</v>
+      </c>
+      <c r="E12" s="62" t="s">
+        <v>297</v>
+      </c>
+      <c r="F12" s="63" t="s">
+        <v>296</v>
       </c>
     </row>
     <row r="13" spans="1:12" ht="29.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B13" s="29" t="s">
+      <c r="B13" s="28" t="s">
+        <v>308</v>
+      </c>
+      <c r="C13" s="28" t="s">
+        <v>309</v>
+      </c>
+      <c r="E13" s="28" t="s">
+        <v>298</v>
+      </c>
+      <c r="F13" s="28" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12" ht="56.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B14" s="24"/>
+      <c r="C14" s="24"/>
+      <c r="E14" s="28" t="s">
+        <v>300</v>
+      </c>
+      <c r="F14" s="28" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12" ht="44.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B15" s="24"/>
+      <c r="C15" s="24"/>
+      <c r="E15" s="28" t="s">
+        <v>311</v>
+      </c>
+      <c r="F15" s="28" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12" ht="58.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B16" s="24"/>
+      <c r="C16" s="24"/>
+      <c r="E16" s="28" t="s">
+        <v>312</v>
+      </c>
+      <c r="F16" s="28" t="s">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="17" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B17" s="24"/>
+      <c r="C17" s="24"/>
+      <c r="E17" s="28" t="s">
         <v>313</v>
       </c>
-      <c r="C13" s="29" t="s">
+      <c r="F17" s="28" t="s">
         <v>314</v>
       </c>
-      <c r="E13" s="29" t="s">
-        <v>303</v>
-      </c>
-      <c r="F13" s="29" t="s">
-        <v>304</v>
-      </c>
-    </row>
-    <row r="14" spans="1:12" ht="56.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B14" s="25"/>
-      <c r="C14" s="25"/>
-      <c r="E14" s="29" t="s">
-        <v>305</v>
-      </c>
-      <c r="F14" s="29" t="s">
+    </row>
+    <row r="18" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B18" s="24"/>
+      <c r="C18" s="24"/>
+      <c r="E18" s="28" t="s">
         <v>315</v>
       </c>
-    </row>
-    <row r="15" spans="1:12" ht="44.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B15" s="25"/>
-      <c r="C15" s="25"/>
-      <c r="E15" s="29" t="s">
+      <c r="F18" s="28" t="s">
         <v>316</v>
-      </c>
-      <c r="F15" s="29" t="s">
-        <v>309</v>
-      </c>
-    </row>
-    <row r="16" spans="1:12" ht="58.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B16" s="25"/>
-      <c r="C16" s="25"/>
-      <c r="E16" s="29" t="s">
-        <v>317</v>
-      </c>
-      <c r="F16" s="29" t="s">
-        <v>311</v>
-      </c>
-    </row>
-    <row r="17" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B17" s="25"/>
-      <c r="C17" s="25"/>
-      <c r="E17" s="29" t="s">
-        <v>318</v>
-      </c>
-      <c r="F17" s="29" t="s">
-        <v>319</v>
-      </c>
-    </row>
-    <row r="18" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B18" s="25"/>
-      <c r="C18" s="25"/>
-      <c r="E18" s="29" t="s">
-        <v>320</v>
-      </c>
-      <c r="F18" s="29" t="s">
-        <v>321</v>
       </c>
     </row>
     <row r="19" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
@@ -13713,7 +14040,7 @@
     <mergeCell ref="B11:C11"/>
     <mergeCell ref="E11:F11"/>
   </mergeCells>
-  <phoneticPr fontId="24"/>
+  <phoneticPr fontId="21"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/簡易基本設計書【Laravel9】.xlsx
+++ b/簡易基本設計書【Laravel9】.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\daiki\Desktop\Atlas\AtlasSNS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F3C1729D-B39B-45AB-AF59-6EF8544DEC91}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{23983D88-53CE-42E6-A271-80AAF9E25E07}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3244,7 +3244,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="94">
+  <cellXfs count="93">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -3442,7 +3442,6 @@
     <xf numFmtId="0" fontId="16" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="標準" xfId="0" builtinId="0"/>
@@ -5138,13 +5137,13 @@
       </c>
     </row>
     <row r="22" spans="1:26" ht="38.25" x14ac:dyDescent="0.2">
-      <c r="B22" s="7" t="s">
+      <c r="B22" s="68" t="s">
         <v>11</v>
       </c>
-      <c r="C22" s="93" t="s">
+      <c r="C22" s="73" t="s">
         <v>337</v>
       </c>
-      <c r="D22" s="11" t="s">
+      <c r="D22" s="78" t="s">
         <v>21</v>
       </c>
     </row>
